--- a/Bibsam_tidskriftslistor/scifree_data_mdpi.xlsx
+++ b/Bibsam_tidskriftslistor/scifree_data_mdpi.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="12" documentId="11_C5DB10D597D522075C1461CA31825FBE1B289501" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3C7D7242-0CCF-4A79-B8CC-BBAEAC70B640}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34E955A1-A6A9-46DB-A3CC-FC087901CAFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="3" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="4" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2719" uniqueCount="1366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3013" uniqueCount="1513">
   <si>
     <t>ISSN Electronic</t>
   </si>
@@ -3394,9 +3394,6 @@
     <t>Engineering Proceedings</t>
   </si>
   <si>
-    <t>Environmental Sciences Proceedings</t>
-  </si>
-  <si>
     <t>FinTech</t>
   </si>
   <si>
@@ -3553,9 +3550,6 @@
     <t>2673-4591</t>
   </si>
   <si>
-    <t>2673-4931</t>
-  </si>
-  <si>
     <t>2674-1032</t>
   </si>
   <si>
@@ -3712,9 +3706,6 @@
     <t>https://www.mdpi.com/journal/engproc</t>
   </si>
   <si>
-    <t>https://www.mdpi.com/journal/environsciproc</t>
-  </si>
-  <si>
     <t>https://www.mdpi.com/journal/fintech</t>
   </si>
   <si>
@@ -4118,6 +4109,456 @@
   </si>
   <si>
     <t>https://www.mdpi.com/journal/wild</t>
+  </si>
+  <si>
+    <t>3042-6618</t>
+  </si>
+  <si>
+    <t>Accounting and Auditing</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/accountaudit</t>
+  </si>
+  <si>
+    <t>3042-6081</t>
+  </si>
+  <si>
+    <t>Adhesives</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/adhesives</t>
+  </si>
+  <si>
+    <t>3042-6723</t>
+  </si>
+  <si>
+    <t>AI Chemistry</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/aichem</t>
+  </si>
+  <si>
+    <t>3042-8831</t>
+  </si>
+  <si>
+    <t>AI for Engineering</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/aieng</t>
+  </si>
+  <si>
+    <t>3042-8130</t>
+  </si>
+  <si>
+    <t>AI in Education</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/aieduc</t>
+  </si>
+  <si>
+    <t>3042-6707</t>
+  </si>
+  <si>
+    <t>AI in Medicine</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/aimed</t>
+  </si>
+  <si>
+    <t>3042-6715</t>
+  </si>
+  <si>
+    <t>AI Materials</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/aimater</t>
+  </si>
+  <si>
+    <t>3042-5999</t>
+  </si>
+  <si>
+    <t>AI Sensors</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/aisens</t>
+  </si>
+  <si>
+    <t>3042-8491</t>
+  </si>
+  <si>
+    <t>Analog</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/analog</t>
+  </si>
+  <si>
+    <t>3042-6553</t>
+  </si>
+  <si>
+    <t>AppliedPhys</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/appliedphys</t>
+  </si>
+  <si>
+    <t>3042-7576</t>
+  </si>
+  <si>
+    <t>Astronautics</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/astronautics</t>
+  </si>
+  <si>
+    <t>3042-8092</t>
+  </si>
+  <si>
+    <t>Bioresources and Bioproducts</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/bioresourbioprod</t>
+  </si>
+  <si>
+    <t>3042-6111</t>
+  </si>
+  <si>
+    <t>Biosphere</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/biosphere</t>
+  </si>
+  <si>
+    <t>1664-204X</t>
+  </si>
+  <si>
+    <t>Cardiovascular Medicine</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/cardiovascmed</t>
+  </si>
+  <si>
+    <t>3042-5158</t>
+  </si>
+  <si>
+    <t>Clinical Bioenergetics</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/clinbioenerg</t>
+  </si>
+  <si>
+    <t>3042-6448</t>
+  </si>
+  <si>
+    <t>Complexities</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/complexities</t>
+  </si>
+  <si>
+    <t>1943-3883</t>
+  </si>
+  <si>
+    <t>Craniomaxillofacial Trauma &amp; Reconstruction</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/cmtr</t>
+  </si>
+  <si>
+    <t>3042-8165</t>
+  </si>
+  <si>
+    <t>Culture</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/culture</t>
+  </si>
+  <si>
+    <t>3042-7592</t>
+  </si>
+  <si>
+    <t>Entropic and Disordered Matter</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/edm</t>
+  </si>
+  <si>
+    <t>3042-5743</t>
+  </si>
+  <si>
+    <t>Environmental and Earth Sciences Proceedings</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/eesp</t>
+  </si>
+  <si>
+    <t>3042-6693</t>
+  </si>
+  <si>
+    <t>Family Sciences</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/famsci</t>
+  </si>
+  <si>
+    <t>2248-2997</t>
+  </si>
+  <si>
+    <t>GERMS</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/germs</t>
+  </si>
+  <si>
+    <t>3042-5832</t>
+  </si>
+  <si>
+    <t>Green Health</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/greenhealth</t>
+  </si>
+  <si>
+    <t>3042-8432</t>
+  </si>
+  <si>
+    <t>Hydropower</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/hydropower</t>
+  </si>
+  <si>
+    <t>3042-8084</t>
+  </si>
+  <si>
+    <t>International Journal of Cognitive Sciences</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/ijcs</t>
+  </si>
+  <si>
+    <t>3042-7681</t>
+  </si>
+  <si>
+    <t>International Journal of Environmental Medicine</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/ijem</t>
+  </si>
+  <si>
+    <t>2694-2526</t>
+  </si>
+  <si>
+    <t>International Journal of Orofacial Myology and Myofunctional Therapy</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/ijom</t>
+  </si>
+  <si>
+    <t>3042-6774</t>
+  </si>
+  <si>
+    <t>Journal of Aesthetic Medicine</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/jaestheticmed</t>
+  </si>
+  <si>
+    <t>3042-6987</t>
+  </si>
+  <si>
+    <t>Journal of CardioRenal Medicine</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/jcrm</t>
+  </si>
+  <si>
+    <t>1995-8692</t>
+  </si>
+  <si>
+    <t>Journal of Eye Movement Research</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/jemr</t>
+  </si>
+  <si>
+    <t>2392-7674</t>
+  </si>
+  <si>
+    <t>Journal of Mind and Medical Sciences</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/jmms</t>
+  </si>
+  <si>
+    <t>3042-5689</t>
+  </si>
+  <si>
+    <t>Journal of Parks</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/jop</t>
+  </si>
+  <si>
+    <t>3042-7886</t>
+  </si>
+  <si>
+    <t>Lights</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/lights</t>
+  </si>
+  <si>
+    <t>3042-5344</t>
+  </si>
+  <si>
+    <t>Microelectronics</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/microelectronics</t>
+  </si>
+  <si>
+    <t>3042-5697</t>
+  </si>
+  <si>
+    <t>Microwave</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/microwave</t>
+  </si>
+  <si>
+    <t>3042-5034</t>
+  </si>
+  <si>
+    <t>Modern Mathematical Physics</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/mmphys</t>
+  </si>
+  <si>
+    <t>3042-6308</t>
+  </si>
+  <si>
+    <t>Multimedia</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/multimedia</t>
+  </si>
+  <si>
+    <t>3042-8807</t>
+  </si>
+  <si>
+    <t>Neuroimaging</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/neuroimaging</t>
+  </si>
+  <si>
+    <t>3042-8637</t>
+  </si>
+  <si>
+    <t>Occupational Health</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/occuphealth</t>
+  </si>
+  <si>
+    <t>3042-6529</t>
+  </si>
+  <si>
+    <t>Peace Studies</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/peacestud</t>
+  </si>
+  <si>
+    <t>3042-7614</t>
+  </si>
+  <si>
+    <t>Precision Oncology</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/precisoncol</t>
+  </si>
+  <si>
+    <t>3042-6197</t>
+  </si>
+  <si>
+    <t>Purification</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/purification</t>
+  </si>
+  <si>
+    <t>3091-101X</t>
+  </si>
+  <si>
+    <t>Romanian Journal of Preventive Medicine</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/rjpm</t>
+  </si>
+  <si>
+    <t>3042-9013</t>
+  </si>
+  <si>
+    <t>Semiconductors and Heterogeneous Integration</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/shi</t>
+  </si>
+  <si>
+    <t>3042-7126</t>
+  </si>
+  <si>
+    <t>Theoretical and Applied Ergonomics</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/tae</t>
+  </si>
+  <si>
+    <t>3042-8629</t>
+  </si>
+  <si>
+    <t>Journal of Innovation</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/joi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3042-9250 </t>
+  </si>
+  <si>
+    <t>Journal of Phytomedicine</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/jphytomed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3042-934X </t>
+  </si>
+  <si>
+    <t>Low-altitude Economy</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/lae</t>
+  </si>
+  <si>
+    <t>3042-8181</t>
+  </si>
+  <si>
+    <t>Trends in Public Health</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/tph</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3042-884X </t>
+  </si>
+  <si>
+    <t>Stratigraphy and Sedimentology</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/stratsediment</t>
   </si>
 </sst>
 </file>
@@ -4173,19 +4614,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AE60BD86-4877-4D7F-B7C4-38C48A89E2E2}" name="Table1" displayName="Table1" ref="A1:G453" totalsRowShown="0">
-  <autoFilter ref="A1:G453" xr:uid="{AE60BD86-4877-4D7F-B7C4-38C48A89E2E2}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G453">
-    <sortCondition ref="D1:D453"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{CE28C0A4-819D-4EF0-9CDA-5E28E0FCFC65}" name="Table2" displayName="Table2" ref="A1:G502" totalsRowShown="0">
+  <autoFilter ref="A1:G502" xr:uid="{CE28C0A4-819D-4EF0-9CDA-5E28E0FCFC65}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G502">
+    <sortCondition ref="D1:D502"/>
   </sortState>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{A7B4B871-D965-4870-B24E-5DEC07E43020}" name="Imprint"/>
-    <tableColumn id="2" xr3:uid="{E1B86DDB-A63C-485E-812D-97E65DD93895}" name="ISSN Electronic"/>
-    <tableColumn id="3" xr3:uid="{5C45E9AD-9D7E-4B36-B62E-6230F5F76681}" name="ISSN Print"/>
-    <tableColumn id="4" xr3:uid="{A756B155-37C3-4242-A71F-BFFA111B2BB9}" name="Journal Name"/>
-    <tableColumn id="5" xr3:uid="{892679C2-A5ED-450E-850F-7B8B2E7C3E6B}" name="JournalURL"/>
-    <tableColumn id="6" xr3:uid="{979B6879-735C-4432-BE9B-607548D03C92}" name="Publishing model"/>
-    <tableColumn id="7" xr3:uid="{25DF5ED7-8B41-4BB9-A386-033D2C262566}" name="CC License options"/>
+    <tableColumn id="1" xr3:uid="{475A72F7-1A1D-4F9A-8D5B-FCE65FA3E5BF}" name="Imprint"/>
+    <tableColumn id="2" xr3:uid="{495E640A-875C-487F-AF2A-F18761EF9C60}" name="ISSN Electronic"/>
+    <tableColumn id="3" xr3:uid="{291B4D49-C825-4DEA-A685-601CC0CC385A}" name="ISSN Print"/>
+    <tableColumn id="4" xr3:uid="{D648F120-C27D-4084-88E0-8DE051AFA388}" name="Journal Name"/>
+    <tableColumn id="5" xr3:uid="{F707CF57-6C74-46E4-BC69-4F2587D5F76D}" name="JournalURL"/>
+    <tableColumn id="6" xr3:uid="{05808A9A-F97F-4D77-ADF2-AA5A47148DC0}" name="Publishing model"/>
+    <tableColumn id="7" xr3:uid="{E328D4DB-D0EE-4DC2-87B8-E1192C3CD74A}" name="CC License options"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4453,8 +4894,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05938FE4-CBEB-4631-A995-4DF7145669AC}">
-  <dimension ref="A1:G453"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5117B6EE-D8F2-49E5-ACBB-C4662ACB3D37}">
+  <dimension ref="A1:G502"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" customWidth="1"/>
@@ -4494,13 +4935,13 @@
         <v>425</v>
       </c>
       <c r="B2" t="s">
-        <v>793</v>
+        <v>1363</v>
       </c>
       <c r="D2" t="s">
-        <v>8</v>
+        <v>1364</v>
       </c>
       <c r="E2" t="s">
-        <v>426</v>
+        <v>1365</v>
       </c>
       <c r="F2" t="s">
         <v>792</v>
@@ -4514,13 +4955,13 @@
         <v>425</v>
       </c>
       <c r="B3" t="s">
-        <v>1300</v>
+        <v>793</v>
       </c>
       <c r="D3" t="s">
-        <v>1301</v>
+        <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>1302</v>
+        <v>426</v>
       </c>
       <c r="F3" t="s">
         <v>792</v>
@@ -4534,13 +4975,13 @@
         <v>425</v>
       </c>
       <c r="B4" t="s">
-        <v>794</v>
+        <v>1297</v>
       </c>
       <c r="D4" t="s">
-        <v>9</v>
+        <v>1298</v>
       </c>
       <c r="E4" t="s">
-        <v>427</v>
+        <v>1299</v>
       </c>
       <c r="F4" t="s">
         <v>792</v>
@@ -4554,13 +4995,13 @@
         <v>425</v>
       </c>
       <c r="B5" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="D5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F5" t="s">
         <v>792</v>
@@ -4574,13 +5015,13 @@
         <v>425</v>
       </c>
       <c r="B6" t="s">
-        <v>796</v>
+        <v>1366</v>
       </c>
       <c r="D6" t="s">
-        <v>11</v>
+        <v>1367</v>
       </c>
       <c r="E6" t="s">
-        <v>429</v>
+        <v>1368</v>
       </c>
       <c r="F6" t="s">
         <v>792</v>
@@ -4594,13 +5035,13 @@
         <v>425</v>
       </c>
       <c r="B7" t="s">
-        <v>1161</v>
+        <v>795</v>
       </c>
       <c r="D7" t="s">
-        <v>1108</v>
+        <v>10</v>
       </c>
       <c r="E7" t="s">
-        <v>1214</v>
+        <v>428</v>
       </c>
       <c r="F7" t="s">
         <v>792</v>
@@ -4614,13 +5055,13 @@
         <v>425</v>
       </c>
       <c r="B8" t="s">
-        <v>1267</v>
+        <v>796</v>
       </c>
       <c r="D8" t="s">
-        <v>1268</v>
+        <v>11</v>
       </c>
       <c r="E8" t="s">
-        <v>1269</v>
+        <v>429</v>
       </c>
       <c r="F8" t="s">
         <v>792</v>
@@ -4634,13 +5075,13 @@
         <v>425</v>
       </c>
       <c r="B9" t="s">
-        <v>797</v>
+        <v>1160</v>
       </c>
       <c r="D9" t="s">
-        <v>12</v>
+        <v>1108</v>
       </c>
       <c r="E9" t="s">
-        <v>430</v>
+        <v>1212</v>
       </c>
       <c r="F9" t="s">
         <v>792</v>
@@ -4654,13 +5095,13 @@
         <v>425</v>
       </c>
       <c r="B10" t="s">
-        <v>798</v>
+        <v>1264</v>
       </c>
       <c r="D10" t="s">
-        <v>13</v>
+        <v>1265</v>
       </c>
       <c r="E10" t="s">
-        <v>431</v>
+        <v>1266</v>
       </c>
       <c r="F10" t="s">
         <v>792</v>
@@ -4674,13 +5115,13 @@
         <v>425</v>
       </c>
       <c r="B11" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="D11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E11" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="F11" t="s">
         <v>792</v>
@@ -4694,13 +5135,13 @@
         <v>425</v>
       </c>
       <c r="B12" t="s">
-        <v>1162</v>
+        <v>798</v>
       </c>
       <c r="D12" t="s">
-        <v>1109</v>
+        <v>13</v>
       </c>
       <c r="E12" t="s">
-        <v>1215</v>
+        <v>431</v>
       </c>
       <c r="F12" t="s">
         <v>792</v>
@@ -4714,13 +5155,13 @@
         <v>425</v>
       </c>
       <c r="B13" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="D13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E13" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="F13" t="s">
         <v>792</v>
@@ -4734,13 +5175,13 @@
         <v>425</v>
       </c>
       <c r="B14" t="s">
-        <v>801</v>
+        <v>1161</v>
       </c>
       <c r="D14" t="s">
-        <v>16</v>
+        <v>1109</v>
       </c>
       <c r="E14" t="s">
-        <v>434</v>
+        <v>1213</v>
       </c>
       <c r="F14" t="s">
         <v>792</v>
@@ -4754,13 +5195,13 @@
         <v>425</v>
       </c>
       <c r="B15" t="s">
-        <v>1163</v>
+        <v>800</v>
       </c>
       <c r="D15" t="s">
-        <v>1110</v>
+        <v>15</v>
       </c>
       <c r="E15" t="s">
-        <v>1216</v>
+        <v>433</v>
       </c>
       <c r="F15" t="s">
         <v>792</v>
@@ -4774,13 +5215,13 @@
         <v>425</v>
       </c>
       <c r="B16" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="D16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E16" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="F16" t="s">
         <v>792</v>
@@ -4794,13 +5235,13 @@
         <v>425</v>
       </c>
       <c r="B17" t="s">
-        <v>803</v>
+        <v>1369</v>
       </c>
       <c r="D17" t="s">
-        <v>18</v>
+        <v>1370</v>
       </c>
       <c r="E17" t="s">
-        <v>436</v>
+        <v>1371</v>
       </c>
       <c r="F17" t="s">
         <v>792</v>
@@ -4814,13 +5255,13 @@
         <v>425</v>
       </c>
       <c r="B18" t="s">
-        <v>1164</v>
+        <v>1372</v>
       </c>
       <c r="D18" t="s">
-        <v>1111</v>
+        <v>1373</v>
       </c>
       <c r="E18" t="s">
-        <v>1217</v>
+        <v>1374</v>
       </c>
       <c r="F18" t="s">
         <v>792</v>
@@ -4834,13 +5275,13 @@
         <v>425</v>
       </c>
       <c r="B19" t="s">
-        <v>804</v>
+        <v>1375</v>
       </c>
       <c r="D19" t="s">
-        <v>19</v>
+        <v>1376</v>
       </c>
       <c r="E19" t="s">
-        <v>437</v>
+        <v>1377</v>
       </c>
       <c r="F19" t="s">
         <v>792</v>
@@ -4854,13 +5295,13 @@
         <v>425</v>
       </c>
       <c r="B20" t="s">
-        <v>1165</v>
+        <v>1378</v>
       </c>
       <c r="D20" t="s">
-        <v>1112</v>
+        <v>1379</v>
       </c>
       <c r="E20" t="s">
-        <v>1218</v>
+        <v>1380</v>
       </c>
       <c r="F20" t="s">
         <v>792</v>
@@ -4874,13 +5315,13 @@
         <v>425</v>
       </c>
       <c r="B21" t="s">
-        <v>1166</v>
+        <v>1381</v>
       </c>
       <c r="D21" t="s">
-        <v>1113</v>
+        <v>1382</v>
       </c>
       <c r="E21" t="s">
-        <v>1219</v>
+        <v>1383</v>
       </c>
       <c r="F21" t="s">
         <v>792</v>
@@ -4894,13 +5335,13 @@
         <v>425</v>
       </c>
       <c r="B22" t="s">
-        <v>1270</v>
+        <v>1384</v>
       </c>
       <c r="D22" t="s">
-        <v>1271</v>
+        <v>1385</v>
       </c>
       <c r="E22" t="s">
-        <v>1272</v>
+        <v>1386</v>
       </c>
       <c r="F22" t="s">
         <v>792</v>
@@ -4914,13 +5355,13 @@
         <v>425</v>
       </c>
       <c r="B23" t="s">
-        <v>805</v>
+        <v>1162</v>
       </c>
       <c r="D23" t="s">
-        <v>20</v>
+        <v>1110</v>
       </c>
       <c r="E23" t="s">
-        <v>438</v>
+        <v>1214</v>
       </c>
       <c r="F23" t="s">
         <v>792</v>
@@ -4934,13 +5375,13 @@
         <v>425</v>
       </c>
       <c r="B24" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="D24" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E24" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="F24" t="s">
         <v>792</v>
@@ -4954,13 +5395,13 @@
         <v>425</v>
       </c>
       <c r="B25" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
       <c r="D25" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E25" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="F25" t="s">
         <v>792</v>
@@ -4974,13 +5415,13 @@
         <v>425</v>
       </c>
       <c r="B26" t="s">
-        <v>808</v>
+        <v>1163</v>
       </c>
       <c r="D26" t="s">
-        <v>23</v>
+        <v>1111</v>
       </c>
       <c r="E26" t="s">
-        <v>441</v>
+        <v>1215</v>
       </c>
       <c r="F26" t="s">
         <v>792</v>
@@ -4994,13 +5435,13 @@
         <v>425</v>
       </c>
       <c r="B27" t="s">
-        <v>1167</v>
+        <v>1387</v>
       </c>
       <c r="D27" t="s">
-        <v>1114</v>
+        <v>1388</v>
       </c>
       <c r="E27" t="s">
-        <v>1220</v>
+        <v>1389</v>
       </c>
       <c r="F27" t="s">
         <v>792</v>
@@ -5014,13 +5455,13 @@
         <v>425</v>
       </c>
       <c r="B28" t="s">
-        <v>809</v>
+        <v>804</v>
       </c>
       <c r="D28" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E28" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="F28" t="s">
         <v>792</v>
@@ -5034,13 +5475,13 @@
         <v>425</v>
       </c>
       <c r="B29" t="s">
-        <v>810</v>
+        <v>1164</v>
       </c>
       <c r="D29" t="s">
-        <v>25</v>
+        <v>1112</v>
       </c>
       <c r="E29" t="s">
-        <v>443</v>
+        <v>1216</v>
       </c>
       <c r="F29" t="s">
         <v>792</v>
@@ -5054,13 +5495,13 @@
         <v>425</v>
       </c>
       <c r="B30" t="s">
-        <v>811</v>
+        <v>1165</v>
       </c>
       <c r="D30" t="s">
-        <v>26</v>
+        <v>1113</v>
       </c>
       <c r="E30" t="s">
-        <v>444</v>
+        <v>1217</v>
       </c>
       <c r="F30" t="s">
         <v>792</v>
@@ -5074,13 +5515,13 @@
         <v>425</v>
       </c>
       <c r="B31" t="s">
-        <v>812</v>
+        <v>1267</v>
       </c>
       <c r="D31" t="s">
-        <v>27</v>
+        <v>1268</v>
       </c>
       <c r="E31" t="s">
-        <v>445</v>
+        <v>1269</v>
       </c>
       <c r="F31" t="s">
         <v>792</v>
@@ -5094,13 +5535,13 @@
         <v>425</v>
       </c>
       <c r="B32" t="s">
-        <v>813</v>
+        <v>805</v>
       </c>
       <c r="D32" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="E32" t="s">
-        <v>446</v>
+        <v>438</v>
       </c>
       <c r="F32" t="s">
         <v>792</v>
@@ -5114,13 +5555,13 @@
         <v>425</v>
       </c>
       <c r="B33" t="s">
-        <v>814</v>
+        <v>806</v>
       </c>
       <c r="D33" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="E33" t="s">
-        <v>447</v>
+        <v>439</v>
       </c>
       <c r="F33" t="s">
         <v>792</v>
@@ -5134,13 +5575,13 @@
         <v>425</v>
       </c>
       <c r="B34" t="s">
-        <v>815</v>
+        <v>807</v>
       </c>
       <c r="D34" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="E34" t="s">
-        <v>448</v>
+        <v>440</v>
       </c>
       <c r="F34" t="s">
         <v>792</v>
@@ -5154,13 +5595,13 @@
         <v>425</v>
       </c>
       <c r="B35" t="s">
-        <v>816</v>
+        <v>808</v>
       </c>
       <c r="D35" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="E35" t="s">
-        <v>449</v>
+        <v>441</v>
       </c>
       <c r="F35" t="s">
         <v>792</v>
@@ -5174,13 +5615,13 @@
         <v>425</v>
       </c>
       <c r="B36" t="s">
-        <v>817</v>
+        <v>1166</v>
       </c>
       <c r="D36" t="s">
-        <v>32</v>
+        <v>1114</v>
       </c>
       <c r="E36" t="s">
-        <v>450</v>
+        <v>1218</v>
       </c>
       <c r="F36" t="s">
         <v>792</v>
@@ -5194,13 +5635,13 @@
         <v>425</v>
       </c>
       <c r="B37" t="s">
-        <v>1168</v>
+        <v>809</v>
       </c>
       <c r="D37" t="s">
-        <v>1115</v>
+        <v>24</v>
       </c>
       <c r="E37" t="s">
-        <v>1221</v>
+        <v>442</v>
       </c>
       <c r="F37" t="s">
         <v>792</v>
@@ -5214,13 +5655,13 @@
         <v>425</v>
       </c>
       <c r="B38" t="s">
-        <v>818</v>
+        <v>810</v>
       </c>
       <c r="D38" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="E38" t="s">
-        <v>451</v>
+        <v>443</v>
       </c>
       <c r="F38" t="s">
         <v>792</v>
@@ -5234,13 +5675,13 @@
         <v>425</v>
       </c>
       <c r="B39" t="s">
-        <v>819</v>
+        <v>811</v>
       </c>
       <c r="D39" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E39" t="s">
-        <v>452</v>
+        <v>444</v>
       </c>
       <c r="F39" t="s">
         <v>792</v>
@@ -5254,13 +5695,13 @@
         <v>425</v>
       </c>
       <c r="B40" t="s">
-        <v>820</v>
+        <v>812</v>
       </c>
       <c r="D40" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="E40" t="s">
-        <v>453</v>
+        <v>445</v>
       </c>
       <c r="F40" t="s">
         <v>792</v>
@@ -5274,13 +5715,13 @@
         <v>425</v>
       </c>
       <c r="B41" t="s">
-        <v>821</v>
+        <v>813</v>
       </c>
       <c r="D41" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="E41" t="s">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="F41" t="s">
         <v>792</v>
@@ -5294,13 +5735,13 @@
         <v>425</v>
       </c>
       <c r="B42" t="s">
-        <v>822</v>
+        <v>814</v>
       </c>
       <c r="D42" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="E42" t="s">
-        <v>455</v>
+        <v>447</v>
       </c>
       <c r="F42" t="s">
         <v>792</v>
@@ -5314,13 +5755,13 @@
         <v>425</v>
       </c>
       <c r="B43" t="s">
-        <v>823</v>
+        <v>815</v>
       </c>
       <c r="D43" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="E43" t="s">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="F43" t="s">
         <v>792</v>
@@ -5334,13 +5775,13 @@
         <v>425</v>
       </c>
       <c r="B44" t="s">
-        <v>824</v>
+        <v>1390</v>
       </c>
       <c r="D44" t="s">
-        <v>39</v>
+        <v>1391</v>
       </c>
       <c r="E44" t="s">
-        <v>457</v>
+        <v>1392</v>
       </c>
       <c r="F44" t="s">
         <v>792</v>
@@ -5354,13 +5795,13 @@
         <v>425</v>
       </c>
       <c r="B45" t="s">
-        <v>1169</v>
+        <v>816</v>
       </c>
       <c r="D45" t="s">
-        <v>1116</v>
+        <v>31</v>
       </c>
       <c r="E45" t="s">
-        <v>1222</v>
+        <v>449</v>
       </c>
       <c r="F45" t="s">
         <v>792</v>
@@ -5374,13 +5815,13 @@
         <v>425</v>
       </c>
       <c r="B46" t="s">
-        <v>825</v>
+        <v>817</v>
       </c>
       <c r="D46" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="E46" t="s">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="F46" t="s">
         <v>792</v>
@@ -5394,13 +5835,13 @@
         <v>425</v>
       </c>
       <c r="B47" t="s">
-        <v>826</v>
+        <v>1167</v>
       </c>
       <c r="D47" t="s">
-        <v>41</v>
+        <v>1115</v>
       </c>
       <c r="E47" t="s">
-        <v>459</v>
+        <v>1219</v>
       </c>
       <c r="F47" t="s">
         <v>792</v>
@@ -5414,13 +5855,13 @@
         <v>425</v>
       </c>
       <c r="B48" t="s">
-        <v>827</v>
+        <v>818</v>
       </c>
       <c r="D48" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="E48" t="s">
-        <v>460</v>
+        <v>451</v>
       </c>
       <c r="F48" t="s">
         <v>792</v>
@@ -5434,13 +5875,13 @@
         <v>425</v>
       </c>
       <c r="B49" t="s">
-        <v>828</v>
+        <v>1393</v>
       </c>
       <c r="D49" t="s">
-        <v>43</v>
+        <v>1394</v>
       </c>
       <c r="E49" t="s">
-        <v>461</v>
+        <v>1395</v>
       </c>
       <c r="F49" t="s">
         <v>792</v>
@@ -5454,13 +5895,13 @@
         <v>425</v>
       </c>
       <c r="B50" t="s">
-        <v>829</v>
+        <v>819</v>
       </c>
       <c r="D50" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="E50" t="s">
-        <v>462</v>
+        <v>452</v>
       </c>
       <c r="F50" t="s">
         <v>792</v>
@@ -5474,13 +5915,13 @@
         <v>425</v>
       </c>
       <c r="B51" t="s">
-        <v>830</v>
+        <v>820</v>
       </c>
       <c r="D51" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="E51" t="s">
-        <v>463</v>
+        <v>453</v>
       </c>
       <c r="F51" t="s">
         <v>792</v>
@@ -5494,13 +5935,13 @@
         <v>425</v>
       </c>
       <c r="B52" t="s">
-        <v>831</v>
+        <v>821</v>
       </c>
       <c r="D52" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="E52" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="F52" t="s">
         <v>792</v>
@@ -5514,13 +5955,13 @@
         <v>425</v>
       </c>
       <c r="B53" t="s">
-        <v>832</v>
+        <v>822</v>
       </c>
       <c r="D53" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="E53" t="s">
-        <v>465</v>
+        <v>455</v>
       </c>
       <c r="F53" t="s">
         <v>792</v>
@@ -5534,13 +5975,13 @@
         <v>425</v>
       </c>
       <c r="B54" t="s">
-        <v>1170</v>
+        <v>823</v>
       </c>
       <c r="D54" t="s">
-        <v>1117</v>
+        <v>38</v>
       </c>
       <c r="E54" t="s">
-        <v>1223</v>
+        <v>456</v>
       </c>
       <c r="F54" t="s">
         <v>792</v>
@@ -5554,13 +5995,13 @@
         <v>425</v>
       </c>
       <c r="B55" t="s">
-        <v>833</v>
+        <v>824</v>
       </c>
       <c r="D55" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E55" t="s">
-        <v>466</v>
+        <v>457</v>
       </c>
       <c r="F55" t="s">
         <v>792</v>
@@ -5574,13 +6015,13 @@
         <v>425</v>
       </c>
       <c r="B56" t="s">
-        <v>834</v>
+        <v>1168</v>
       </c>
       <c r="D56" t="s">
-        <v>49</v>
+        <v>1116</v>
       </c>
       <c r="E56" t="s">
-        <v>467</v>
+        <v>1220</v>
       </c>
       <c r="F56" t="s">
         <v>792</v>
@@ -5594,13 +6035,13 @@
         <v>425</v>
       </c>
       <c r="B57" t="s">
-        <v>835</v>
+        <v>825</v>
       </c>
       <c r="D57" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E57" t="s">
-        <v>468</v>
+        <v>458</v>
       </c>
       <c r="F57" t="s">
         <v>792</v>
@@ -5614,13 +6055,13 @@
         <v>425</v>
       </c>
       <c r="B58" t="s">
-        <v>836</v>
+        <v>826</v>
       </c>
       <c r="D58" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="E58" t="s">
-        <v>469</v>
+        <v>459</v>
       </c>
       <c r="F58" t="s">
         <v>792</v>
@@ -5634,13 +6075,13 @@
         <v>425</v>
       </c>
       <c r="B59" t="s">
-        <v>837</v>
+        <v>827</v>
       </c>
       <c r="D59" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="E59" t="s">
-        <v>470</v>
+        <v>460</v>
       </c>
       <c r="F59" t="s">
         <v>792</v>
@@ -5654,13 +6095,13 @@
         <v>425</v>
       </c>
       <c r="B60" t="s">
-        <v>838</v>
+        <v>828</v>
       </c>
       <c r="D60" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="E60" t="s">
-        <v>471</v>
+        <v>461</v>
       </c>
       <c r="F60" t="s">
         <v>792</v>
@@ -5674,13 +6115,13 @@
         <v>425</v>
       </c>
       <c r="B61" t="s">
-        <v>839</v>
+        <v>829</v>
       </c>
       <c r="D61" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="E61" t="s">
-        <v>472</v>
+        <v>462</v>
       </c>
       <c r="F61" t="s">
         <v>792</v>
@@ -5694,13 +6135,13 @@
         <v>425</v>
       </c>
       <c r="B62" t="s">
-        <v>840</v>
+        <v>830</v>
       </c>
       <c r="D62" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="E62" t="s">
-        <v>473</v>
+        <v>463</v>
       </c>
       <c r="F62" t="s">
         <v>792</v>
@@ -5714,13 +6155,13 @@
         <v>425</v>
       </c>
       <c r="B63" t="s">
-        <v>841</v>
+        <v>831</v>
       </c>
       <c r="D63" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="E63" t="s">
-        <v>474</v>
+        <v>464</v>
       </c>
       <c r="F63" t="s">
         <v>792</v>
@@ -5734,13 +6175,13 @@
         <v>425</v>
       </c>
       <c r="B64" t="s">
-        <v>842</v>
+        <v>832</v>
       </c>
       <c r="D64" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="E64" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="F64" t="s">
         <v>792</v>
@@ -5754,13 +6195,13 @@
         <v>425</v>
       </c>
       <c r="B65" t="s">
-        <v>843</v>
+        <v>1169</v>
       </c>
       <c r="D65" t="s">
-        <v>58</v>
+        <v>1117</v>
       </c>
       <c r="E65" t="s">
-        <v>476</v>
+        <v>1221</v>
       </c>
       <c r="F65" t="s">
         <v>792</v>
@@ -5774,13 +6215,13 @@
         <v>425</v>
       </c>
       <c r="B66" t="s">
-        <v>1273</v>
+        <v>833</v>
       </c>
       <c r="D66" t="s">
-        <v>1274</v>
+        <v>48</v>
       </c>
       <c r="E66" t="s">
-        <v>1275</v>
+        <v>466</v>
       </c>
       <c r="F66" t="s">
         <v>792</v>
@@ -5794,13 +6235,13 @@
         <v>425</v>
       </c>
       <c r="B67" t="s">
-        <v>844</v>
+        <v>834</v>
       </c>
       <c r="D67" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="E67" t="s">
-        <v>477</v>
+        <v>467</v>
       </c>
       <c r="F67" t="s">
         <v>792</v>
@@ -5814,13 +6255,13 @@
         <v>425</v>
       </c>
       <c r="B68" t="s">
-        <v>845</v>
+        <v>835</v>
       </c>
       <c r="D68" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E68" t="s">
-        <v>478</v>
+        <v>468</v>
       </c>
       <c r="F68" t="s">
         <v>792</v>
@@ -5834,13 +6275,13 @@
         <v>425</v>
       </c>
       <c r="B69" t="s">
-        <v>846</v>
+        <v>836</v>
       </c>
       <c r="D69" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="E69" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="F69" t="s">
         <v>792</v>
@@ -5854,13 +6295,13 @@
         <v>425</v>
       </c>
       <c r="B70" t="s">
-        <v>847</v>
+        <v>837</v>
       </c>
       <c r="D70" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="E70" t="s">
-        <v>480</v>
+        <v>470</v>
       </c>
       <c r="F70" t="s">
         <v>792</v>
@@ -5874,13 +6315,13 @@
         <v>425</v>
       </c>
       <c r="B71" t="s">
-        <v>848</v>
+        <v>838</v>
       </c>
       <c r="D71" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E71" t="s">
-        <v>481</v>
+        <v>471</v>
       </c>
       <c r="F71" t="s">
         <v>792</v>
@@ -5894,13 +6335,13 @@
         <v>425</v>
       </c>
       <c r="B72" t="s">
-        <v>849</v>
+        <v>839</v>
       </c>
       <c r="D72" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E72" t="s">
-        <v>482</v>
+        <v>472</v>
       </c>
       <c r="F72" t="s">
         <v>792</v>
@@ -5914,13 +6355,13 @@
         <v>425</v>
       </c>
       <c r="B73" t="s">
-        <v>850</v>
+        <v>840</v>
       </c>
       <c r="D73" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="E73" t="s">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="F73" t="s">
         <v>792</v>
@@ -5934,13 +6375,13 @@
         <v>425</v>
       </c>
       <c r="B74" t="s">
-        <v>851</v>
+        <v>1396</v>
       </c>
       <c r="D74" t="s">
-        <v>66</v>
+        <v>1397</v>
       </c>
       <c r="E74" t="s">
-        <v>484</v>
+        <v>1398</v>
       </c>
       <c r="F74" t="s">
         <v>792</v>
@@ -5954,13 +6395,13 @@
         <v>425</v>
       </c>
       <c r="B75" t="s">
-        <v>852</v>
+        <v>841</v>
       </c>
       <c r="D75" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="E75" t="s">
-        <v>485</v>
+        <v>474</v>
       </c>
       <c r="F75" t="s">
         <v>792</v>
@@ -5974,13 +6415,13 @@
         <v>425</v>
       </c>
       <c r="B76" t="s">
-        <v>853</v>
+        <v>1399</v>
       </c>
       <c r="D76" t="s">
-        <v>68</v>
+        <v>1400</v>
       </c>
       <c r="E76" t="s">
-        <v>486</v>
+        <v>1401</v>
       </c>
       <c r="F76" t="s">
         <v>792</v>
@@ -5994,13 +6435,13 @@
         <v>425</v>
       </c>
       <c r="B77" t="s">
-        <v>854</v>
+        <v>842</v>
       </c>
       <c r="D77" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="E77" t="s">
-        <v>487</v>
+        <v>475</v>
       </c>
       <c r="F77" t="s">
         <v>792</v>
@@ -6014,13 +6455,13 @@
         <v>425</v>
       </c>
       <c r="B78" t="s">
-        <v>855</v>
+        <v>843</v>
       </c>
       <c r="D78" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="E78" t="s">
-        <v>488</v>
+        <v>476</v>
       </c>
       <c r="F78" t="s">
         <v>792</v>
@@ -6034,13 +6475,13 @@
         <v>425</v>
       </c>
       <c r="B79" t="s">
-        <v>1171</v>
+        <v>1270</v>
       </c>
       <c r="D79" t="s">
-        <v>1118</v>
+        <v>1271</v>
       </c>
       <c r="E79" t="s">
-        <v>1224</v>
+        <v>1272</v>
       </c>
       <c r="F79" t="s">
         <v>792</v>
@@ -6054,13 +6495,13 @@
         <v>425</v>
       </c>
       <c r="B80" t="s">
-        <v>856</v>
+        <v>844</v>
       </c>
       <c r="D80" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="E80" t="s">
-        <v>489</v>
+        <v>477</v>
       </c>
       <c r="F80" t="s">
         <v>792</v>
@@ -6074,13 +6515,13 @@
         <v>425</v>
       </c>
       <c r="B81" t="s">
-        <v>857</v>
+        <v>845</v>
       </c>
       <c r="D81" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="E81" t="s">
-        <v>490</v>
+        <v>478</v>
       </c>
       <c r="F81" t="s">
         <v>792</v>
@@ -6094,13 +6535,13 @@
         <v>425</v>
       </c>
       <c r="B82" t="s">
-        <v>858</v>
+        <v>846</v>
       </c>
       <c r="D82" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="E82" t="s">
-        <v>491</v>
+        <v>479</v>
       </c>
       <c r="F82" t="s">
         <v>792</v>
@@ -6114,13 +6555,13 @@
         <v>425</v>
       </c>
       <c r="B83" t="s">
-        <v>859</v>
+        <v>847</v>
       </c>
       <c r="D83" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="E83" t="s">
-        <v>492</v>
+        <v>480</v>
       </c>
       <c r="F83" t="s">
         <v>792</v>
@@ -6134,13 +6575,13 @@
         <v>425</v>
       </c>
       <c r="B84" t="s">
-        <v>860</v>
+        <v>848</v>
       </c>
       <c r="D84" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="E84" t="s">
-        <v>493</v>
+        <v>481</v>
       </c>
       <c r="F84" t="s">
         <v>792</v>
@@ -6154,13 +6595,13 @@
         <v>425</v>
       </c>
       <c r="B85" t="s">
-        <v>861</v>
+        <v>849</v>
       </c>
       <c r="D85" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="E85" t="s">
-        <v>494</v>
+        <v>482</v>
       </c>
       <c r="F85" t="s">
         <v>792</v>
@@ -6174,13 +6615,13 @@
         <v>425</v>
       </c>
       <c r="B86" t="s">
-        <v>862</v>
+        <v>1402</v>
       </c>
       <c r="D86" t="s">
-        <v>77</v>
+        <v>1403</v>
       </c>
       <c r="E86" t="s">
-        <v>495</v>
+        <v>1404</v>
       </c>
       <c r="F86" t="s">
         <v>792</v>
@@ -6194,13 +6635,13 @@
         <v>425</v>
       </c>
       <c r="B87" t="s">
-        <v>863</v>
+        <v>850</v>
       </c>
       <c r="D87" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="E87" t="s">
-        <v>496</v>
+        <v>483</v>
       </c>
       <c r="F87" t="s">
         <v>792</v>
@@ -6214,13 +6655,13 @@
         <v>425</v>
       </c>
       <c r="B88" t="s">
-        <v>864</v>
+        <v>851</v>
       </c>
       <c r="D88" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="E88" t="s">
-        <v>497</v>
+        <v>484</v>
       </c>
       <c r="F88" t="s">
         <v>792</v>
@@ -6234,13 +6675,13 @@
         <v>425</v>
       </c>
       <c r="B89" t="s">
-        <v>865</v>
+        <v>852</v>
       </c>
       <c r="D89" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="E89" t="s">
-        <v>498</v>
+        <v>485</v>
       </c>
       <c r="F89" t="s">
         <v>792</v>
@@ -6254,13 +6695,13 @@
         <v>425</v>
       </c>
       <c r="B90" t="s">
-        <v>866</v>
+        <v>853</v>
       </c>
       <c r="D90" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="E90" t="s">
-        <v>499</v>
+        <v>486</v>
       </c>
       <c r="F90" t="s">
         <v>792</v>
@@ -6274,13 +6715,13 @@
         <v>425</v>
       </c>
       <c r="B91" t="s">
-        <v>867</v>
+        <v>854</v>
       </c>
       <c r="D91" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="E91" t="s">
-        <v>500</v>
+        <v>487</v>
       </c>
       <c r="F91" t="s">
         <v>792</v>
@@ -6294,13 +6735,13 @@
         <v>425</v>
       </c>
       <c r="B92" t="s">
-        <v>868</v>
+        <v>855</v>
       </c>
       <c r="D92" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="E92" t="s">
-        <v>501</v>
+        <v>488</v>
       </c>
       <c r="F92" t="s">
         <v>792</v>
@@ -6314,13 +6755,13 @@
         <v>425</v>
       </c>
       <c r="B93" t="s">
-        <v>1172</v>
+        <v>1170</v>
       </c>
       <c r="D93" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="E93" t="s">
-        <v>1225</v>
+        <v>1222</v>
       </c>
       <c r="F93" t="s">
         <v>792</v>
@@ -6334,13 +6775,13 @@
         <v>425</v>
       </c>
       <c r="B94" t="s">
-        <v>1173</v>
+        <v>856</v>
       </c>
       <c r="D94" t="s">
-        <v>1120</v>
+        <v>71</v>
       </c>
       <c r="E94" t="s">
-        <v>1226</v>
+        <v>489</v>
       </c>
       <c r="F94" t="s">
         <v>792</v>
@@ -6354,13 +6795,13 @@
         <v>425</v>
       </c>
       <c r="B95" t="s">
-        <v>869</v>
+        <v>857</v>
       </c>
       <c r="D95" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="E95" t="s">
-        <v>502</v>
+        <v>490</v>
       </c>
       <c r="F95" t="s">
         <v>792</v>
@@ -6374,13 +6815,13 @@
         <v>425</v>
       </c>
       <c r="B96" t="s">
-        <v>870</v>
+        <v>858</v>
       </c>
       <c r="D96" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="E96" t="s">
-        <v>503</v>
+        <v>491</v>
       </c>
       <c r="F96" t="s">
         <v>792</v>
@@ -6394,13 +6835,13 @@
         <v>425</v>
       </c>
       <c r="B97" t="s">
-        <v>1174</v>
+        <v>859</v>
       </c>
       <c r="D97" t="s">
-        <v>1121</v>
+        <v>74</v>
       </c>
       <c r="E97" t="s">
-        <v>1227</v>
+        <v>492</v>
       </c>
       <c r="F97" t="s">
         <v>792</v>
@@ -6414,13 +6855,13 @@
         <v>425</v>
       </c>
       <c r="B98" t="s">
-        <v>871</v>
+        <v>860</v>
       </c>
       <c r="D98" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="E98" t="s">
-        <v>504</v>
+        <v>493</v>
       </c>
       <c r="F98" t="s">
         <v>792</v>
@@ -6434,13 +6875,13 @@
         <v>425</v>
       </c>
       <c r="B99" t="s">
-        <v>872</v>
+        <v>861</v>
       </c>
       <c r="D99" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="E99" t="s">
-        <v>505</v>
+        <v>494</v>
       </c>
       <c r="F99" t="s">
         <v>792</v>
@@ -6454,13 +6895,13 @@
         <v>425</v>
       </c>
       <c r="B100" t="s">
-        <v>873</v>
+        <v>862</v>
       </c>
       <c r="D100" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="E100" t="s">
-        <v>506</v>
+        <v>495</v>
       </c>
       <c r="F100" t="s">
         <v>792</v>
@@ -6474,13 +6915,13 @@
         <v>425</v>
       </c>
       <c r="B101" t="s">
-        <v>874</v>
+        <v>1405</v>
       </c>
       <c r="D101" t="s">
-        <v>89</v>
+        <v>1406</v>
       </c>
       <c r="E101" t="s">
-        <v>507</v>
+        <v>1407</v>
       </c>
       <c r="F101" t="s">
         <v>792</v>
@@ -6494,13 +6935,13 @@
         <v>425</v>
       </c>
       <c r="B102" t="s">
-        <v>875</v>
+        <v>863</v>
       </c>
       <c r="D102" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="E102" t="s">
-        <v>508</v>
+        <v>496</v>
       </c>
       <c r="F102" t="s">
         <v>792</v>
@@ -6514,13 +6955,13 @@
         <v>425</v>
       </c>
       <c r="B103" t="s">
-        <v>876</v>
+        <v>864</v>
       </c>
       <c r="D103" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="E103" t="s">
-        <v>509</v>
+        <v>497</v>
       </c>
       <c r="F103" t="s">
         <v>792</v>
@@ -6534,13 +6975,13 @@
         <v>425</v>
       </c>
       <c r="B104" t="s">
-        <v>877</v>
+        <v>865</v>
       </c>
       <c r="D104" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="E104" t="s">
-        <v>510</v>
+        <v>498</v>
       </c>
       <c r="F104" t="s">
         <v>792</v>
@@ -6554,13 +6995,13 @@
         <v>425</v>
       </c>
       <c r="B105" t="s">
-        <v>878</v>
+        <v>866</v>
       </c>
       <c r="D105" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="E105" t="s">
-        <v>511</v>
+        <v>499</v>
       </c>
       <c r="F105" t="s">
         <v>792</v>
@@ -6574,13 +7015,13 @@
         <v>425</v>
       </c>
       <c r="B106" t="s">
-        <v>1303</v>
+        <v>867</v>
       </c>
       <c r="D106" t="s">
-        <v>1304</v>
+        <v>82</v>
       </c>
       <c r="E106" t="s">
-        <v>1305</v>
+        <v>500</v>
       </c>
       <c r="F106" t="s">
         <v>792</v>
@@ -6594,13 +7035,13 @@
         <v>425</v>
       </c>
       <c r="B107" t="s">
-        <v>879</v>
+        <v>868</v>
       </c>
       <c r="D107" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="E107" t="s">
-        <v>512</v>
+        <v>501</v>
       </c>
       <c r="F107" t="s">
         <v>792</v>
@@ -6614,13 +7055,13 @@
         <v>425</v>
       </c>
       <c r="B108" t="s">
-        <v>880</v>
+        <v>1171</v>
       </c>
       <c r="D108" t="s">
-        <v>95</v>
+        <v>1119</v>
       </c>
       <c r="E108" t="s">
-        <v>513</v>
+        <v>1223</v>
       </c>
       <c r="F108" t="s">
         <v>792</v>
@@ -6634,13 +7075,13 @@
         <v>425</v>
       </c>
       <c r="B109" t="s">
-        <v>881</v>
+        <v>1408</v>
       </c>
       <c r="D109" t="s">
-        <v>96</v>
+        <v>1409</v>
       </c>
       <c r="E109" t="s">
-        <v>514</v>
+        <v>1410</v>
       </c>
       <c r="F109" t="s">
         <v>792</v>
@@ -6654,13 +7095,13 @@
         <v>425</v>
       </c>
       <c r="B110" t="s">
-        <v>882</v>
+        <v>1172</v>
       </c>
       <c r="D110" t="s">
-        <v>97</v>
+        <v>1120</v>
       </c>
       <c r="E110" t="s">
-        <v>515</v>
+        <v>1224</v>
       </c>
       <c r="F110" t="s">
         <v>792</v>
@@ -6674,13 +7115,13 @@
         <v>425</v>
       </c>
       <c r="B111" t="s">
-        <v>883</v>
+        <v>869</v>
       </c>
       <c r="D111" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="E111" t="s">
-        <v>516</v>
+        <v>502</v>
       </c>
       <c r="F111" t="s">
         <v>792</v>
@@ -6694,13 +7135,13 @@
         <v>425</v>
       </c>
       <c r="B112" t="s">
-        <v>884</v>
+        <v>870</v>
       </c>
       <c r="D112" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="E112" t="s">
-        <v>517</v>
+        <v>503</v>
       </c>
       <c r="F112" t="s">
         <v>792</v>
@@ -6714,13 +7155,13 @@
         <v>425</v>
       </c>
       <c r="B113" t="s">
-        <v>885</v>
+        <v>1173</v>
       </c>
       <c r="D113" t="s">
-        <v>100</v>
+        <v>1121</v>
       </c>
       <c r="E113" t="s">
-        <v>518</v>
+        <v>1225</v>
       </c>
       <c r="F113" t="s">
         <v>792</v>
@@ -6734,13 +7175,13 @@
         <v>425</v>
       </c>
       <c r="B114" t="s">
-        <v>886</v>
+        <v>871</v>
       </c>
       <c r="D114" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="E114" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="F114" t="s">
         <v>792</v>
@@ -6754,13 +7195,13 @@
         <v>425</v>
       </c>
       <c r="B115" t="s">
-        <v>887</v>
+        <v>872</v>
       </c>
       <c r="D115" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="E115" t="s">
-        <v>520</v>
+        <v>505</v>
       </c>
       <c r="F115" t="s">
         <v>792</v>
@@ -6774,13 +7215,13 @@
         <v>425</v>
       </c>
       <c r="B116" t="s">
-        <v>888</v>
+        <v>873</v>
       </c>
       <c r="D116" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="E116" t="s">
-        <v>521</v>
+        <v>506</v>
       </c>
       <c r="F116" t="s">
         <v>792</v>
@@ -6794,13 +7235,13 @@
         <v>425</v>
       </c>
       <c r="B117" t="s">
-        <v>889</v>
+        <v>874</v>
       </c>
       <c r="D117" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="E117" t="s">
-        <v>522</v>
+        <v>507</v>
       </c>
       <c r="F117" t="s">
         <v>792</v>
@@ -6814,13 +7255,13 @@
         <v>425</v>
       </c>
       <c r="B118" t="s">
-        <v>890</v>
+        <v>875</v>
       </c>
       <c r="D118" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="E118" t="s">
-        <v>523</v>
+        <v>508</v>
       </c>
       <c r="F118" t="s">
         <v>792</v>
@@ -6834,13 +7275,13 @@
         <v>425</v>
       </c>
       <c r="B119" t="s">
-        <v>891</v>
+        <v>876</v>
       </c>
       <c r="D119" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="E119" t="s">
-        <v>524</v>
+        <v>509</v>
       </c>
       <c r="F119" t="s">
         <v>792</v>
@@ -6854,13 +7295,13 @@
         <v>425</v>
       </c>
       <c r="B120" t="s">
-        <v>892</v>
+        <v>877</v>
       </c>
       <c r="D120" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="E120" t="s">
-        <v>525</v>
+        <v>510</v>
       </c>
       <c r="F120" t="s">
         <v>792</v>
@@ -6874,13 +7315,13 @@
         <v>425</v>
       </c>
       <c r="B121" t="s">
-        <v>893</v>
+        <v>1411</v>
       </c>
       <c r="D121" t="s">
-        <v>108</v>
+        <v>1412</v>
       </c>
       <c r="E121" t="s">
-        <v>526</v>
+        <v>1413</v>
       </c>
       <c r="F121" t="s">
         <v>792</v>
@@ -6894,13 +7335,13 @@
         <v>425</v>
       </c>
       <c r="B122" t="s">
-        <v>894</v>
+        <v>878</v>
       </c>
       <c r="D122" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="E122" t="s">
-        <v>527</v>
+        <v>511</v>
       </c>
       <c r="F122" t="s">
         <v>792</v>
@@ -6914,13 +7355,13 @@
         <v>425</v>
       </c>
       <c r="B123" t="s">
-        <v>895</v>
+        <v>1300</v>
       </c>
       <c r="D123" t="s">
-        <v>110</v>
+        <v>1301</v>
       </c>
       <c r="E123" t="s">
-        <v>528</v>
+        <v>1302</v>
       </c>
       <c r="F123" t="s">
         <v>792</v>
@@ -6934,13 +7375,13 @@
         <v>425</v>
       </c>
       <c r="B124" t="s">
-        <v>896</v>
+        <v>879</v>
       </c>
       <c r="D124" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="E124" t="s">
-        <v>529</v>
+        <v>512</v>
       </c>
       <c r="F124" t="s">
         <v>792</v>
@@ -6954,13 +7395,13 @@
         <v>425</v>
       </c>
       <c r="B125" t="s">
-        <v>897</v>
+        <v>880</v>
       </c>
       <c r="D125" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="E125" t="s">
-        <v>530</v>
+        <v>513</v>
       </c>
       <c r="F125" t="s">
         <v>792</v>
@@ -6974,13 +7415,13 @@
         <v>425</v>
       </c>
       <c r="B126" t="s">
-        <v>1175</v>
+        <v>1414</v>
       </c>
       <c r="D126" t="s">
-        <v>1122</v>
+        <v>1415</v>
       </c>
       <c r="E126" t="s">
-        <v>1228</v>
+        <v>1416</v>
       </c>
       <c r="F126" t="s">
         <v>792</v>
@@ -6994,13 +7435,13 @@
         <v>425</v>
       </c>
       <c r="B127" t="s">
-        <v>898</v>
+        <v>881</v>
       </c>
       <c r="D127" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="E127" t="s">
-        <v>531</v>
+        <v>514</v>
       </c>
       <c r="F127" t="s">
         <v>792</v>
@@ -7014,13 +7455,13 @@
         <v>425</v>
       </c>
       <c r="B128" t="s">
-        <v>899</v>
+        <v>882</v>
       </c>
       <c r="D128" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="E128" t="s">
-        <v>532</v>
+        <v>515</v>
       </c>
       <c r="F128" t="s">
         <v>792</v>
@@ -7034,13 +7475,13 @@
         <v>425</v>
       </c>
       <c r="B129" t="s">
-        <v>900</v>
+        <v>883</v>
       </c>
       <c r="D129" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="E129" t="s">
-        <v>533</v>
+        <v>516</v>
       </c>
       <c r="F129" t="s">
         <v>792</v>
@@ -7054,13 +7495,13 @@
         <v>425</v>
       </c>
       <c r="B130" t="s">
-        <v>901</v>
+        <v>884</v>
       </c>
       <c r="D130" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="E130" t="s">
-        <v>534</v>
+        <v>517</v>
       </c>
       <c r="F130" t="s">
         <v>792</v>
@@ -7074,13 +7515,13 @@
         <v>425</v>
       </c>
       <c r="B131" t="s">
-        <v>902</v>
+        <v>885</v>
       </c>
       <c r="D131" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="E131" t="s">
-        <v>535</v>
+        <v>518</v>
       </c>
       <c r="F131" t="s">
         <v>792</v>
@@ -7094,13 +7535,13 @@
         <v>425</v>
       </c>
       <c r="B132" t="s">
-        <v>903</v>
+        <v>886</v>
       </c>
       <c r="D132" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="E132" t="s">
-        <v>536</v>
+        <v>519</v>
       </c>
       <c r="F132" t="s">
         <v>792</v>
@@ -7114,13 +7555,13 @@
         <v>425</v>
       </c>
       <c r="B133" t="s">
-        <v>904</v>
+        <v>887</v>
       </c>
       <c r="D133" t="s">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="E133" t="s">
-        <v>537</v>
+        <v>520</v>
       </c>
       <c r="F133" t="s">
         <v>792</v>
@@ -7134,13 +7575,13 @@
         <v>425</v>
       </c>
       <c r="B134" t="s">
-        <v>905</v>
+        <v>888</v>
       </c>
       <c r="D134" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="E134" t="s">
-        <v>538</v>
+        <v>521</v>
       </c>
       <c r="F134" t="s">
         <v>792</v>
@@ -7154,13 +7595,13 @@
         <v>425</v>
       </c>
       <c r="B135" t="s">
-        <v>906</v>
+        <v>889</v>
       </c>
       <c r="D135" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="E135" t="s">
-        <v>539</v>
+        <v>522</v>
       </c>
       <c r="F135" t="s">
         <v>792</v>
@@ -7174,13 +7615,13 @@
         <v>425</v>
       </c>
       <c r="B136" t="s">
-        <v>907</v>
+        <v>890</v>
       </c>
       <c r="D136" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="E136" t="s">
-        <v>540</v>
+        <v>523</v>
       </c>
       <c r="F136" t="s">
         <v>792</v>
@@ -7194,13 +7635,13 @@
         <v>425</v>
       </c>
       <c r="B137" t="s">
-        <v>1276</v>
+        <v>891</v>
       </c>
       <c r="D137" t="s">
-        <v>1277</v>
+        <v>106</v>
       </c>
       <c r="E137" t="s">
-        <v>1278</v>
+        <v>524</v>
       </c>
       <c r="F137" t="s">
         <v>792</v>
@@ -7214,13 +7655,13 @@
         <v>425</v>
       </c>
       <c r="B138" t="s">
-        <v>908</v>
+        <v>892</v>
       </c>
       <c r="D138" t="s">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="E138" t="s">
-        <v>541</v>
+        <v>525</v>
       </c>
       <c r="F138" t="s">
         <v>792</v>
@@ -7234,13 +7675,13 @@
         <v>425</v>
       </c>
       <c r="B139" t="s">
-        <v>909</v>
+        <v>893</v>
       </c>
       <c r="D139" t="s">
-        <v>124</v>
+        <v>108</v>
       </c>
       <c r="E139" t="s">
-        <v>542</v>
+        <v>526</v>
       </c>
       <c r="F139" t="s">
         <v>792</v>
@@ -7254,13 +7695,13 @@
         <v>425</v>
       </c>
       <c r="B140" t="s">
-        <v>910</v>
+        <v>894</v>
       </c>
       <c r="D140" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="E140" t="s">
-        <v>543</v>
+        <v>527</v>
       </c>
       <c r="F140" t="s">
         <v>792</v>
@@ -7274,13 +7715,13 @@
         <v>425</v>
       </c>
       <c r="B141" t="s">
-        <v>1306</v>
+        <v>895</v>
       </c>
       <c r="D141" t="s">
-        <v>1307</v>
+        <v>110</v>
       </c>
       <c r="E141" t="s">
-        <v>1308</v>
+        <v>528</v>
       </c>
       <c r="F141" t="s">
         <v>792</v>
@@ -7294,13 +7735,13 @@
         <v>425</v>
       </c>
       <c r="B142" t="s">
-        <v>911</v>
+        <v>896</v>
       </c>
       <c r="D142" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="E142" t="s">
-        <v>544</v>
+        <v>529</v>
       </c>
       <c r="F142" t="s">
         <v>792</v>
@@ -7314,13 +7755,13 @@
         <v>425</v>
       </c>
       <c r="B143" t="s">
-        <v>1176</v>
+        <v>897</v>
       </c>
       <c r="D143" t="s">
-        <v>1123</v>
+        <v>112</v>
       </c>
       <c r="E143" t="s">
-        <v>1229</v>
+        <v>530</v>
       </c>
       <c r="F143" t="s">
         <v>792</v>
@@ -7334,13 +7775,13 @@
         <v>425</v>
       </c>
       <c r="B144" t="s">
-        <v>912</v>
+        <v>1174</v>
       </c>
       <c r="D144" t="s">
-        <v>127</v>
+        <v>1122</v>
       </c>
       <c r="E144" t="s">
-        <v>545</v>
+        <v>1226</v>
       </c>
       <c r="F144" t="s">
         <v>792</v>
@@ -7354,13 +7795,13 @@
         <v>425</v>
       </c>
       <c r="B145" t="s">
-        <v>1177</v>
+        <v>898</v>
       </c>
       <c r="D145" t="s">
-        <v>1124</v>
+        <v>113</v>
       </c>
       <c r="E145" t="s">
-        <v>1230</v>
+        <v>531</v>
       </c>
       <c r="F145" t="s">
         <v>792</v>
@@ -7374,13 +7815,13 @@
         <v>425</v>
       </c>
       <c r="B146" t="s">
-        <v>913</v>
+        <v>899</v>
       </c>
       <c r="D146" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="E146" t="s">
-        <v>546</v>
+        <v>532</v>
       </c>
       <c r="F146" t="s">
         <v>792</v>
@@ -7394,13 +7835,13 @@
         <v>425</v>
       </c>
       <c r="B147" t="s">
-        <v>914</v>
+        <v>900</v>
       </c>
       <c r="D147" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="E147" t="s">
-        <v>547</v>
+        <v>533</v>
       </c>
       <c r="F147" t="s">
         <v>792</v>
@@ -7414,13 +7855,13 @@
         <v>425</v>
       </c>
       <c r="B148" t="s">
-        <v>915</v>
+        <v>901</v>
       </c>
       <c r="D148" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="E148" t="s">
-        <v>548</v>
+        <v>534</v>
       </c>
       <c r="F148" t="s">
         <v>792</v>
@@ -7434,13 +7875,13 @@
         <v>425</v>
       </c>
       <c r="B149" t="s">
-        <v>916</v>
+        <v>902</v>
       </c>
       <c r="D149" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="E149" t="s">
-        <v>549</v>
+        <v>535</v>
       </c>
       <c r="F149" t="s">
         <v>792</v>
@@ -7454,13 +7895,13 @@
         <v>425</v>
       </c>
       <c r="B150" t="s">
-        <v>917</v>
+        <v>903</v>
       </c>
       <c r="D150" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="E150" t="s">
-        <v>550</v>
+        <v>536</v>
       </c>
       <c r="F150" t="s">
         <v>792</v>
@@ -7474,13 +7915,13 @@
         <v>425</v>
       </c>
       <c r="B151" t="s">
-        <v>918</v>
+        <v>904</v>
       </c>
       <c r="D151" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="E151" t="s">
-        <v>551</v>
+        <v>537</v>
       </c>
       <c r="F151" t="s">
         <v>792</v>
@@ -7494,13 +7935,13 @@
         <v>425</v>
       </c>
       <c r="B152" t="s">
-        <v>919</v>
+        <v>905</v>
       </c>
       <c r="D152" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="E152" t="s">
-        <v>552</v>
+        <v>538</v>
       </c>
       <c r="F152" t="s">
         <v>792</v>
@@ -7514,13 +7955,13 @@
         <v>425</v>
       </c>
       <c r="B153" t="s">
-        <v>1178</v>
+        <v>906</v>
       </c>
       <c r="D153" t="s">
-        <v>1125</v>
+        <v>121</v>
       </c>
       <c r="E153" t="s">
-        <v>1231</v>
+        <v>539</v>
       </c>
       <c r="F153" t="s">
         <v>792</v>
@@ -7534,13 +7975,13 @@
         <v>425</v>
       </c>
       <c r="B154" t="s">
-        <v>920</v>
+        <v>907</v>
       </c>
       <c r="D154" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="E154" t="s">
-        <v>553</v>
+        <v>540</v>
       </c>
       <c r="F154" t="s">
         <v>792</v>
@@ -7554,13 +7995,13 @@
         <v>425</v>
       </c>
       <c r="B155" t="s">
-        <v>921</v>
+        <v>1273</v>
       </c>
       <c r="D155" t="s">
-        <v>136</v>
+        <v>1274</v>
       </c>
       <c r="E155" t="s">
-        <v>554</v>
+        <v>1275</v>
       </c>
       <c r="F155" t="s">
         <v>792</v>
@@ -7574,13 +8015,13 @@
         <v>425</v>
       </c>
       <c r="B156" t="s">
-        <v>922</v>
+        <v>908</v>
       </c>
       <c r="D156" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="E156" t="s">
-        <v>555</v>
+        <v>541</v>
       </c>
       <c r="F156" t="s">
         <v>792</v>
@@ -7594,13 +8035,13 @@
         <v>425</v>
       </c>
       <c r="B157" t="s">
-        <v>923</v>
+        <v>909</v>
       </c>
       <c r="D157" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="E157" t="s">
-        <v>556</v>
+        <v>542</v>
       </c>
       <c r="F157" t="s">
         <v>792</v>
@@ -7614,13 +8055,13 @@
         <v>425</v>
       </c>
       <c r="B158" t="s">
-        <v>924</v>
+        <v>910</v>
       </c>
       <c r="D158" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="E158" t="s">
-        <v>557</v>
+        <v>543</v>
       </c>
       <c r="F158" t="s">
         <v>792</v>
@@ -7634,13 +8075,13 @@
         <v>425</v>
       </c>
       <c r="B159" t="s">
-        <v>925</v>
+        <v>1303</v>
       </c>
       <c r="D159" t="s">
-        <v>140</v>
+        <v>1304</v>
       </c>
       <c r="E159" t="s">
-        <v>558</v>
+        <v>1305</v>
       </c>
       <c r="F159" t="s">
         <v>792</v>
@@ -7654,13 +8095,13 @@
         <v>425</v>
       </c>
       <c r="B160" t="s">
-        <v>926</v>
+        <v>911</v>
       </c>
       <c r="D160" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="E160" t="s">
-        <v>559</v>
+        <v>544</v>
       </c>
       <c r="F160" t="s">
         <v>792</v>
@@ -7674,13 +8115,13 @@
         <v>425</v>
       </c>
       <c r="B161" t="s">
-        <v>1279</v>
+        <v>1175</v>
       </c>
       <c r="D161" t="s">
-        <v>1280</v>
+        <v>1123</v>
       </c>
       <c r="E161" t="s">
-        <v>1281</v>
+        <v>1227</v>
       </c>
       <c r="F161" t="s">
         <v>792</v>
@@ -7694,13 +8135,13 @@
         <v>425</v>
       </c>
       <c r="B162" t="s">
-        <v>927</v>
+        <v>1417</v>
       </c>
       <c r="D162" t="s">
-        <v>142</v>
+        <v>1418</v>
       </c>
       <c r="E162" t="s">
-        <v>560</v>
+        <v>1419</v>
       </c>
       <c r="F162" t="s">
         <v>792</v>
@@ -7714,13 +8155,13 @@
         <v>425</v>
       </c>
       <c r="B163" t="s">
-        <v>928</v>
+        <v>912</v>
       </c>
       <c r="D163" t="s">
-        <v>143</v>
+        <v>127</v>
       </c>
       <c r="E163" t="s">
-        <v>561</v>
+        <v>545</v>
       </c>
       <c r="F163" t="s">
         <v>792</v>
@@ -7734,13 +8175,13 @@
         <v>425</v>
       </c>
       <c r="B164" t="s">
-        <v>929</v>
+        <v>1420</v>
       </c>
       <c r="D164" t="s">
-        <v>144</v>
+        <v>1421</v>
       </c>
       <c r="E164" t="s">
-        <v>562</v>
+        <v>1422</v>
       </c>
       <c r="F164" t="s">
         <v>792</v>
@@ -7754,13 +8195,13 @@
         <v>425</v>
       </c>
       <c r="B165" t="s">
-        <v>1179</v>
+        <v>913</v>
       </c>
       <c r="D165" t="s">
-        <v>1126</v>
+        <v>128</v>
       </c>
       <c r="E165" t="s">
-        <v>1232</v>
+        <v>546</v>
       </c>
       <c r="F165" t="s">
         <v>792</v>
@@ -7774,13 +8215,13 @@
         <v>425</v>
       </c>
       <c r="B166" t="s">
-        <v>930</v>
+        <v>914</v>
       </c>
       <c r="D166" t="s">
-        <v>145</v>
+        <v>129</v>
       </c>
       <c r="E166" t="s">
-        <v>563</v>
+        <v>547</v>
       </c>
       <c r="F166" t="s">
         <v>792</v>
@@ -7794,13 +8235,13 @@
         <v>425</v>
       </c>
       <c r="B167" t="s">
-        <v>931</v>
+        <v>915</v>
       </c>
       <c r="D167" t="s">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="E167" t="s">
-        <v>564</v>
+        <v>548</v>
       </c>
       <c r="F167" t="s">
         <v>792</v>
@@ -7814,13 +8255,13 @@
         <v>425</v>
       </c>
       <c r="B168" t="s">
-        <v>932</v>
+        <v>916</v>
       </c>
       <c r="D168" t="s">
-        <v>147</v>
+        <v>131</v>
       </c>
       <c r="E168" t="s">
-        <v>565</v>
+        <v>549</v>
       </c>
       <c r="F168" t="s">
         <v>792</v>
@@ -7834,13 +8275,13 @@
         <v>425</v>
       </c>
       <c r="B169" t="s">
-        <v>933</v>
+        <v>917</v>
       </c>
       <c r="D169" t="s">
-        <v>148</v>
+        <v>132</v>
       </c>
       <c r="E169" t="s">
-        <v>566</v>
+        <v>550</v>
       </c>
       <c r="F169" t="s">
         <v>792</v>
@@ -7854,13 +8295,13 @@
         <v>425</v>
       </c>
       <c r="B170" t="s">
-        <v>934</v>
+        <v>1423</v>
       </c>
       <c r="D170" t="s">
-        <v>149</v>
+        <v>1424</v>
       </c>
       <c r="E170" t="s">
-        <v>567</v>
+        <v>1425</v>
       </c>
       <c r="F170" t="s">
         <v>792</v>
@@ -7874,13 +8315,13 @@
         <v>425</v>
       </c>
       <c r="B171" t="s">
-        <v>935</v>
+        <v>918</v>
       </c>
       <c r="D171" t="s">
-        <v>150</v>
+        <v>133</v>
       </c>
       <c r="E171" t="s">
-        <v>568</v>
+        <v>551</v>
       </c>
       <c r="F171" t="s">
         <v>792</v>
@@ -7894,13 +8335,13 @@
         <v>425</v>
       </c>
       <c r="B172" t="s">
-        <v>936</v>
+        <v>919</v>
       </c>
       <c r="D172" t="s">
-        <v>151</v>
+        <v>134</v>
       </c>
       <c r="E172" t="s">
-        <v>569</v>
+        <v>552</v>
       </c>
       <c r="F172" t="s">
         <v>792</v>
@@ -7914,13 +8355,13 @@
         <v>425</v>
       </c>
       <c r="B173" t="s">
-        <v>937</v>
+        <v>1176</v>
       </c>
       <c r="D173" t="s">
-        <v>152</v>
+        <v>1124</v>
       </c>
       <c r="E173" t="s">
-        <v>570</v>
+        <v>1228</v>
       </c>
       <c r="F173" t="s">
         <v>792</v>
@@ -7934,13 +8375,13 @@
         <v>425</v>
       </c>
       <c r="B174" t="s">
-        <v>1282</v>
+        <v>920</v>
       </c>
       <c r="D174" t="s">
-        <v>1283</v>
+        <v>135</v>
       </c>
       <c r="E174" t="s">
-        <v>1284</v>
+        <v>553</v>
       </c>
       <c r="F174" t="s">
         <v>792</v>
@@ -7954,13 +8395,13 @@
         <v>425</v>
       </c>
       <c r="B175" t="s">
-        <v>938</v>
+        <v>921</v>
       </c>
       <c r="D175" t="s">
-        <v>153</v>
+        <v>136</v>
       </c>
       <c r="E175" t="s">
-        <v>571</v>
+        <v>554</v>
       </c>
       <c r="F175" t="s">
         <v>792</v>
@@ -7974,13 +8415,13 @@
         <v>425</v>
       </c>
       <c r="B176" t="s">
-        <v>939</v>
+        <v>922</v>
       </c>
       <c r="D176" t="s">
-        <v>154</v>
+        <v>137</v>
       </c>
       <c r="E176" t="s">
-        <v>572</v>
+        <v>555</v>
       </c>
       <c r="F176" t="s">
         <v>792</v>
@@ -7994,13 +8435,13 @@
         <v>425</v>
       </c>
       <c r="B177" t="s">
-        <v>940</v>
+        <v>923</v>
       </c>
       <c r="D177" t="s">
-        <v>155</v>
+        <v>138</v>
       </c>
       <c r="E177" t="s">
-        <v>573</v>
+        <v>556</v>
       </c>
       <c r="F177" t="s">
         <v>792</v>
@@ -8014,13 +8455,13 @@
         <v>425</v>
       </c>
       <c r="B178" t="s">
-        <v>941</v>
+        <v>924</v>
       </c>
       <c r="D178" t="s">
-        <v>156</v>
+        <v>139</v>
       </c>
       <c r="E178" t="s">
-        <v>574</v>
+        <v>557</v>
       </c>
       <c r="F178" t="s">
         <v>792</v>
@@ -8034,13 +8475,13 @@
         <v>425</v>
       </c>
       <c r="B179" t="s">
-        <v>942</v>
+        <v>925</v>
       </c>
       <c r="D179" t="s">
-        <v>157</v>
+        <v>140</v>
       </c>
       <c r="E179" t="s">
-        <v>575</v>
+        <v>558</v>
       </c>
       <c r="F179" t="s">
         <v>792</v>
@@ -8054,13 +8495,13 @@
         <v>425</v>
       </c>
       <c r="B180" t="s">
-        <v>943</v>
+        <v>926</v>
       </c>
       <c r="D180" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="E180" t="s">
-        <v>576</v>
+        <v>559</v>
       </c>
       <c r="F180" t="s">
         <v>792</v>
@@ -8074,13 +8515,13 @@
         <v>425</v>
       </c>
       <c r="B181" t="s">
-        <v>1309</v>
+        <v>1276</v>
       </c>
       <c r="D181" t="s">
-        <v>1310</v>
+        <v>1277</v>
       </c>
       <c r="E181" t="s">
-        <v>1311</v>
+        <v>1278</v>
       </c>
       <c r="F181" t="s">
         <v>792</v>
@@ -8094,13 +8535,13 @@
         <v>425</v>
       </c>
       <c r="B182" t="s">
-        <v>944</v>
+        <v>927</v>
       </c>
       <c r="D182" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="E182" t="s">
-        <v>577</v>
+        <v>560</v>
       </c>
       <c r="F182" t="s">
         <v>792</v>
@@ -8114,13 +8555,13 @@
         <v>425</v>
       </c>
       <c r="B183" t="s">
-        <v>945</v>
+        <v>928</v>
       </c>
       <c r="D183" t="s">
-        <v>160</v>
+        <v>143</v>
       </c>
       <c r="E183" t="s">
-        <v>578</v>
+        <v>561</v>
       </c>
       <c r="F183" t="s">
         <v>792</v>
@@ -8134,13 +8575,13 @@
         <v>425</v>
       </c>
       <c r="B184" t="s">
-        <v>946</v>
+        <v>929</v>
       </c>
       <c r="D184" t="s">
-        <v>161</v>
+        <v>144</v>
       </c>
       <c r="E184" t="s">
-        <v>579</v>
+        <v>562</v>
       </c>
       <c r="F184" t="s">
         <v>792</v>
@@ -8154,13 +8595,13 @@
         <v>425</v>
       </c>
       <c r="B185" t="s">
-        <v>1312</v>
+        <v>1177</v>
       </c>
       <c r="D185" t="s">
-        <v>1313</v>
+        <v>1125</v>
       </c>
       <c r="E185" t="s">
-        <v>1314</v>
+        <v>1229</v>
       </c>
       <c r="F185" t="s">
         <v>792</v>
@@ -8174,13 +8615,13 @@
         <v>425</v>
       </c>
       <c r="B186" t="s">
-        <v>1180</v>
+        <v>930</v>
       </c>
       <c r="D186" t="s">
-        <v>1127</v>
+        <v>145</v>
       </c>
       <c r="E186" t="s">
-        <v>1233</v>
+        <v>563</v>
       </c>
       <c r="F186" t="s">
         <v>792</v>
@@ -8194,13 +8635,13 @@
         <v>425</v>
       </c>
       <c r="B187" t="s">
-        <v>1181</v>
+        <v>931</v>
       </c>
       <c r="D187" t="s">
-        <v>1128</v>
+        <v>146</v>
       </c>
       <c r="E187" t="s">
-        <v>1234</v>
+        <v>564</v>
       </c>
       <c r="F187" t="s">
         <v>792</v>
@@ -8214,13 +8655,13 @@
         <v>425</v>
       </c>
       <c r="B188" t="s">
-        <v>1285</v>
+        <v>932</v>
       </c>
       <c r="D188" t="s">
-        <v>1286</v>
+        <v>147</v>
       </c>
       <c r="E188" t="s">
-        <v>1287</v>
+        <v>565</v>
       </c>
       <c r="F188" t="s">
         <v>792</v>
@@ -8234,13 +8675,13 @@
         <v>425</v>
       </c>
       <c r="B189" t="s">
-        <v>947</v>
+        <v>933</v>
       </c>
       <c r="D189" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="E189" t="s">
-        <v>580</v>
+        <v>566</v>
       </c>
       <c r="F189" t="s">
         <v>792</v>
@@ -8254,13 +8695,13 @@
         <v>425</v>
       </c>
       <c r="B190" t="s">
-        <v>948</v>
+        <v>934</v>
       </c>
       <c r="D190" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="E190" t="s">
-        <v>581</v>
+        <v>567</v>
       </c>
       <c r="F190" t="s">
         <v>792</v>
@@ -8274,13 +8715,13 @@
         <v>425</v>
       </c>
       <c r="B191" t="s">
-        <v>949</v>
+        <v>935</v>
       </c>
       <c r="D191" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="E191" t="s">
-        <v>582</v>
+        <v>568</v>
       </c>
       <c r="F191" t="s">
         <v>792</v>
@@ -8294,13 +8735,13 @@
         <v>425</v>
       </c>
       <c r="B192" t="s">
-        <v>1182</v>
+        <v>936</v>
       </c>
       <c r="D192" t="s">
-        <v>1129</v>
+        <v>151</v>
       </c>
       <c r="E192" t="s">
-        <v>1235</v>
+        <v>569</v>
       </c>
       <c r="F192" t="s">
         <v>792</v>
@@ -8314,13 +8755,13 @@
         <v>425</v>
       </c>
       <c r="B193" t="s">
-        <v>950</v>
+        <v>937</v>
       </c>
       <c r="D193" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="E193" t="s">
-        <v>583</v>
+        <v>570</v>
       </c>
       <c r="F193" t="s">
         <v>792</v>
@@ -8334,13 +8775,13 @@
         <v>425</v>
       </c>
       <c r="B194" t="s">
-        <v>951</v>
+        <v>1279</v>
       </c>
       <c r="D194" t="s">
-        <v>166</v>
+        <v>1280</v>
       </c>
       <c r="E194" t="s">
-        <v>584</v>
+        <v>1281</v>
       </c>
       <c r="F194" t="s">
         <v>792</v>
@@ -8354,13 +8795,13 @@
         <v>425</v>
       </c>
       <c r="B195" t="s">
-        <v>952</v>
+        <v>938</v>
       </c>
       <c r="D195" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="E195" t="s">
-        <v>585</v>
+        <v>571</v>
       </c>
       <c r="F195" t="s">
         <v>792</v>
@@ -8374,13 +8815,13 @@
         <v>425</v>
       </c>
       <c r="B196" t="s">
-        <v>1183</v>
+        <v>939</v>
       </c>
       <c r="D196" t="s">
-        <v>1130</v>
+        <v>154</v>
       </c>
       <c r="E196" t="s">
-        <v>1236</v>
+        <v>572</v>
       </c>
       <c r="F196" t="s">
         <v>792</v>
@@ -8394,13 +8835,13 @@
         <v>425</v>
       </c>
       <c r="B197" t="s">
-        <v>953</v>
+        <v>940</v>
       </c>
       <c r="D197" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="E197" t="s">
-        <v>586</v>
+        <v>573</v>
       </c>
       <c r="F197" t="s">
         <v>792</v>
@@ -8414,13 +8855,13 @@
         <v>425</v>
       </c>
       <c r="B198" t="s">
-        <v>954</v>
+        <v>941</v>
       </c>
       <c r="D198" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="E198" t="s">
-        <v>587</v>
+        <v>574</v>
       </c>
       <c r="F198" t="s">
         <v>792</v>
@@ -8434,13 +8875,13 @@
         <v>425</v>
       </c>
       <c r="B199" t="s">
-        <v>955</v>
+        <v>942</v>
       </c>
       <c r="D199" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="E199" t="s">
-        <v>588</v>
+        <v>575</v>
       </c>
       <c r="F199" t="s">
         <v>792</v>
@@ -8454,13 +8895,13 @@
         <v>425</v>
       </c>
       <c r="B200" t="s">
-        <v>956</v>
+        <v>943</v>
       </c>
       <c r="D200" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="E200" t="s">
-        <v>589</v>
+        <v>576</v>
       </c>
       <c r="F200" t="s">
         <v>792</v>
@@ -8474,13 +8915,13 @@
         <v>425</v>
       </c>
       <c r="B201" t="s">
-        <v>957</v>
+        <v>1306</v>
       </c>
       <c r="D201" t="s">
-        <v>172</v>
+        <v>1307</v>
       </c>
       <c r="E201" t="s">
-        <v>590</v>
+        <v>1308</v>
       </c>
       <c r="F201" t="s">
         <v>792</v>
@@ -8494,13 +8935,13 @@
         <v>425</v>
       </c>
       <c r="B202" t="s">
-        <v>958</v>
+        <v>944</v>
       </c>
       <c r="D202" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="E202" t="s">
-        <v>591</v>
+        <v>577</v>
       </c>
       <c r="F202" t="s">
         <v>792</v>
@@ -8514,13 +8955,13 @@
         <v>425</v>
       </c>
       <c r="B203" t="s">
-        <v>959</v>
+        <v>945</v>
       </c>
       <c r="D203" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="E203" t="s">
-        <v>592</v>
+        <v>578</v>
       </c>
       <c r="F203" t="s">
         <v>792</v>
@@ -8534,13 +8975,13 @@
         <v>425</v>
       </c>
       <c r="B204" t="s">
-        <v>960</v>
+        <v>946</v>
       </c>
       <c r="D204" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
       <c r="E204" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="F204" t="s">
         <v>792</v>
@@ -8554,13 +8995,13 @@
         <v>425</v>
       </c>
       <c r="B205" t="s">
-        <v>961</v>
+        <v>1426</v>
       </c>
       <c r="D205" t="s">
-        <v>176</v>
+        <v>1427</v>
       </c>
       <c r="E205" t="s">
-        <v>594</v>
+        <v>1428</v>
       </c>
       <c r="F205" t="s">
         <v>792</v>
@@ -8574,13 +9015,13 @@
         <v>425</v>
       </c>
       <c r="B206" t="s">
-        <v>962</v>
+        <v>1309</v>
       </c>
       <c r="D206" t="s">
-        <v>177</v>
+        <v>1310</v>
       </c>
       <c r="E206" t="s">
-        <v>595</v>
+        <v>1311</v>
       </c>
       <c r="F206" t="s">
         <v>792</v>
@@ -8594,13 +9035,13 @@
         <v>425</v>
       </c>
       <c r="B207" t="s">
-        <v>963</v>
+        <v>1178</v>
       </c>
       <c r="D207" t="s">
-        <v>178</v>
+        <v>1126</v>
       </c>
       <c r="E207" t="s">
-        <v>596</v>
+        <v>1230</v>
       </c>
       <c r="F207" t="s">
         <v>792</v>
@@ -8614,13 +9055,13 @@
         <v>425</v>
       </c>
       <c r="B208" t="s">
-        <v>964</v>
+        <v>1179</v>
       </c>
       <c r="D208" t="s">
-        <v>179</v>
+        <v>1127</v>
       </c>
       <c r="E208" t="s">
-        <v>597</v>
+        <v>1231</v>
       </c>
       <c r="F208" t="s">
         <v>792</v>
@@ -8634,13 +9075,13 @@
         <v>425</v>
       </c>
       <c r="B209" t="s">
-        <v>965</v>
+        <v>1429</v>
       </c>
       <c r="D209" t="s">
-        <v>180</v>
+        <v>1430</v>
       </c>
       <c r="E209" t="s">
-        <v>598</v>
+        <v>1431</v>
       </c>
       <c r="F209" t="s">
         <v>792</v>
@@ -8654,13 +9095,13 @@
         <v>425</v>
       </c>
       <c r="B210" t="s">
-        <v>966</v>
+        <v>1282</v>
       </c>
       <c r="D210" t="s">
-        <v>181</v>
+        <v>1283</v>
       </c>
       <c r="E210" t="s">
-        <v>599</v>
+        <v>1284</v>
       </c>
       <c r="F210" t="s">
         <v>792</v>
@@ -8674,13 +9115,13 @@
         <v>425</v>
       </c>
       <c r="B211" t="s">
-        <v>1315</v>
+        <v>947</v>
       </c>
       <c r="D211" t="s">
-        <v>1316</v>
+        <v>162</v>
       </c>
       <c r="E211" t="s">
-        <v>1317</v>
+        <v>580</v>
       </c>
       <c r="F211" t="s">
         <v>792</v>
@@ -8694,13 +9135,13 @@
         <v>425</v>
       </c>
       <c r="B212" t="s">
-        <v>967</v>
+        <v>948</v>
       </c>
       <c r="D212" t="s">
-        <v>182</v>
+        <v>163</v>
       </c>
       <c r="E212" t="s">
-        <v>600</v>
+        <v>581</v>
       </c>
       <c r="F212" t="s">
         <v>792</v>
@@ -8714,13 +9155,13 @@
         <v>425</v>
       </c>
       <c r="B213" t="s">
-        <v>968</v>
+        <v>949</v>
       </c>
       <c r="D213" t="s">
-        <v>183</v>
+        <v>164</v>
       </c>
       <c r="E213" t="s">
-        <v>601</v>
+        <v>582</v>
       </c>
       <c r="F213" t="s">
         <v>792</v>
@@ -8734,13 +9175,13 @@
         <v>425</v>
       </c>
       <c r="B214" t="s">
-        <v>969</v>
+        <v>1180</v>
       </c>
       <c r="D214" t="s">
-        <v>184</v>
+        <v>1128</v>
       </c>
       <c r="E214" t="s">
-        <v>602</v>
+        <v>1232</v>
       </c>
       <c r="F214" t="s">
         <v>792</v>
@@ -8754,13 +9195,13 @@
         <v>425</v>
       </c>
       <c r="B215" t="s">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="D215" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="E215" t="s">
-        <v>603</v>
+        <v>583</v>
       </c>
       <c r="F215" t="s">
         <v>792</v>
@@ -8774,13 +9215,13 @@
         <v>425</v>
       </c>
       <c r="B216" t="s">
-        <v>1184</v>
+        <v>951</v>
       </c>
       <c r="D216" t="s">
-        <v>1131</v>
+        <v>166</v>
       </c>
       <c r="E216" t="s">
-        <v>1237</v>
+        <v>584</v>
       </c>
       <c r="F216" t="s">
         <v>792</v>
@@ -8794,13 +9235,13 @@
         <v>425</v>
       </c>
       <c r="B217" t="s">
-        <v>1318</v>
+        <v>952</v>
       </c>
       <c r="D217" t="s">
-        <v>1319</v>
+        <v>167</v>
       </c>
       <c r="E217" t="s">
-        <v>1320</v>
+        <v>585</v>
       </c>
       <c r="F217" t="s">
         <v>792</v>
@@ -8814,13 +9255,13 @@
         <v>425</v>
       </c>
       <c r="B218" t="s">
-        <v>971</v>
+        <v>1181</v>
       </c>
       <c r="D218" t="s">
-        <v>186</v>
+        <v>1129</v>
       </c>
       <c r="E218" t="s">
-        <v>604</v>
+        <v>1233</v>
       </c>
       <c r="F218" t="s">
         <v>792</v>
@@ -8834,13 +9275,13 @@
         <v>425</v>
       </c>
       <c r="B219" t="s">
-        <v>972</v>
+        <v>953</v>
       </c>
       <c r="D219" t="s">
-        <v>187</v>
+        <v>168</v>
       </c>
       <c r="E219" t="s">
-        <v>605</v>
+        <v>586</v>
       </c>
       <c r="F219" t="s">
         <v>792</v>
@@ -8854,13 +9295,13 @@
         <v>425</v>
       </c>
       <c r="B220" t="s">
-        <v>1185</v>
+        <v>954</v>
       </c>
       <c r="D220" t="s">
-        <v>1132</v>
+        <v>169</v>
       </c>
       <c r="E220" t="s">
-        <v>1238</v>
+        <v>587</v>
       </c>
       <c r="F220" t="s">
         <v>792</v>
@@ -8874,13 +9315,13 @@
         <v>425</v>
       </c>
       <c r="B221" t="s">
-        <v>973</v>
+        <v>955</v>
       </c>
       <c r="D221" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="E221" t="s">
-        <v>606</v>
+        <v>588</v>
       </c>
       <c r="F221" t="s">
         <v>792</v>
@@ -8894,13 +9335,13 @@
         <v>425</v>
       </c>
       <c r="B222" t="s">
-        <v>974</v>
+        <v>956</v>
       </c>
       <c r="D222" t="s">
-        <v>189</v>
+        <v>171</v>
       </c>
       <c r="E222" t="s">
-        <v>607</v>
+        <v>589</v>
       </c>
       <c r="F222" t="s">
         <v>792</v>
@@ -8914,13 +9355,13 @@
         <v>425</v>
       </c>
       <c r="B223" t="s">
-        <v>975</v>
+        <v>957</v>
       </c>
       <c r="D223" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
       <c r="E223" t="s">
-        <v>608</v>
+        <v>590</v>
       </c>
       <c r="F223" t="s">
         <v>792</v>
@@ -8934,13 +9375,13 @@
         <v>425</v>
       </c>
       <c r="B224" t="s">
-        <v>976</v>
+        <v>1432</v>
       </c>
       <c r="D224" t="s">
-        <v>191</v>
+        <v>1433</v>
       </c>
       <c r="E224" t="s">
-        <v>609</v>
+        <v>1434</v>
       </c>
       <c r="F224" t="s">
         <v>792</v>
@@ -8954,13 +9395,13 @@
         <v>425</v>
       </c>
       <c r="B225" t="s">
-        <v>977</v>
+        <v>958</v>
       </c>
       <c r="D225" t="s">
-        <v>192</v>
+        <v>173</v>
       </c>
       <c r="E225" t="s">
-        <v>610</v>
+        <v>591</v>
       </c>
       <c r="F225" t="s">
         <v>792</v>
@@ -8974,13 +9415,13 @@
         <v>425</v>
       </c>
       <c r="B226" t="s">
-        <v>978</v>
+        <v>959</v>
       </c>
       <c r="D226" t="s">
-        <v>193</v>
+        <v>174</v>
       </c>
       <c r="E226" t="s">
-        <v>611</v>
+        <v>592</v>
       </c>
       <c r="F226" t="s">
         <v>792</v>
@@ -8994,13 +9435,13 @@
         <v>425</v>
       </c>
       <c r="B227" t="s">
-        <v>1186</v>
+        <v>960</v>
       </c>
       <c r="D227" t="s">
-        <v>1133</v>
+        <v>175</v>
       </c>
       <c r="E227" t="s">
-        <v>1239</v>
+        <v>593</v>
       </c>
       <c r="F227" t="s">
         <v>792</v>
@@ -9014,13 +9455,13 @@
         <v>425</v>
       </c>
       <c r="B228" t="s">
-        <v>979</v>
+        <v>961</v>
       </c>
       <c r="D228" t="s">
-        <v>194</v>
+        <v>176</v>
       </c>
       <c r="E228" t="s">
-        <v>612</v>
+        <v>594</v>
       </c>
       <c r="F228" t="s">
         <v>792</v>
@@ -9034,13 +9475,13 @@
         <v>425</v>
       </c>
       <c r="B229" t="s">
-        <v>980</v>
+        <v>962</v>
       </c>
       <c r="D229" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="E229" t="s">
-        <v>613</v>
+        <v>595</v>
       </c>
       <c r="F229" t="s">
         <v>792</v>
@@ -9054,13 +9495,13 @@
         <v>425</v>
       </c>
       <c r="B230" t="s">
-        <v>981</v>
+        <v>963</v>
       </c>
       <c r="D230" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="E230" t="s">
-        <v>614</v>
+        <v>596</v>
       </c>
       <c r="F230" t="s">
         <v>792</v>
@@ -9074,13 +9515,13 @@
         <v>425</v>
       </c>
       <c r="B231" t="s">
-        <v>1321</v>
+        <v>964</v>
       </c>
       <c r="D231" t="s">
-        <v>1322</v>
+        <v>179</v>
       </c>
       <c r="E231" t="s">
-        <v>1323</v>
+        <v>597</v>
       </c>
       <c r="F231" t="s">
         <v>792</v>
@@ -9094,13 +9535,13 @@
         <v>425</v>
       </c>
       <c r="B232" t="s">
-        <v>982</v>
+        <v>965</v>
       </c>
       <c r="D232" t="s">
-        <v>197</v>
+        <v>180</v>
       </c>
       <c r="E232" t="s">
-        <v>615</v>
+        <v>598</v>
       </c>
       <c r="F232" t="s">
         <v>792</v>
@@ -9114,13 +9555,13 @@
         <v>425</v>
       </c>
       <c r="B233" t="s">
-        <v>1187</v>
+        <v>966</v>
       </c>
       <c r="D233" t="s">
-        <v>1134</v>
+        <v>181</v>
       </c>
       <c r="E233" t="s">
-        <v>1240</v>
+        <v>599</v>
       </c>
       <c r="F233" t="s">
         <v>792</v>
@@ -9134,13 +9575,13 @@
         <v>425</v>
       </c>
       <c r="B234" t="s">
-        <v>983</v>
+        <v>1312</v>
       </c>
       <c r="D234" t="s">
-        <v>198</v>
+        <v>1313</v>
       </c>
       <c r="E234" t="s">
-        <v>616</v>
+        <v>1314</v>
       </c>
       <c r="F234" t="s">
         <v>792</v>
@@ -9154,13 +9595,13 @@
         <v>425</v>
       </c>
       <c r="B235" t="s">
-        <v>984</v>
+        <v>1435</v>
       </c>
       <c r="D235" t="s">
-        <v>199</v>
+        <v>1436</v>
       </c>
       <c r="E235" t="s">
-        <v>617</v>
+        <v>1437</v>
       </c>
       <c r="F235" t="s">
         <v>792</v>
@@ -9174,13 +9615,13 @@
         <v>425</v>
       </c>
       <c r="B236" t="s">
-        <v>985</v>
+        <v>1438</v>
       </c>
       <c r="D236" t="s">
-        <v>200</v>
+        <v>1439</v>
       </c>
       <c r="E236" t="s">
-        <v>618</v>
+        <v>1440</v>
       </c>
       <c r="F236" t="s">
         <v>792</v>
@@ -9194,13 +9635,13 @@
         <v>425</v>
       </c>
       <c r="B237" t="s">
-        <v>986</v>
+        <v>967</v>
       </c>
       <c r="D237" t="s">
-        <v>201</v>
+        <v>182</v>
       </c>
       <c r="E237" t="s">
-        <v>619</v>
+        <v>600</v>
       </c>
       <c r="F237" t="s">
         <v>792</v>
@@ -9214,13 +9655,13 @@
         <v>425</v>
       </c>
       <c r="B238" t="s">
-        <v>987</v>
+        <v>968</v>
       </c>
       <c r="D238" t="s">
-        <v>202</v>
+        <v>183</v>
       </c>
       <c r="E238" t="s">
-        <v>620</v>
+        <v>601</v>
       </c>
       <c r="F238" t="s">
         <v>792</v>
@@ -9234,13 +9675,13 @@
         <v>425</v>
       </c>
       <c r="B239" t="s">
-        <v>988</v>
+        <v>969</v>
       </c>
       <c r="D239" t="s">
-        <v>203</v>
+        <v>184</v>
       </c>
       <c r="E239" t="s">
-        <v>621</v>
+        <v>602</v>
       </c>
       <c r="F239" t="s">
         <v>792</v>
@@ -9254,13 +9695,13 @@
         <v>425</v>
       </c>
       <c r="B240" t="s">
-        <v>989</v>
+        <v>970</v>
       </c>
       <c r="D240" t="s">
-        <v>204</v>
+        <v>185</v>
       </c>
       <c r="E240" t="s">
-        <v>622</v>
+        <v>603</v>
       </c>
       <c r="F240" t="s">
         <v>792</v>
@@ -9274,13 +9715,13 @@
         <v>425</v>
       </c>
       <c r="B241" t="s">
-        <v>990</v>
+        <v>1441</v>
       </c>
       <c r="D241" t="s">
-        <v>205</v>
+        <v>1442</v>
       </c>
       <c r="E241" t="s">
-        <v>623</v>
+        <v>1443</v>
       </c>
       <c r="F241" t="s">
         <v>792</v>
@@ -9294,13 +9735,13 @@
         <v>425</v>
       </c>
       <c r="B242" t="s">
-        <v>1324</v>
+        <v>1182</v>
       </c>
       <c r="D242" t="s">
-        <v>1325</v>
+        <v>1130</v>
       </c>
       <c r="E242" t="s">
-        <v>1326</v>
+        <v>1234</v>
       </c>
       <c r="F242" t="s">
         <v>792</v>
@@ -9314,13 +9755,13 @@
         <v>425</v>
       </c>
       <c r="B243" t="s">
-        <v>991</v>
+        <v>1315</v>
       </c>
       <c r="D243" t="s">
-        <v>206</v>
+        <v>1316</v>
       </c>
       <c r="E243" t="s">
-        <v>624</v>
+        <v>1317</v>
       </c>
       <c r="F243" t="s">
         <v>792</v>
@@ -9334,13 +9775,13 @@
         <v>425</v>
       </c>
       <c r="B244" t="s">
-        <v>992</v>
+        <v>971</v>
       </c>
       <c r="D244" t="s">
-        <v>207</v>
+        <v>186</v>
       </c>
       <c r="E244" t="s">
-        <v>625</v>
+        <v>604</v>
       </c>
       <c r="F244" t="s">
         <v>792</v>
@@ -9354,13 +9795,13 @@
         <v>425</v>
       </c>
       <c r="B245" t="s">
-        <v>993</v>
+        <v>972</v>
       </c>
       <c r="D245" t="s">
-        <v>208</v>
+        <v>187</v>
       </c>
       <c r="E245" t="s">
-        <v>626</v>
+        <v>605</v>
       </c>
       <c r="F245" t="s">
         <v>792</v>
@@ -9374,13 +9815,13 @@
         <v>425</v>
       </c>
       <c r="B246" t="s">
-        <v>994</v>
+        <v>1183</v>
       </c>
       <c r="D246" t="s">
-        <v>209</v>
+        <v>1131</v>
       </c>
       <c r="E246" t="s">
-        <v>627</v>
+        <v>1235</v>
       </c>
       <c r="F246" t="s">
         <v>792</v>
@@ -9394,13 +9835,13 @@
         <v>425</v>
       </c>
       <c r="B247" t="s">
-        <v>995</v>
+        <v>973</v>
       </c>
       <c r="D247" t="s">
-        <v>210</v>
+        <v>188</v>
       </c>
       <c r="E247" t="s">
-        <v>628</v>
+        <v>606</v>
       </c>
       <c r="F247" t="s">
         <v>792</v>
@@ -9414,13 +9855,13 @@
         <v>425</v>
       </c>
       <c r="B248" t="s">
-        <v>1327</v>
+        <v>974</v>
       </c>
       <c r="D248" t="s">
-        <v>1328</v>
+        <v>189</v>
       </c>
       <c r="E248" t="s">
-        <v>1329</v>
+        <v>607</v>
       </c>
       <c r="F248" t="s">
         <v>792</v>
@@ -9434,13 +9875,13 @@
         <v>425</v>
       </c>
       <c r="B249" t="s">
-        <v>996</v>
+        <v>975</v>
       </c>
       <c r="D249" t="s">
-        <v>211</v>
+        <v>190</v>
       </c>
       <c r="E249" t="s">
-        <v>629</v>
+        <v>608</v>
       </c>
       <c r="F249" t="s">
         <v>792</v>
@@ -9454,13 +9895,13 @@
         <v>425</v>
       </c>
       <c r="B250" t="s">
-        <v>997</v>
+        <v>976</v>
       </c>
       <c r="D250" t="s">
-        <v>212</v>
+        <v>191</v>
       </c>
       <c r="E250" t="s">
-        <v>630</v>
+        <v>609</v>
       </c>
       <c r="F250" t="s">
         <v>792</v>
@@ -9474,13 +9915,13 @@
         <v>425</v>
       </c>
       <c r="B251" t="s">
-        <v>998</v>
+        <v>1444</v>
       </c>
       <c r="D251" t="s">
-        <v>213</v>
+        <v>1445</v>
       </c>
       <c r="E251" t="s">
-        <v>631</v>
+        <v>1446</v>
       </c>
       <c r="F251" t="s">
         <v>792</v>
@@ -9494,13 +9935,13 @@
         <v>425</v>
       </c>
       <c r="B252" t="s">
-        <v>1330</v>
+        <v>977</v>
       </c>
       <c r="D252" t="s">
-        <v>1331</v>
+        <v>192</v>
       </c>
       <c r="E252" t="s">
-        <v>1332</v>
+        <v>610</v>
       </c>
       <c r="F252" t="s">
         <v>792</v>
@@ -9514,13 +9955,13 @@
         <v>425</v>
       </c>
       <c r="B253" t="s">
-        <v>999</v>
+        <v>1447</v>
       </c>
       <c r="D253" t="s">
-        <v>214</v>
+        <v>1448</v>
       </c>
       <c r="E253" t="s">
-        <v>632</v>
+        <v>1449</v>
       </c>
       <c r="F253" t="s">
         <v>792</v>
@@ -9534,13 +9975,13 @@
         <v>425</v>
       </c>
       <c r="B254" t="s">
-        <v>1188</v>
+        <v>978</v>
       </c>
       <c r="D254" t="s">
-        <v>1135</v>
+        <v>193</v>
       </c>
       <c r="E254" t="s">
-        <v>1241</v>
+        <v>611</v>
       </c>
       <c r="F254" t="s">
         <v>792</v>
@@ -9554,13 +9995,13 @@
         <v>425</v>
       </c>
       <c r="B255" t="s">
-        <v>1000</v>
+        <v>1184</v>
       </c>
       <c r="D255" t="s">
-        <v>215</v>
+        <v>1132</v>
       </c>
       <c r="E255" t="s">
-        <v>633</v>
+        <v>1236</v>
       </c>
       <c r="F255" t="s">
         <v>792</v>
@@ -9574,13 +10015,13 @@
         <v>425</v>
       </c>
       <c r="B256" t="s">
-        <v>1001</v>
+        <v>979</v>
       </c>
       <c r="D256" t="s">
-        <v>216</v>
+        <v>194</v>
       </c>
       <c r="E256" t="s">
-        <v>634</v>
+        <v>612</v>
       </c>
       <c r="F256" t="s">
         <v>792</v>
@@ -9594,13 +10035,13 @@
         <v>425</v>
       </c>
       <c r="B257" t="s">
-        <v>1002</v>
+        <v>980</v>
       </c>
       <c r="D257" t="s">
-        <v>217</v>
+        <v>195</v>
       </c>
       <c r="E257" t="s">
-        <v>635</v>
+        <v>613</v>
       </c>
       <c r="F257" t="s">
         <v>792</v>
@@ -9614,13 +10055,13 @@
         <v>425</v>
       </c>
       <c r="B258" t="s">
-        <v>1003</v>
+        <v>981</v>
       </c>
       <c r="D258" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="E258" t="s">
-        <v>636</v>
+        <v>614</v>
       </c>
       <c r="F258" t="s">
         <v>792</v>
@@ -9634,13 +10075,13 @@
         <v>425</v>
       </c>
       <c r="B259" t="s">
-        <v>1189</v>
+        <v>1318</v>
       </c>
       <c r="D259" t="s">
-        <v>1136</v>
+        <v>1319</v>
       </c>
       <c r="E259" t="s">
-        <v>1242</v>
+        <v>1320</v>
       </c>
       <c r="F259" t="s">
         <v>792</v>
@@ -9654,13 +10095,13 @@
         <v>425</v>
       </c>
       <c r="B260" t="s">
-        <v>1004</v>
+        <v>982</v>
       </c>
       <c r="D260" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="E260" t="s">
-        <v>637</v>
+        <v>615</v>
       </c>
       <c r="F260" t="s">
         <v>792</v>
@@ -9674,13 +10115,13 @@
         <v>425</v>
       </c>
       <c r="B261" t="s">
-        <v>1333</v>
+        <v>1185</v>
       </c>
       <c r="D261" t="s">
-        <v>1334</v>
+        <v>1133</v>
       </c>
       <c r="E261" t="s">
-        <v>1335</v>
+        <v>1237</v>
       </c>
       <c r="F261" t="s">
         <v>792</v>
@@ -9694,13 +10135,13 @@
         <v>425</v>
       </c>
       <c r="B262" t="s">
-        <v>1336</v>
+        <v>1450</v>
       </c>
       <c r="D262" t="s">
-        <v>1337</v>
+        <v>1451</v>
       </c>
       <c r="E262" t="s">
-        <v>1338</v>
+        <v>1452</v>
       </c>
       <c r="F262" t="s">
         <v>792</v>
@@ -9714,13 +10155,13 @@
         <v>425</v>
       </c>
       <c r="B263" t="s">
-        <v>1005</v>
+        <v>983</v>
       </c>
       <c r="D263" t="s">
-        <v>220</v>
+        <v>198</v>
       </c>
       <c r="E263" t="s">
-        <v>638</v>
+        <v>616</v>
       </c>
       <c r="F263" t="s">
         <v>792</v>
@@ -9734,13 +10175,13 @@
         <v>425</v>
       </c>
       <c r="B264" t="s">
-        <v>1006</v>
+        <v>984</v>
       </c>
       <c r="D264" t="s">
-        <v>221</v>
+        <v>199</v>
       </c>
       <c r="E264" t="s">
-        <v>639</v>
+        <v>617</v>
       </c>
       <c r="F264" t="s">
         <v>792</v>
@@ -9754,13 +10195,13 @@
         <v>425</v>
       </c>
       <c r="B265" t="s">
-        <v>1007</v>
+        <v>985</v>
       </c>
       <c r="D265" t="s">
-        <v>222</v>
+        <v>200</v>
       </c>
       <c r="E265" t="s">
-        <v>640</v>
+        <v>618</v>
       </c>
       <c r="F265" t="s">
         <v>792</v>
@@ -9774,13 +10215,13 @@
         <v>425</v>
       </c>
       <c r="B266" t="s">
-        <v>1008</v>
+        <v>986</v>
       </c>
       <c r="D266" t="s">
-        <v>223</v>
+        <v>201</v>
       </c>
       <c r="E266" t="s">
-        <v>641</v>
+        <v>619</v>
       </c>
       <c r="F266" t="s">
         <v>792</v>
@@ -9794,13 +10235,13 @@
         <v>425</v>
       </c>
       <c r="B267" t="s">
-        <v>1288</v>
+        <v>1498</v>
       </c>
       <c r="D267" t="s">
-        <v>1289</v>
+        <v>1499</v>
       </c>
       <c r="E267" t="s">
-        <v>1290</v>
+        <v>1500</v>
       </c>
       <c r="F267" t="s">
         <v>792</v>
@@ -9814,13 +10255,13 @@
         <v>425</v>
       </c>
       <c r="B268" t="s">
-        <v>1339</v>
+        <v>987</v>
       </c>
       <c r="D268" t="s">
-        <v>1340</v>
+        <v>202</v>
       </c>
       <c r="E268" t="s">
-        <v>1341</v>
+        <v>620</v>
       </c>
       <c r="F268" t="s">
         <v>792</v>
@@ -9834,13 +10275,13 @@
         <v>425</v>
       </c>
       <c r="B269" t="s">
-        <v>1009</v>
+        <v>988</v>
       </c>
       <c r="D269" t="s">
-        <v>224</v>
+        <v>203</v>
       </c>
       <c r="E269" t="s">
-        <v>642</v>
+        <v>621</v>
       </c>
       <c r="F269" t="s">
         <v>792</v>
@@ -9854,13 +10295,13 @@
         <v>425</v>
       </c>
       <c r="B270" t="s">
-        <v>1010</v>
+        <v>989</v>
       </c>
       <c r="D270" t="s">
-        <v>225</v>
+        <v>204</v>
       </c>
       <c r="E270" t="s">
-        <v>643</v>
+        <v>622</v>
       </c>
       <c r="F270" t="s">
         <v>792</v>
@@ -9874,13 +10315,13 @@
         <v>425</v>
       </c>
       <c r="B271" t="s">
-        <v>1011</v>
+        <v>990</v>
       </c>
       <c r="D271" t="s">
-        <v>226</v>
+        <v>205</v>
       </c>
       <c r="E271" t="s">
-        <v>644</v>
+        <v>623</v>
       </c>
       <c r="F271" t="s">
         <v>792</v>
@@ -9894,13 +10335,13 @@
         <v>425</v>
       </c>
       <c r="B272" t="s">
-        <v>1190</v>
+        <v>1321</v>
       </c>
       <c r="D272" t="s">
-        <v>1137</v>
+        <v>1322</v>
       </c>
       <c r="E272" t="s">
-        <v>1243</v>
+        <v>1323</v>
       </c>
       <c r="F272" t="s">
         <v>792</v>
@@ -9914,13 +10355,13 @@
         <v>425</v>
       </c>
       <c r="B273" t="s">
-        <v>1012</v>
+        <v>1453</v>
       </c>
       <c r="D273" t="s">
-        <v>227</v>
+        <v>1454</v>
       </c>
       <c r="E273" t="s">
-        <v>645</v>
+        <v>1455</v>
       </c>
       <c r="F273" t="s">
         <v>792</v>
@@ -9934,13 +10375,13 @@
         <v>425</v>
       </c>
       <c r="B274" t="s">
-        <v>1013</v>
+        <v>991</v>
       </c>
       <c r="D274" t="s">
-        <v>228</v>
+        <v>206</v>
       </c>
       <c r="E274" t="s">
-        <v>646</v>
+        <v>624</v>
       </c>
       <c r="F274" t="s">
         <v>792</v>
@@ -9954,13 +10395,13 @@
         <v>425</v>
       </c>
       <c r="B275" t="s">
-        <v>1191</v>
+        <v>992</v>
       </c>
       <c r="D275" t="s">
-        <v>1138</v>
+        <v>207</v>
       </c>
       <c r="E275" t="s">
-        <v>1244</v>
+        <v>625</v>
       </c>
       <c r="F275" t="s">
         <v>792</v>
@@ -9974,13 +10415,13 @@
         <v>425</v>
       </c>
       <c r="B276" t="s">
-        <v>1014</v>
+        <v>993</v>
       </c>
       <c r="D276" t="s">
-        <v>229</v>
+        <v>208</v>
       </c>
       <c r="E276" t="s">
-        <v>647</v>
+        <v>626</v>
       </c>
       <c r="F276" t="s">
         <v>792</v>
@@ -9994,13 +10435,13 @@
         <v>425</v>
       </c>
       <c r="B277" t="s">
-        <v>1015</v>
+        <v>994</v>
       </c>
       <c r="D277" t="s">
-        <v>230</v>
+        <v>209</v>
       </c>
       <c r="E277" t="s">
-        <v>648</v>
+        <v>627</v>
       </c>
       <c r="F277" t="s">
         <v>792</v>
@@ -10014,13 +10455,13 @@
         <v>425</v>
       </c>
       <c r="B278" t="s">
-        <v>1016</v>
+        <v>1456</v>
       </c>
       <c r="D278" t="s">
-        <v>231</v>
+        <v>1457</v>
       </c>
       <c r="E278" t="s">
-        <v>649</v>
+        <v>1458</v>
       </c>
       <c r="F278" t="s">
         <v>792</v>
@@ -10034,13 +10475,13 @@
         <v>425</v>
       </c>
       <c r="B279" t="s">
-        <v>1017</v>
+        <v>995</v>
       </c>
       <c r="D279" t="s">
-        <v>232</v>
+        <v>210</v>
       </c>
       <c r="E279" t="s">
-        <v>650</v>
+        <v>628</v>
       </c>
       <c r="F279" t="s">
         <v>792</v>
@@ -10054,13 +10495,13 @@
         <v>425</v>
       </c>
       <c r="B280" t="s">
-        <v>1018</v>
+        <v>1324</v>
       </c>
       <c r="D280" t="s">
-        <v>233</v>
+        <v>1325</v>
       </c>
       <c r="E280" t="s">
-        <v>651</v>
+        <v>1326</v>
       </c>
       <c r="F280" t="s">
         <v>792</v>
@@ -10074,13 +10515,13 @@
         <v>425</v>
       </c>
       <c r="B281" t="s">
-        <v>1019</v>
+        <v>1501</v>
       </c>
       <c r="D281" t="s">
-        <v>234</v>
+        <v>1502</v>
       </c>
       <c r="E281" t="s">
-        <v>652</v>
+        <v>1503</v>
       </c>
       <c r="F281" t="s">
         <v>792</v>
@@ -10094,13 +10535,13 @@
         <v>425</v>
       </c>
       <c r="B282" t="s">
-        <v>1020</v>
+        <v>996</v>
       </c>
       <c r="D282" t="s">
-        <v>235</v>
+        <v>211</v>
       </c>
       <c r="E282" t="s">
-        <v>653</v>
+        <v>629</v>
       </c>
       <c r="F282" t="s">
         <v>792</v>
@@ -10114,13 +10555,13 @@
         <v>425</v>
       </c>
       <c r="B283" t="s">
-        <v>1192</v>
+        <v>997</v>
       </c>
       <c r="D283" t="s">
-        <v>1139</v>
+        <v>212</v>
       </c>
       <c r="E283" t="s">
-        <v>1245</v>
+        <v>630</v>
       </c>
       <c r="F283" t="s">
         <v>792</v>
@@ -10134,13 +10575,13 @@
         <v>425</v>
       </c>
       <c r="B284" t="s">
-        <v>1021</v>
+        <v>998</v>
       </c>
       <c r="D284" t="s">
-        <v>236</v>
+        <v>213</v>
       </c>
       <c r="E284" t="s">
-        <v>654</v>
+        <v>631</v>
       </c>
       <c r="F284" t="s">
         <v>792</v>
@@ -10154,13 +10595,13 @@
         <v>425</v>
       </c>
       <c r="B285" t="s">
-        <v>1022</v>
+        <v>1327</v>
       </c>
       <c r="D285" t="s">
-        <v>237</v>
+        <v>1328</v>
       </c>
       <c r="E285" t="s">
-        <v>655</v>
+        <v>1329</v>
       </c>
       <c r="F285" t="s">
         <v>792</v>
@@ -10174,13 +10615,13 @@
         <v>425</v>
       </c>
       <c r="B286" t="s">
-        <v>1023</v>
+        <v>999</v>
       </c>
       <c r="D286" t="s">
-        <v>238</v>
+        <v>214</v>
       </c>
       <c r="E286" t="s">
-        <v>656</v>
+        <v>632</v>
       </c>
       <c r="F286" t="s">
         <v>792</v>
@@ -10194,13 +10635,13 @@
         <v>425</v>
       </c>
       <c r="B287" t="s">
-        <v>1193</v>
+        <v>1186</v>
       </c>
       <c r="D287" t="s">
-        <v>1140</v>
+        <v>1134</v>
       </c>
       <c r="E287" t="s">
-        <v>1246</v>
+        <v>1238</v>
       </c>
       <c r="F287" t="s">
         <v>792</v>
@@ -10214,13 +10655,13 @@
         <v>425</v>
       </c>
       <c r="B288" t="s">
-        <v>1024</v>
+        <v>1000</v>
       </c>
       <c r="D288" t="s">
-        <v>239</v>
+        <v>215</v>
       </c>
       <c r="E288" t="s">
-        <v>657</v>
+        <v>633</v>
       </c>
       <c r="F288" t="s">
         <v>792</v>
@@ -10234,13 +10675,13 @@
         <v>425</v>
       </c>
       <c r="B289" t="s">
-        <v>1025</v>
+        <v>1001</v>
       </c>
       <c r="D289" t="s">
-        <v>240</v>
+        <v>216</v>
       </c>
       <c r="E289" t="s">
-        <v>658</v>
+        <v>634</v>
       </c>
       <c r="F289" t="s">
         <v>792</v>
@@ -10254,13 +10695,13 @@
         <v>425</v>
       </c>
       <c r="B290" t="s">
-        <v>1026</v>
+        <v>1002</v>
       </c>
       <c r="D290" t="s">
-        <v>241</v>
+        <v>217</v>
       </c>
       <c r="E290" t="s">
-        <v>659</v>
+        <v>635</v>
       </c>
       <c r="F290" t="s">
         <v>792</v>
@@ -10274,13 +10715,13 @@
         <v>425</v>
       </c>
       <c r="B291" t="s">
-        <v>1027</v>
+        <v>1003</v>
       </c>
       <c r="D291" t="s">
-        <v>242</v>
+        <v>218</v>
       </c>
       <c r="E291" t="s">
-        <v>660</v>
+        <v>636</v>
       </c>
       <c r="F291" t="s">
         <v>792</v>
@@ -10294,13 +10735,13 @@
         <v>425</v>
       </c>
       <c r="B292" t="s">
-        <v>1028</v>
+        <v>1187</v>
       </c>
       <c r="D292" t="s">
-        <v>243</v>
+        <v>1135</v>
       </c>
       <c r="E292" t="s">
-        <v>661</v>
+        <v>1239</v>
       </c>
       <c r="F292" t="s">
         <v>792</v>
@@ -10314,13 +10755,13 @@
         <v>425</v>
       </c>
       <c r="B293" t="s">
-        <v>1029</v>
+        <v>1004</v>
       </c>
       <c r="D293" t="s">
-        <v>244</v>
+        <v>219</v>
       </c>
       <c r="E293" t="s">
-        <v>662</v>
+        <v>637</v>
       </c>
       <c r="F293" t="s">
         <v>792</v>
@@ -10334,13 +10775,13 @@
         <v>425</v>
       </c>
       <c r="B294" t="s">
-        <v>1030</v>
+        <v>1330</v>
       </c>
       <c r="D294" t="s">
-        <v>245</v>
+        <v>1331</v>
       </c>
       <c r="E294" t="s">
-        <v>663</v>
+        <v>1332</v>
       </c>
       <c r="F294" t="s">
         <v>792</v>
@@ -10354,13 +10795,13 @@
         <v>425</v>
       </c>
       <c r="B295" t="s">
-        <v>1031</v>
+        <v>1333</v>
       </c>
       <c r="D295" t="s">
-        <v>246</v>
+        <v>1334</v>
       </c>
       <c r="E295" t="s">
-        <v>664</v>
+        <v>1335</v>
       </c>
       <c r="F295" t="s">
         <v>792</v>
@@ -10374,13 +10815,13 @@
         <v>425</v>
       </c>
       <c r="B296" t="s">
-        <v>1032</v>
+        <v>1005</v>
       </c>
       <c r="D296" t="s">
-        <v>247</v>
+        <v>220</v>
       </c>
       <c r="E296" t="s">
-        <v>665</v>
+        <v>638</v>
       </c>
       <c r="F296" t="s">
         <v>792</v>
@@ -10394,13 +10835,13 @@
         <v>425</v>
       </c>
       <c r="B297" t="s">
-        <v>1342</v>
+        <v>1006</v>
       </c>
       <c r="D297" t="s">
-        <v>1343</v>
+        <v>221</v>
       </c>
       <c r="E297" t="s">
-        <v>1344</v>
+        <v>639</v>
       </c>
       <c r="F297" t="s">
         <v>792</v>
@@ -10414,13 +10855,13 @@
         <v>425</v>
       </c>
       <c r="B298" t="s">
-        <v>1033</v>
+        <v>1007</v>
       </c>
       <c r="D298" t="s">
-        <v>248</v>
+        <v>222</v>
       </c>
       <c r="E298" t="s">
-        <v>666</v>
+        <v>640</v>
       </c>
       <c r="F298" t="s">
         <v>792</v>
@@ -10434,13 +10875,13 @@
         <v>425</v>
       </c>
       <c r="B299" t="s">
-        <v>1034</v>
+        <v>1008</v>
       </c>
       <c r="D299" t="s">
-        <v>249</v>
+        <v>223</v>
       </c>
       <c r="E299" t="s">
-        <v>667</v>
+        <v>641</v>
       </c>
       <c r="F299" t="s">
         <v>792</v>
@@ -10454,13 +10895,13 @@
         <v>425</v>
       </c>
       <c r="B300" t="s">
-        <v>1035</v>
+        <v>1459</v>
       </c>
       <c r="D300" t="s">
-        <v>250</v>
+        <v>1460</v>
       </c>
       <c r="E300" t="s">
-        <v>668</v>
+        <v>1461</v>
       </c>
       <c r="F300" t="s">
         <v>792</v>
@@ -10474,13 +10915,13 @@
         <v>425</v>
       </c>
       <c r="B301" t="s">
-        <v>1036</v>
+        <v>1285</v>
       </c>
       <c r="D301" t="s">
-        <v>251</v>
+        <v>1286</v>
       </c>
       <c r="E301" t="s">
-        <v>669</v>
+        <v>1287</v>
       </c>
       <c r="F301" t="s">
         <v>792</v>
@@ -10494,13 +10935,13 @@
         <v>425</v>
       </c>
       <c r="B302" t="s">
-        <v>1037</v>
+        <v>1336</v>
       </c>
       <c r="D302" t="s">
-        <v>252</v>
+        <v>1337</v>
       </c>
       <c r="E302" t="s">
-        <v>670</v>
+        <v>1338</v>
       </c>
       <c r="F302" t="s">
         <v>792</v>
@@ -10514,13 +10955,13 @@
         <v>425</v>
       </c>
       <c r="B303" t="s">
-        <v>1038</v>
+        <v>1009</v>
       </c>
       <c r="D303" t="s">
-        <v>253</v>
+        <v>224</v>
       </c>
       <c r="E303" t="s">
-        <v>671</v>
+        <v>642</v>
       </c>
       <c r="F303" t="s">
         <v>792</v>
@@ -10534,13 +10975,13 @@
         <v>425</v>
       </c>
       <c r="B304" t="s">
-        <v>1039</v>
+        <v>1010</v>
       </c>
       <c r="D304" t="s">
-        <v>254</v>
+        <v>225</v>
       </c>
       <c r="E304" t="s">
-        <v>672</v>
+        <v>643</v>
       </c>
       <c r="F304" t="s">
         <v>792</v>
@@ -10554,13 +10995,13 @@
         <v>425</v>
       </c>
       <c r="B305" t="s">
-        <v>1040</v>
+        <v>1011</v>
       </c>
       <c r="D305" t="s">
-        <v>255</v>
+        <v>226</v>
       </c>
       <c r="E305" t="s">
-        <v>673</v>
+        <v>644</v>
       </c>
       <c r="F305" t="s">
         <v>792</v>
@@ -10574,13 +11015,13 @@
         <v>425</v>
       </c>
       <c r="B306" t="s">
-        <v>1041</v>
+        <v>1188</v>
       </c>
       <c r="D306" t="s">
-        <v>256</v>
+        <v>1136</v>
       </c>
       <c r="E306" t="s">
-        <v>674</v>
+        <v>1240</v>
       </c>
       <c r="F306" t="s">
         <v>792</v>
@@ -10594,13 +11035,13 @@
         <v>425</v>
       </c>
       <c r="B307" t="s">
-        <v>1042</v>
+        <v>1012</v>
       </c>
       <c r="D307" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
       <c r="E307" t="s">
-        <v>675</v>
+        <v>645</v>
       </c>
       <c r="F307" t="s">
         <v>792</v>
@@ -10614,13 +11055,13 @@
         <v>425</v>
       </c>
       <c r="B308" t="s">
-        <v>1043</v>
+        <v>1504</v>
       </c>
       <c r="D308" t="s">
-        <v>258</v>
+        <v>1505</v>
       </c>
       <c r="E308" t="s">
-        <v>676</v>
+        <v>1506</v>
       </c>
       <c r="F308" t="s">
         <v>792</v>
@@ -10634,13 +11075,13 @@
         <v>425</v>
       </c>
       <c r="B309" t="s">
-        <v>1044</v>
+        <v>1013</v>
       </c>
       <c r="D309" t="s">
-        <v>259</v>
+        <v>228</v>
       </c>
       <c r="E309" t="s">
-        <v>677</v>
+        <v>646</v>
       </c>
       <c r="F309" t="s">
         <v>792</v>
@@ -10654,13 +11095,13 @@
         <v>425</v>
       </c>
       <c r="B310" t="s">
-        <v>1194</v>
+        <v>1189</v>
       </c>
       <c r="D310" t="s">
-        <v>1141</v>
+        <v>1137</v>
       </c>
       <c r="E310" t="s">
-        <v>1247</v>
+        <v>1241</v>
       </c>
       <c r="F310" t="s">
         <v>792</v>
@@ -10674,13 +11115,13 @@
         <v>425</v>
       </c>
       <c r="B311" t="s">
-        <v>1045</v>
+        <v>1014</v>
       </c>
       <c r="D311" t="s">
-        <v>260</v>
+        <v>229</v>
       </c>
       <c r="E311" t="s">
-        <v>678</v>
+        <v>647</v>
       </c>
       <c r="F311" t="s">
         <v>792</v>
@@ -10694,13 +11135,13 @@
         <v>425</v>
       </c>
       <c r="B312" t="s">
-        <v>1046</v>
+        <v>1015</v>
       </c>
       <c r="D312" t="s">
-        <v>261</v>
+        <v>230</v>
       </c>
       <c r="E312" t="s">
-        <v>679</v>
+        <v>648</v>
       </c>
       <c r="F312" t="s">
         <v>792</v>
@@ -10714,13 +11155,13 @@
         <v>425</v>
       </c>
       <c r="B313" t="s">
-        <v>1047</v>
+        <v>1016</v>
       </c>
       <c r="D313" t="s">
-        <v>262</v>
+        <v>231</v>
       </c>
       <c r="E313" t="s">
-        <v>680</v>
+        <v>649</v>
       </c>
       <c r="F313" t="s">
         <v>792</v>
@@ -10734,13 +11175,13 @@
         <v>425</v>
       </c>
       <c r="B314" t="s">
-        <v>1291</v>
+        <v>1017</v>
       </c>
       <c r="D314" t="s">
-        <v>1292</v>
+        <v>232</v>
       </c>
       <c r="E314" t="s">
-        <v>1293</v>
+        <v>650</v>
       </c>
       <c r="F314" t="s">
         <v>792</v>
@@ -10754,13 +11195,13 @@
         <v>425</v>
       </c>
       <c r="B315" t="s">
-        <v>1048</v>
+        <v>1018</v>
       </c>
       <c r="D315" t="s">
-        <v>263</v>
+        <v>233</v>
       </c>
       <c r="E315" t="s">
-        <v>681</v>
+        <v>651</v>
       </c>
       <c r="F315" t="s">
         <v>792</v>
@@ -10774,13 +11215,13 @@
         <v>425</v>
       </c>
       <c r="B316" t="s">
-        <v>1049</v>
+        <v>1019</v>
       </c>
       <c r="D316" t="s">
-        <v>264</v>
+        <v>234</v>
       </c>
       <c r="E316" t="s">
-        <v>682</v>
+        <v>652</v>
       </c>
       <c r="F316" t="s">
         <v>792</v>
@@ -10794,13 +11235,13 @@
         <v>425</v>
       </c>
       <c r="B317" t="s">
-        <v>1050</v>
+        <v>1020</v>
       </c>
       <c r="D317" t="s">
-        <v>265</v>
+        <v>235</v>
       </c>
       <c r="E317" t="s">
-        <v>683</v>
+        <v>653</v>
       </c>
       <c r="F317" t="s">
         <v>792</v>
@@ -10814,13 +11255,13 @@
         <v>425</v>
       </c>
       <c r="B318" t="s">
-        <v>1051</v>
+        <v>1190</v>
       </c>
       <c r="D318" t="s">
-        <v>266</v>
+        <v>1138</v>
       </c>
       <c r="E318" t="s">
-        <v>684</v>
+        <v>1242</v>
       </c>
       <c r="F318" t="s">
         <v>792</v>
@@ -10834,13 +11275,13 @@
         <v>425</v>
       </c>
       <c r="B319" t="s">
-        <v>1052</v>
+        <v>1021</v>
       </c>
       <c r="D319" t="s">
-        <v>267</v>
+        <v>236</v>
       </c>
       <c r="E319" t="s">
-        <v>685</v>
+        <v>654</v>
       </c>
       <c r="F319" t="s">
         <v>792</v>
@@ -10854,13 +11295,13 @@
         <v>425</v>
       </c>
       <c r="B320" t="s">
-        <v>1053</v>
+        <v>1022</v>
       </c>
       <c r="D320" t="s">
-        <v>268</v>
+        <v>237</v>
       </c>
       <c r="E320" t="s">
-        <v>686</v>
+        <v>655</v>
       </c>
       <c r="F320" t="s">
         <v>792</v>
@@ -10874,13 +11315,13 @@
         <v>425</v>
       </c>
       <c r="B321" t="s">
-        <v>1054</v>
+        <v>1023</v>
       </c>
       <c r="D321" t="s">
-        <v>269</v>
+        <v>238</v>
       </c>
       <c r="E321" t="s">
-        <v>687</v>
+        <v>656</v>
       </c>
       <c r="F321" t="s">
         <v>792</v>
@@ -10894,13 +11335,13 @@
         <v>425</v>
       </c>
       <c r="B322" t="s">
-        <v>1055</v>
+        <v>1191</v>
       </c>
       <c r="D322" t="s">
-        <v>270</v>
+        <v>1139</v>
       </c>
       <c r="E322" t="s">
-        <v>688</v>
+        <v>1243</v>
       </c>
       <c r="F322" t="s">
         <v>792</v>
@@ -10914,13 +11355,13 @@
         <v>425</v>
       </c>
       <c r="B323" t="s">
-        <v>1056</v>
+        <v>1024</v>
       </c>
       <c r="D323" t="s">
-        <v>271</v>
+        <v>239</v>
       </c>
       <c r="E323" t="s">
-        <v>689</v>
+        <v>657</v>
       </c>
       <c r="F323" t="s">
         <v>792</v>
@@ -10934,13 +11375,13 @@
         <v>425</v>
       </c>
       <c r="B324" t="s">
-        <v>1057</v>
+        <v>1025</v>
       </c>
       <c r="D324" t="s">
-        <v>272</v>
+        <v>240</v>
       </c>
       <c r="E324" t="s">
-        <v>690</v>
+        <v>658</v>
       </c>
       <c r="F324" t="s">
         <v>792</v>
@@ -10954,13 +11395,13 @@
         <v>425</v>
       </c>
       <c r="B325" t="s">
-        <v>1058</v>
+        <v>1026</v>
       </c>
       <c r="D325" t="s">
-        <v>273</v>
+        <v>241</v>
       </c>
       <c r="E325" t="s">
-        <v>691</v>
+        <v>659</v>
       </c>
       <c r="F325" t="s">
         <v>792</v>
@@ -10974,13 +11415,13 @@
         <v>425</v>
       </c>
       <c r="B326" t="s">
-        <v>1059</v>
+        <v>1027</v>
       </c>
       <c r="D326" t="s">
-        <v>274</v>
+        <v>242</v>
       </c>
       <c r="E326" t="s">
-        <v>692</v>
+        <v>660</v>
       </c>
       <c r="F326" t="s">
         <v>792</v>
@@ -10994,13 +11435,13 @@
         <v>425</v>
       </c>
       <c r="B327" t="s">
-        <v>1060</v>
+        <v>1028</v>
       </c>
       <c r="D327" t="s">
-        <v>275</v>
+        <v>243</v>
       </c>
       <c r="E327" t="s">
-        <v>693</v>
+        <v>661</v>
       </c>
       <c r="F327" t="s">
         <v>792</v>
@@ -11014,13 +11455,13 @@
         <v>425</v>
       </c>
       <c r="B328" t="s">
-        <v>1061</v>
+        <v>1029</v>
       </c>
       <c r="D328" t="s">
-        <v>276</v>
+        <v>244</v>
       </c>
       <c r="E328" t="s">
-        <v>694</v>
+        <v>662</v>
       </c>
       <c r="F328" t="s">
         <v>792</v>
@@ -11034,13 +11475,13 @@
         <v>425</v>
       </c>
       <c r="B329" t="s">
-        <v>1062</v>
+        <v>1030</v>
       </c>
       <c r="D329" t="s">
-        <v>277</v>
+        <v>245</v>
       </c>
       <c r="E329" t="s">
-        <v>695</v>
+        <v>663</v>
       </c>
       <c r="F329" t="s">
         <v>792</v>
@@ -11054,13 +11495,13 @@
         <v>425</v>
       </c>
       <c r="B330" t="s">
-        <v>1063</v>
+        <v>1031</v>
       </c>
       <c r="D330" t="s">
-        <v>278</v>
+        <v>246</v>
       </c>
       <c r="E330" t="s">
-        <v>696</v>
+        <v>664</v>
       </c>
       <c r="F330" t="s">
         <v>792</v>
@@ -11074,13 +11515,13 @@
         <v>425</v>
       </c>
       <c r="B331" t="s">
-        <v>1064</v>
+        <v>1032</v>
       </c>
       <c r="D331" t="s">
-        <v>279</v>
+        <v>247</v>
       </c>
       <c r="E331" t="s">
-        <v>697</v>
+        <v>665</v>
       </c>
       <c r="F331" t="s">
         <v>792</v>
@@ -11094,13 +11535,13 @@
         <v>425</v>
       </c>
       <c r="B332" t="s">
-        <v>1065</v>
+        <v>1339</v>
       </c>
       <c r="D332" t="s">
-        <v>280</v>
+        <v>1340</v>
       </c>
       <c r="E332" t="s">
-        <v>698</v>
+        <v>1341</v>
       </c>
       <c r="F332" t="s">
         <v>792</v>
@@ -11114,13 +11555,13 @@
         <v>425</v>
       </c>
       <c r="B333" t="s">
-        <v>1066</v>
+        <v>1033</v>
       </c>
       <c r="D333" t="s">
-        <v>281</v>
+        <v>248</v>
       </c>
       <c r="E333" t="s">
-        <v>699</v>
+        <v>666</v>
       </c>
       <c r="F333" t="s">
         <v>792</v>
@@ -11134,13 +11575,13 @@
         <v>425</v>
       </c>
       <c r="B334" t="s">
-        <v>1067</v>
+        <v>1034</v>
       </c>
       <c r="D334" t="s">
-        <v>282</v>
+        <v>249</v>
       </c>
       <c r="E334" t="s">
-        <v>700</v>
+        <v>667</v>
       </c>
       <c r="F334" t="s">
         <v>792</v>
@@ -11154,13 +11595,13 @@
         <v>425</v>
       </c>
       <c r="B335" t="s">
-        <v>1068</v>
+        <v>1035</v>
       </c>
       <c r="D335" t="s">
-        <v>283</v>
+        <v>250</v>
       </c>
       <c r="E335" t="s">
-        <v>701</v>
+        <v>668</v>
       </c>
       <c r="F335" t="s">
         <v>792</v>
@@ -11174,13 +11615,13 @@
         <v>425</v>
       </c>
       <c r="B336" t="s">
-        <v>1069</v>
+        <v>1462</v>
       </c>
       <c r="D336" t="s">
-        <v>284</v>
+        <v>1463</v>
       </c>
       <c r="E336" t="s">
-        <v>702</v>
+        <v>1464</v>
       </c>
       <c r="F336" t="s">
         <v>792</v>
@@ -11194,13 +11635,13 @@
         <v>425</v>
       </c>
       <c r="B337" t="s">
-        <v>1070</v>
+        <v>1036</v>
       </c>
       <c r="D337" t="s">
-        <v>285</v>
+        <v>251</v>
       </c>
       <c r="E337" t="s">
-        <v>703</v>
+        <v>669</v>
       </c>
       <c r="F337" t="s">
         <v>792</v>
@@ -11214,13 +11655,13 @@
         <v>425</v>
       </c>
       <c r="B338" t="s">
-        <v>1345</v>
+        <v>1037</v>
       </c>
       <c r="D338" t="s">
-        <v>1346</v>
+        <v>252</v>
       </c>
       <c r="E338" t="s">
-        <v>1347</v>
+        <v>670</v>
       </c>
       <c r="F338" t="s">
         <v>792</v>
@@ -11234,13 +11675,13 @@
         <v>425</v>
       </c>
       <c r="B339" t="s">
-        <v>1071</v>
+        <v>1038</v>
       </c>
       <c r="D339" t="s">
-        <v>286</v>
+        <v>253</v>
       </c>
       <c r="E339" t="s">
-        <v>704</v>
+        <v>671</v>
       </c>
       <c r="F339" t="s">
         <v>792</v>
@@ -11254,13 +11695,13 @@
         <v>425</v>
       </c>
       <c r="B340" t="s">
-        <v>1072</v>
+        <v>1465</v>
       </c>
       <c r="D340" t="s">
-        <v>287</v>
+        <v>1466</v>
       </c>
       <c r="E340" t="s">
-        <v>705</v>
+        <v>1467</v>
       </c>
       <c r="F340" t="s">
         <v>792</v>
@@ -11274,13 +11715,13 @@
         <v>425</v>
       </c>
       <c r="B341" t="s">
-        <v>1195</v>
+        <v>1039</v>
       </c>
       <c r="D341" t="s">
-        <v>1142</v>
+        <v>254</v>
       </c>
       <c r="E341" t="s">
-        <v>1248</v>
+        <v>672</v>
       </c>
       <c r="F341" t="s">
         <v>792</v>
@@ -11294,13 +11735,13 @@
         <v>425</v>
       </c>
       <c r="B342" t="s">
-        <v>1073</v>
+        <v>1040</v>
       </c>
       <c r="D342" t="s">
-        <v>288</v>
+        <v>255</v>
       </c>
       <c r="E342" t="s">
-        <v>706</v>
+        <v>673</v>
       </c>
       <c r="F342" t="s">
         <v>792</v>
@@ -11314,13 +11755,13 @@
         <v>425</v>
       </c>
       <c r="B343" t="s">
-        <v>1074</v>
+        <v>1041</v>
       </c>
       <c r="D343" t="s">
-        <v>289</v>
+        <v>256</v>
       </c>
       <c r="E343" t="s">
-        <v>707</v>
+        <v>674</v>
       </c>
       <c r="F343" t="s">
         <v>792</v>
@@ -11334,13 +11775,13 @@
         <v>425</v>
       </c>
       <c r="B344" t="s">
-        <v>1075</v>
+        <v>1468</v>
       </c>
       <c r="D344" t="s">
-        <v>290</v>
+        <v>1469</v>
       </c>
       <c r="E344" t="s">
-        <v>708</v>
+        <v>1470</v>
       </c>
       <c r="F344" t="s">
         <v>792</v>
@@ -11354,13 +11795,13 @@
         <v>425</v>
       </c>
       <c r="B345" t="s">
-        <v>1076</v>
+        <v>1042</v>
       </c>
       <c r="D345" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="E345" t="s">
-        <v>709</v>
+        <v>675</v>
       </c>
       <c r="F345" t="s">
         <v>792</v>
@@ -11374,13 +11815,13 @@
         <v>425</v>
       </c>
       <c r="B346" t="s">
-        <v>1077</v>
+        <v>1043</v>
       </c>
       <c r="D346" t="s">
-        <v>292</v>
+        <v>258</v>
       </c>
       <c r="E346" t="s">
-        <v>710</v>
+        <v>676</v>
       </c>
       <c r="F346" t="s">
         <v>792</v>
@@ -11394,13 +11835,13 @@
         <v>425</v>
       </c>
       <c r="B347" t="s">
-        <v>1078</v>
+        <v>1471</v>
       </c>
       <c r="D347" t="s">
-        <v>293</v>
+        <v>1472</v>
       </c>
       <c r="E347" t="s">
-        <v>711</v>
+        <v>1473</v>
       </c>
       <c r="F347" t="s">
         <v>792</v>
@@ -11414,13 +11855,13 @@
         <v>425</v>
       </c>
       <c r="B348" t="s">
-        <v>1196</v>
+        <v>1044</v>
       </c>
       <c r="D348" t="s">
-        <v>1143</v>
+        <v>259</v>
       </c>
       <c r="E348" t="s">
-        <v>1249</v>
+        <v>677</v>
       </c>
       <c r="F348" t="s">
         <v>792</v>
@@ -11434,13 +11875,13 @@
         <v>425</v>
       </c>
       <c r="B349" t="s">
-        <v>1079</v>
+        <v>1192</v>
       </c>
       <c r="D349" t="s">
-        <v>294</v>
+        <v>1140</v>
       </c>
       <c r="E349" t="s">
-        <v>712</v>
+        <v>1244</v>
       </c>
       <c r="F349" t="s">
         <v>792</v>
@@ -11454,13 +11895,13 @@
         <v>425</v>
       </c>
       <c r="B350" t="s">
-        <v>1080</v>
+        <v>1045</v>
       </c>
       <c r="D350" t="s">
-        <v>295</v>
+        <v>260</v>
       </c>
       <c r="E350" t="s">
-        <v>713</v>
+        <v>678</v>
       </c>
       <c r="F350" t="s">
         <v>792</v>
@@ -11474,13 +11915,13 @@
         <v>425</v>
       </c>
       <c r="B351" t="s">
-        <v>1081</v>
+        <v>1046</v>
       </c>
       <c r="D351" t="s">
-        <v>296</v>
+        <v>261</v>
       </c>
       <c r="E351" t="s">
-        <v>714</v>
+        <v>679</v>
       </c>
       <c r="F351" t="s">
         <v>792</v>
@@ -11494,13 +11935,13 @@
         <v>425</v>
       </c>
       <c r="B352" t="s">
-        <v>1082</v>
+        <v>1047</v>
       </c>
       <c r="D352" t="s">
-        <v>297</v>
+        <v>262</v>
       </c>
       <c r="E352" t="s">
-        <v>715</v>
+        <v>680</v>
       </c>
       <c r="F352" t="s">
         <v>792</v>
@@ -11514,13 +11955,13 @@
         <v>425</v>
       </c>
       <c r="B353" t="s">
-        <v>1197</v>
+        <v>1288</v>
       </c>
       <c r="D353" t="s">
-        <v>1144</v>
+        <v>1289</v>
       </c>
       <c r="E353" t="s">
-        <v>1250</v>
+        <v>1290</v>
       </c>
       <c r="F353" t="s">
         <v>792</v>
@@ -11534,13 +11975,13 @@
         <v>425</v>
       </c>
       <c r="B354" t="s">
-        <v>1083</v>
+        <v>1048</v>
       </c>
       <c r="D354" t="s">
-        <v>298</v>
+        <v>263</v>
       </c>
       <c r="E354" t="s">
-        <v>716</v>
+        <v>681</v>
       </c>
       <c r="F354" t="s">
         <v>792</v>
@@ -11554,13 +11995,13 @@
         <v>425</v>
       </c>
       <c r="B355" t="s">
-        <v>1084</v>
+        <v>1049</v>
       </c>
       <c r="D355" t="s">
-        <v>299</v>
+        <v>264</v>
       </c>
       <c r="E355" t="s">
-        <v>717</v>
+        <v>682</v>
       </c>
       <c r="F355" t="s">
         <v>792</v>
@@ -11574,13 +12015,13 @@
         <v>425</v>
       </c>
       <c r="B356" t="s">
-        <v>1085</v>
+        <v>1474</v>
       </c>
       <c r="D356" t="s">
-        <v>300</v>
+        <v>1475</v>
       </c>
       <c r="E356" t="s">
-        <v>718</v>
+        <v>1476</v>
       </c>
       <c r="F356" t="s">
         <v>792</v>
@@ -11594,13 +12035,13 @@
         <v>425</v>
       </c>
       <c r="B357" t="s">
-        <v>1348</v>
+        <v>1050</v>
       </c>
       <c r="D357" t="s">
-        <v>1349</v>
+        <v>265</v>
       </c>
       <c r="E357" t="s">
-        <v>1350</v>
+        <v>683</v>
       </c>
       <c r="F357" t="s">
         <v>792</v>
@@ -11614,13 +12055,13 @@
         <v>425</v>
       </c>
       <c r="B358" t="s">
-        <v>1198</v>
+        <v>1051</v>
       </c>
       <c r="D358" t="s">
-        <v>1145</v>
+        <v>266</v>
       </c>
       <c r="E358" t="s">
-        <v>1251</v>
+        <v>684</v>
       </c>
       <c r="F358" t="s">
         <v>792</v>
@@ -11634,13 +12075,13 @@
         <v>425</v>
       </c>
       <c r="B359" t="s">
-        <v>1199</v>
+        <v>1052</v>
       </c>
       <c r="D359" t="s">
-        <v>1146</v>
+        <v>267</v>
       </c>
       <c r="E359" t="s">
-        <v>1252</v>
+        <v>685</v>
       </c>
       <c r="F359" t="s">
         <v>792</v>
@@ -11654,13 +12095,13 @@
         <v>425</v>
       </c>
       <c r="B360" t="s">
-        <v>1200</v>
+        <v>1053</v>
       </c>
       <c r="D360" t="s">
-        <v>1147</v>
+        <v>268</v>
       </c>
       <c r="E360" t="s">
-        <v>1253</v>
+        <v>686</v>
       </c>
       <c r="F360" t="s">
         <v>792</v>
@@ -11674,13 +12115,13 @@
         <v>425</v>
       </c>
       <c r="B361" t="s">
-        <v>1086</v>
+        <v>1054</v>
       </c>
       <c r="D361" t="s">
-        <v>301</v>
+        <v>269</v>
       </c>
       <c r="E361" t="s">
-        <v>719</v>
+        <v>687</v>
       </c>
       <c r="F361" t="s">
         <v>792</v>
@@ -11694,13 +12135,13 @@
         <v>425</v>
       </c>
       <c r="B362" t="s">
-        <v>1087</v>
+        <v>1055</v>
       </c>
       <c r="D362" t="s">
-        <v>302</v>
+        <v>270</v>
       </c>
       <c r="E362" t="s">
-        <v>720</v>
+        <v>688</v>
       </c>
       <c r="F362" t="s">
         <v>792</v>
@@ -11714,13 +12155,13 @@
         <v>425</v>
       </c>
       <c r="B363" t="s">
-        <v>1088</v>
+        <v>1056</v>
       </c>
       <c r="D363" t="s">
-        <v>303</v>
+        <v>271</v>
       </c>
       <c r="E363" t="s">
-        <v>721</v>
+        <v>689</v>
       </c>
       <c r="F363" t="s">
         <v>792</v>
@@ -11734,13 +12175,13 @@
         <v>425</v>
       </c>
       <c r="B364" t="s">
-        <v>1089</v>
+        <v>1057</v>
       </c>
       <c r="D364" t="s">
-        <v>304</v>
+        <v>272</v>
       </c>
       <c r="E364" t="s">
-        <v>722</v>
+        <v>690</v>
       </c>
       <c r="F364" t="s">
         <v>792</v>
@@ -11754,13 +12195,13 @@
         <v>425</v>
       </c>
       <c r="B365" t="s">
-        <v>1201</v>
+        <v>1477</v>
       </c>
       <c r="D365" t="s">
-        <v>1148</v>
+        <v>1478</v>
       </c>
       <c r="E365" t="s">
-        <v>1254</v>
+        <v>1479</v>
       </c>
       <c r="F365" t="s">
         <v>792</v>
@@ -11774,13 +12215,13 @@
         <v>425</v>
       </c>
       <c r="B366" t="s">
-        <v>1297</v>
+        <v>1058</v>
       </c>
       <c r="D366" t="s">
-        <v>1298</v>
+        <v>273</v>
       </c>
       <c r="E366" t="s">
-        <v>1299</v>
+        <v>691</v>
       </c>
       <c r="F366" t="s">
         <v>792</v>
@@ -11794,13 +12235,13 @@
         <v>425</v>
       </c>
       <c r="B367" t="s">
-        <v>1090</v>
+        <v>1059</v>
       </c>
       <c r="D367" t="s">
-        <v>305</v>
+        <v>274</v>
       </c>
       <c r="E367" t="s">
-        <v>723</v>
+        <v>692</v>
       </c>
       <c r="F367" t="s">
         <v>792</v>
@@ -11814,13 +12255,13 @@
         <v>425</v>
       </c>
       <c r="B368" t="s">
-        <v>1091</v>
+        <v>1060</v>
       </c>
       <c r="D368" t="s">
-        <v>306</v>
+        <v>275</v>
       </c>
       <c r="E368" t="s">
-        <v>724</v>
+        <v>693</v>
       </c>
       <c r="F368" t="s">
         <v>792</v>
@@ -11834,13 +12275,13 @@
         <v>425</v>
       </c>
       <c r="B369" t="s">
-        <v>1092</v>
+        <v>1061</v>
       </c>
       <c r="D369" t="s">
-        <v>307</v>
+        <v>276</v>
       </c>
       <c r="E369" t="s">
-        <v>725</v>
+        <v>694</v>
       </c>
       <c r="F369" t="s">
         <v>792</v>
@@ -11854,13 +12295,13 @@
         <v>425</v>
       </c>
       <c r="B370" t="s">
-        <v>1093</v>
+        <v>1062</v>
       </c>
       <c r="D370" t="s">
-        <v>308</v>
+        <v>277</v>
       </c>
       <c r="E370" t="s">
-        <v>726</v>
+        <v>695</v>
       </c>
       <c r="F370" t="s">
         <v>792</v>
@@ -11874,13 +12315,13 @@
         <v>425</v>
       </c>
       <c r="B371" t="s">
-        <v>1094</v>
+        <v>1063</v>
       </c>
       <c r="D371" t="s">
-        <v>309</v>
+        <v>278</v>
       </c>
       <c r="E371" t="s">
-        <v>727</v>
+        <v>696</v>
       </c>
       <c r="F371" t="s">
         <v>792</v>
@@ -11894,13 +12335,13 @@
         <v>425</v>
       </c>
       <c r="B372" t="s">
-        <v>1095</v>
+        <v>1064</v>
       </c>
       <c r="D372" t="s">
-        <v>310</v>
+        <v>279</v>
       </c>
       <c r="E372" t="s">
-        <v>728</v>
+        <v>697</v>
       </c>
       <c r="F372" t="s">
         <v>792</v>
@@ -11914,13 +12355,13 @@
         <v>425</v>
       </c>
       <c r="B373" t="s">
-        <v>1294</v>
+        <v>1065</v>
       </c>
       <c r="D373" t="s">
-        <v>1295</v>
+        <v>280</v>
       </c>
       <c r="E373" t="s">
-        <v>1296</v>
+        <v>698</v>
       </c>
       <c r="F373" t="s">
         <v>792</v>
@@ -11934,13 +12375,13 @@
         <v>425</v>
       </c>
       <c r="B374" t="s">
-        <v>1202</v>
+        <v>1066</v>
       </c>
       <c r="D374" t="s">
-        <v>1149</v>
+        <v>281</v>
       </c>
       <c r="E374" t="s">
-        <v>1255</v>
+        <v>699</v>
       </c>
       <c r="F374" t="s">
         <v>792</v>
@@ -11954,13 +12395,13 @@
         <v>425</v>
       </c>
       <c r="B375" t="s">
-        <v>1096</v>
+        <v>1067</v>
       </c>
       <c r="D375" t="s">
-        <v>311</v>
+        <v>282</v>
       </c>
       <c r="E375" t="s">
-        <v>729</v>
+        <v>700</v>
       </c>
       <c r="F375" t="s">
         <v>792</v>
@@ -11974,13 +12415,13 @@
         <v>425</v>
       </c>
       <c r="B376" t="s">
-        <v>1351</v>
+        <v>1068</v>
       </c>
       <c r="D376" t="s">
-        <v>1352</v>
+        <v>283</v>
       </c>
       <c r="E376" t="s">
-        <v>1353</v>
+        <v>701</v>
       </c>
       <c r="F376" t="s">
         <v>792</v>
@@ -11994,13 +12435,13 @@
         <v>425</v>
       </c>
       <c r="B377" t="s">
-        <v>1097</v>
+        <v>1069</v>
       </c>
       <c r="D377" t="s">
-        <v>312</v>
+        <v>284</v>
       </c>
       <c r="E377" t="s">
-        <v>730</v>
+        <v>702</v>
       </c>
       <c r="F377" t="s">
         <v>792</v>
@@ -12014,13 +12455,13 @@
         <v>425</v>
       </c>
       <c r="B378" t="s">
-        <v>1098</v>
+        <v>1480</v>
       </c>
       <c r="D378" t="s">
-        <v>313</v>
+        <v>1481</v>
       </c>
       <c r="E378" t="s">
-        <v>731</v>
+        <v>1482</v>
       </c>
       <c r="F378" t="s">
         <v>792</v>
@@ -12034,13 +12475,13 @@
         <v>425</v>
       </c>
       <c r="B379" t="s">
-        <v>1099</v>
+        <v>1070</v>
       </c>
       <c r="D379" t="s">
-        <v>314</v>
+        <v>285</v>
       </c>
       <c r="E379" t="s">
-        <v>732</v>
+        <v>703</v>
       </c>
       <c r="F379" t="s">
         <v>792</v>
@@ -12054,13 +12495,13 @@
         <v>425</v>
       </c>
       <c r="B380" t="s">
-        <v>1100</v>
+        <v>1342</v>
       </c>
       <c r="D380" t="s">
-        <v>315</v>
+        <v>1343</v>
       </c>
       <c r="E380" t="s">
-        <v>733</v>
+        <v>1344</v>
       </c>
       <c r="F380" t="s">
         <v>792</v>
@@ -12074,13 +12515,13 @@
         <v>425</v>
       </c>
       <c r="B381" t="s">
-        <v>1101</v>
+        <v>1071</v>
       </c>
       <c r="D381" t="s">
-        <v>316</v>
+        <v>286</v>
       </c>
       <c r="E381" t="s">
-        <v>734</v>
+        <v>704</v>
       </c>
       <c r="F381" t="s">
         <v>792</v>
@@ -12094,13 +12535,13 @@
         <v>425</v>
       </c>
       <c r="B382" t="s">
-        <v>1102</v>
+        <v>1072</v>
       </c>
       <c r="D382" t="s">
-        <v>317</v>
+        <v>287</v>
       </c>
       <c r="E382" t="s">
-        <v>735</v>
+        <v>705</v>
       </c>
       <c r="F382" t="s">
         <v>792</v>
@@ -12114,13 +12555,13 @@
         <v>425</v>
       </c>
       <c r="B383" t="s">
-        <v>1103</v>
+        <v>1193</v>
       </c>
       <c r="D383" t="s">
-        <v>318</v>
+        <v>1141</v>
       </c>
       <c r="E383" t="s">
-        <v>736</v>
+        <v>1245</v>
       </c>
       <c r="F383" t="s">
         <v>792</v>
@@ -12134,13 +12575,13 @@
         <v>425</v>
       </c>
       <c r="B384" t="s">
-        <v>1104</v>
+        <v>1073</v>
       </c>
       <c r="D384" t="s">
-        <v>319</v>
+        <v>288</v>
       </c>
       <c r="E384" t="s">
-        <v>737</v>
+        <v>706</v>
       </c>
       <c r="F384" t="s">
         <v>792</v>
@@ -12154,13 +12595,13 @@
         <v>425</v>
       </c>
       <c r="B385" t="s">
-        <v>1105</v>
+        <v>1074</v>
       </c>
       <c r="D385" t="s">
-        <v>320</v>
+        <v>289</v>
       </c>
       <c r="E385" t="s">
-        <v>738</v>
+        <v>707</v>
       </c>
       <c r="F385" t="s">
         <v>792</v>
@@ -12174,13 +12615,13 @@
         <v>425</v>
       </c>
       <c r="B386" t="s">
-        <v>1106</v>
+        <v>1075</v>
       </c>
       <c r="D386" t="s">
-        <v>321</v>
+        <v>290</v>
       </c>
       <c r="E386" t="s">
-        <v>739</v>
+        <v>708</v>
       </c>
       <c r="F386" t="s">
         <v>792</v>
@@ -12194,13 +12635,13 @@
         <v>425</v>
       </c>
       <c r="B387" t="s">
-        <v>1107</v>
+        <v>1076</v>
       </c>
       <c r="D387" t="s">
-        <v>322</v>
+        <v>291</v>
       </c>
       <c r="E387" t="s">
-        <v>740</v>
+        <v>709</v>
       </c>
       <c r="F387" t="s">
         <v>792</v>
@@ -12214,13 +12655,13 @@
         <v>425</v>
       </c>
       <c r="B388" t="s">
-        <v>374</v>
+        <v>1077</v>
       </c>
       <c r="D388" t="s">
-        <v>323</v>
+        <v>292</v>
       </c>
       <c r="E388" t="s">
-        <v>741</v>
+        <v>710</v>
       </c>
       <c r="F388" t="s">
         <v>792</v>
@@ -12234,13 +12675,13 @@
         <v>425</v>
       </c>
       <c r="B389" t="s">
-        <v>1203</v>
+        <v>1078</v>
       </c>
       <c r="D389" t="s">
-        <v>1150</v>
+        <v>293</v>
       </c>
       <c r="E389" t="s">
-        <v>1256</v>
+        <v>711</v>
       </c>
       <c r="F389" t="s">
         <v>792</v>
@@ -12254,13 +12695,13 @@
         <v>425</v>
       </c>
       <c r="B390" t="s">
-        <v>375</v>
+        <v>1194</v>
       </c>
       <c r="D390" t="s">
-        <v>324</v>
+        <v>1142</v>
       </c>
       <c r="E390" t="s">
-        <v>742</v>
+        <v>1246</v>
       </c>
       <c r="F390" t="s">
         <v>792</v>
@@ -12274,13 +12715,13 @@
         <v>425</v>
       </c>
       <c r="B391" t="s">
-        <v>376</v>
+        <v>1079</v>
       </c>
       <c r="D391" t="s">
-        <v>325</v>
+        <v>294</v>
       </c>
       <c r="E391" t="s">
-        <v>743</v>
+        <v>712</v>
       </c>
       <c r="F391" t="s">
         <v>792</v>
@@ -12294,13 +12735,13 @@
         <v>425</v>
       </c>
       <c r="B392" t="s">
-        <v>377</v>
+        <v>1080</v>
       </c>
       <c r="D392" t="s">
-        <v>326</v>
+        <v>295</v>
       </c>
       <c r="E392" t="s">
-        <v>744</v>
+        <v>713</v>
       </c>
       <c r="F392" t="s">
         <v>792</v>
@@ -12314,13 +12755,13 @@
         <v>425</v>
       </c>
       <c r="B393" t="s">
-        <v>378</v>
+        <v>1081</v>
       </c>
       <c r="D393" t="s">
-        <v>327</v>
+        <v>296</v>
       </c>
       <c r="E393" t="s">
-        <v>745</v>
+        <v>714</v>
       </c>
       <c r="F393" t="s">
         <v>792</v>
@@ -12334,13 +12775,13 @@
         <v>425</v>
       </c>
       <c r="B394" t="s">
-        <v>379</v>
+        <v>1082</v>
       </c>
       <c r="D394" t="s">
-        <v>328</v>
+        <v>297</v>
       </c>
       <c r="E394" t="s">
-        <v>746</v>
+        <v>715</v>
       </c>
       <c r="F394" t="s">
         <v>792</v>
@@ -12354,13 +12795,13 @@
         <v>425</v>
       </c>
       <c r="B395" t="s">
-        <v>380</v>
+        <v>1195</v>
       </c>
       <c r="D395" t="s">
-        <v>329</v>
+        <v>1143</v>
       </c>
       <c r="E395" t="s">
-        <v>747</v>
+        <v>1247</v>
       </c>
       <c r="F395" t="s">
         <v>792</v>
@@ -12374,13 +12815,13 @@
         <v>425</v>
       </c>
       <c r="B396" t="s">
-        <v>381</v>
+        <v>1083</v>
       </c>
       <c r="D396" t="s">
-        <v>330</v>
+        <v>298</v>
       </c>
       <c r="E396" t="s">
-        <v>748</v>
+        <v>716</v>
       </c>
       <c r="F396" t="s">
         <v>792</v>
@@ -12394,13 +12835,13 @@
         <v>425</v>
       </c>
       <c r="B397" t="s">
-        <v>382</v>
+        <v>1084</v>
       </c>
       <c r="D397" t="s">
-        <v>331</v>
+        <v>299</v>
       </c>
       <c r="E397" t="s">
-        <v>749</v>
+        <v>717</v>
       </c>
       <c r="F397" t="s">
         <v>792</v>
@@ -12414,13 +12855,13 @@
         <v>425</v>
       </c>
       <c r="B398" t="s">
-        <v>1354</v>
+        <v>1085</v>
       </c>
       <c r="D398" t="s">
-        <v>1355</v>
+        <v>300</v>
       </c>
       <c r="E398" t="s">
-        <v>1356</v>
+        <v>718</v>
       </c>
       <c r="F398" t="s">
         <v>792</v>
@@ -12434,13 +12875,13 @@
         <v>425</v>
       </c>
       <c r="B399" t="s">
-        <v>383</v>
+        <v>1345</v>
       </c>
       <c r="D399" t="s">
-        <v>332</v>
+        <v>1346</v>
       </c>
       <c r="E399" t="s">
-        <v>750</v>
+        <v>1347</v>
       </c>
       <c r="F399" t="s">
         <v>792</v>
@@ -12454,13 +12895,13 @@
         <v>425</v>
       </c>
       <c r="B400" t="s">
-        <v>1204</v>
+        <v>1196</v>
       </c>
       <c r="D400" t="s">
-        <v>1151</v>
+        <v>1144</v>
       </c>
       <c r="E400" t="s">
-        <v>1257</v>
+        <v>1248</v>
       </c>
       <c r="F400" t="s">
         <v>792</v>
@@ -12474,13 +12915,13 @@
         <v>425</v>
       </c>
       <c r="B401" t="s">
-        <v>384</v>
+        <v>1197</v>
       </c>
       <c r="D401" t="s">
-        <v>333</v>
+        <v>1145</v>
       </c>
       <c r="E401" t="s">
-        <v>751</v>
+        <v>1249</v>
       </c>
       <c r="F401" t="s">
         <v>792</v>
@@ -12494,13 +12935,13 @@
         <v>425</v>
       </c>
       <c r="B402" t="s">
-        <v>385</v>
+        <v>1483</v>
       </c>
       <c r="D402" t="s">
-        <v>334</v>
+        <v>1484</v>
       </c>
       <c r="E402" t="s">
-        <v>752</v>
+        <v>1485</v>
       </c>
       <c r="F402" t="s">
         <v>792</v>
@@ -12514,13 +12955,13 @@
         <v>425</v>
       </c>
       <c r="B403" t="s">
-        <v>386</v>
+        <v>1198</v>
       </c>
       <c r="D403" t="s">
-        <v>335</v>
+        <v>1146</v>
       </c>
       <c r="E403" t="s">
-        <v>753</v>
+        <v>1250</v>
       </c>
       <c r="F403" t="s">
         <v>792</v>
@@ -12534,13 +12975,13 @@
         <v>425</v>
       </c>
       <c r="B404" t="s">
-        <v>1205</v>
+        <v>1086</v>
       </c>
       <c r="D404" t="s">
-        <v>1152</v>
+        <v>301</v>
       </c>
       <c r="E404" t="s">
-        <v>1258</v>
+        <v>719</v>
       </c>
       <c r="F404" t="s">
         <v>792</v>
@@ -12554,13 +12995,13 @@
         <v>425</v>
       </c>
       <c r="B405" t="s">
-        <v>387</v>
+        <v>1087</v>
       </c>
       <c r="D405" t="s">
-        <v>336</v>
+        <v>302</v>
       </c>
       <c r="E405" t="s">
-        <v>754</v>
+        <v>720</v>
       </c>
       <c r="F405" t="s">
         <v>792</v>
@@ -12574,13 +13015,13 @@
         <v>425</v>
       </c>
       <c r="B406" t="s">
-        <v>388</v>
+        <v>1088</v>
       </c>
       <c r="D406" t="s">
-        <v>337</v>
+        <v>303</v>
       </c>
       <c r="E406" t="s">
-        <v>755</v>
+        <v>721</v>
       </c>
       <c r="F406" t="s">
         <v>792</v>
@@ -12594,13 +13035,13 @@
         <v>425</v>
       </c>
       <c r="B407" t="s">
-        <v>389</v>
+        <v>1089</v>
       </c>
       <c r="D407" t="s">
-        <v>338</v>
+        <v>304</v>
       </c>
       <c r="E407" t="s">
-        <v>756</v>
+        <v>722</v>
       </c>
       <c r="F407" t="s">
         <v>792</v>
@@ -12614,13 +13055,13 @@
         <v>425</v>
       </c>
       <c r="B408" t="s">
-        <v>390</v>
+        <v>1199</v>
       </c>
       <c r="D408" t="s">
-        <v>339</v>
+        <v>1147</v>
       </c>
       <c r="E408" t="s">
-        <v>757</v>
+        <v>1251</v>
       </c>
       <c r="F408" t="s">
         <v>792</v>
@@ -12634,13 +13075,13 @@
         <v>425</v>
       </c>
       <c r="B409" t="s">
-        <v>391</v>
+        <v>1294</v>
       </c>
       <c r="D409" t="s">
-        <v>340</v>
+        <v>1295</v>
       </c>
       <c r="E409" t="s">
-        <v>758</v>
+        <v>1296</v>
       </c>
       <c r="F409" t="s">
         <v>792</v>
@@ -12654,13 +13095,13 @@
         <v>425</v>
       </c>
       <c r="B410" t="s">
-        <v>392</v>
+        <v>1090</v>
       </c>
       <c r="D410" t="s">
-        <v>341</v>
+        <v>305</v>
       </c>
       <c r="E410" t="s">
-        <v>759</v>
+        <v>723</v>
       </c>
       <c r="F410" t="s">
         <v>792</v>
@@ -12674,13 +13115,13 @@
         <v>425</v>
       </c>
       <c r="B411" t="s">
-        <v>1206</v>
+        <v>1486</v>
       </c>
       <c r="D411" t="s">
-        <v>1153</v>
+        <v>1487</v>
       </c>
       <c r="E411" t="s">
-        <v>1259</v>
+        <v>1488</v>
       </c>
       <c r="F411" t="s">
         <v>792</v>
@@ -12694,13 +13135,13 @@
         <v>425</v>
       </c>
       <c r="B412" t="s">
-        <v>393</v>
+        <v>1091</v>
       </c>
       <c r="D412" t="s">
-        <v>342</v>
+        <v>306</v>
       </c>
       <c r="E412" t="s">
-        <v>760</v>
+        <v>724</v>
       </c>
       <c r="F412" t="s">
         <v>792</v>
@@ -12714,13 +13155,13 @@
         <v>425</v>
       </c>
       <c r="B413" t="s">
-        <v>394</v>
+        <v>1092</v>
       </c>
       <c r="D413" t="s">
-        <v>343</v>
+        <v>307</v>
       </c>
       <c r="E413" t="s">
-        <v>761</v>
+        <v>725</v>
       </c>
       <c r="F413" t="s">
         <v>792</v>
@@ -12734,13 +13175,13 @@
         <v>425</v>
       </c>
       <c r="B414" t="s">
-        <v>395</v>
+        <v>1093</v>
       </c>
       <c r="D414" t="s">
-        <v>344</v>
+        <v>308</v>
       </c>
       <c r="E414" t="s">
-        <v>762</v>
+        <v>726</v>
       </c>
       <c r="F414" t="s">
         <v>792</v>
@@ -12754,13 +13195,13 @@
         <v>425</v>
       </c>
       <c r="B415" t="s">
-        <v>1207</v>
+        <v>1094</v>
       </c>
       <c r="D415" t="s">
-        <v>1154</v>
+        <v>309</v>
       </c>
       <c r="E415" t="s">
-        <v>1260</v>
+        <v>727</v>
       </c>
       <c r="F415" t="s">
         <v>792</v>
@@ -12774,13 +13215,13 @@
         <v>425</v>
       </c>
       <c r="B416" t="s">
-        <v>396</v>
+        <v>1095</v>
       </c>
       <c r="D416" t="s">
-        <v>345</v>
+        <v>310</v>
       </c>
       <c r="E416" t="s">
-        <v>763</v>
+        <v>728</v>
       </c>
       <c r="F416" t="s">
         <v>792</v>
@@ -12794,13 +13235,13 @@
         <v>425</v>
       </c>
       <c r="B417" t="s">
-        <v>1208</v>
+        <v>1291</v>
       </c>
       <c r="D417" t="s">
-        <v>1155</v>
+        <v>1292</v>
       </c>
       <c r="E417" t="s">
-        <v>1261</v>
+        <v>1293</v>
       </c>
       <c r="F417" t="s">
         <v>792</v>
@@ -12814,13 +13255,13 @@
         <v>425</v>
       </c>
       <c r="B418" t="s">
-        <v>397</v>
+        <v>1200</v>
       </c>
       <c r="D418" t="s">
-        <v>346</v>
+        <v>1148</v>
       </c>
       <c r="E418" t="s">
-        <v>764</v>
+        <v>1252</v>
       </c>
       <c r="F418" t="s">
         <v>792</v>
@@ -12834,13 +13275,13 @@
         <v>425</v>
       </c>
       <c r="B419" t="s">
-        <v>398</v>
+        <v>1096</v>
       </c>
       <c r="D419" t="s">
-        <v>347</v>
+        <v>311</v>
       </c>
       <c r="E419" t="s">
-        <v>765</v>
+        <v>729</v>
       </c>
       <c r="F419" t="s">
         <v>792</v>
@@ -12854,13 +13295,13 @@
         <v>425</v>
       </c>
       <c r="B420" t="s">
-        <v>399</v>
+        <v>1348</v>
       </c>
       <c r="D420" t="s">
-        <v>348</v>
+        <v>1349</v>
       </c>
       <c r="E420" t="s">
-        <v>766</v>
+        <v>1350</v>
       </c>
       <c r="F420" t="s">
         <v>792</v>
@@ -12874,13 +13315,13 @@
         <v>425</v>
       </c>
       <c r="B421" t="s">
-        <v>400</v>
+        <v>1097</v>
       </c>
       <c r="D421" t="s">
-        <v>349</v>
+        <v>312</v>
       </c>
       <c r="E421" t="s">
-        <v>767</v>
+        <v>730</v>
       </c>
       <c r="F421" t="s">
         <v>792</v>
@@ -12894,13 +13335,13 @@
         <v>425</v>
       </c>
       <c r="B422" t="s">
-        <v>1209</v>
+        <v>1098</v>
       </c>
       <c r="D422" t="s">
-        <v>1156</v>
+        <v>313</v>
       </c>
       <c r="E422" t="s">
-        <v>1262</v>
+        <v>731</v>
       </c>
       <c r="F422" t="s">
         <v>792</v>
@@ -12914,13 +13355,13 @@
         <v>425</v>
       </c>
       <c r="B423" t="s">
-        <v>1357</v>
+        <v>1099</v>
       </c>
       <c r="D423" t="s">
-        <v>1358</v>
+        <v>314</v>
       </c>
       <c r="E423" t="s">
-        <v>1359</v>
+        <v>732</v>
       </c>
       <c r="F423" t="s">
         <v>792</v>
@@ -12934,13 +13375,13 @@
         <v>425</v>
       </c>
       <c r="B424" t="s">
-        <v>401</v>
+        <v>1100</v>
       </c>
       <c r="D424" t="s">
-        <v>350</v>
+        <v>315</v>
       </c>
       <c r="E424" t="s">
-        <v>768</v>
+        <v>733</v>
       </c>
       <c r="F424" t="s">
         <v>792</v>
@@ -12954,13 +13395,13 @@
         <v>425</v>
       </c>
       <c r="B425" t="s">
-        <v>1360</v>
+        <v>1101</v>
       </c>
       <c r="D425" t="s">
-        <v>1361</v>
+        <v>316</v>
       </c>
       <c r="E425" t="s">
-        <v>1362</v>
+        <v>734</v>
       </c>
       <c r="F425" t="s">
         <v>792</v>
@@ -12974,13 +13415,13 @@
         <v>425</v>
       </c>
       <c r="B426" t="s">
-        <v>402</v>
+        <v>1102</v>
       </c>
       <c r="D426" t="s">
-        <v>351</v>
+        <v>317</v>
       </c>
       <c r="E426" t="s">
-        <v>769</v>
+        <v>735</v>
       </c>
       <c r="F426" t="s">
         <v>792</v>
@@ -12994,13 +13435,13 @@
         <v>425</v>
       </c>
       <c r="B427" t="s">
-        <v>403</v>
+        <v>1103</v>
       </c>
       <c r="D427" t="s">
-        <v>352</v>
+        <v>318</v>
       </c>
       <c r="E427" t="s">
-        <v>770</v>
+        <v>736</v>
       </c>
       <c r="F427" t="s">
         <v>792</v>
@@ -13014,13 +13455,13 @@
         <v>425</v>
       </c>
       <c r="B428" t="s">
-        <v>404</v>
+        <v>1104</v>
       </c>
       <c r="D428" t="s">
-        <v>353</v>
+        <v>319</v>
       </c>
       <c r="E428" t="s">
-        <v>771</v>
+        <v>737</v>
       </c>
       <c r="F428" t="s">
         <v>792</v>
@@ -13034,13 +13475,13 @@
         <v>425</v>
       </c>
       <c r="B429" t="s">
-        <v>405</v>
+        <v>1489</v>
       </c>
       <c r="D429" t="s">
-        <v>354</v>
+        <v>1490</v>
       </c>
       <c r="E429" t="s">
-        <v>772</v>
+        <v>1491</v>
       </c>
       <c r="F429" t="s">
         <v>792</v>
@@ -13054,13 +13495,13 @@
         <v>425</v>
       </c>
       <c r="B430" t="s">
-        <v>406</v>
+        <v>1105</v>
       </c>
       <c r="D430" t="s">
-        <v>355</v>
+        <v>320</v>
       </c>
       <c r="E430" t="s">
-        <v>773</v>
+        <v>738</v>
       </c>
       <c r="F430" t="s">
         <v>792</v>
@@ -13074,13 +13515,13 @@
         <v>425</v>
       </c>
       <c r="B431" t="s">
-        <v>407</v>
+        <v>1106</v>
       </c>
       <c r="D431" t="s">
-        <v>356</v>
+        <v>321</v>
       </c>
       <c r="E431" t="s">
-        <v>774</v>
+        <v>739</v>
       </c>
       <c r="F431" t="s">
         <v>792</v>
@@ -13094,13 +13535,13 @@
         <v>425</v>
       </c>
       <c r="B432" t="s">
-        <v>1210</v>
+        <v>1107</v>
       </c>
       <c r="D432" t="s">
-        <v>1157</v>
+        <v>322</v>
       </c>
       <c r="E432" t="s">
-        <v>1263</v>
+        <v>740</v>
       </c>
       <c r="F432" t="s">
         <v>792</v>
@@ -13114,13 +13555,13 @@
         <v>425</v>
       </c>
       <c r="B433" t="s">
-        <v>408</v>
+        <v>374</v>
       </c>
       <c r="D433" t="s">
-        <v>357</v>
+        <v>323</v>
       </c>
       <c r="E433" t="s">
-        <v>775</v>
+        <v>741</v>
       </c>
       <c r="F433" t="s">
         <v>792</v>
@@ -13134,13 +13575,13 @@
         <v>425</v>
       </c>
       <c r="B434" t="s">
-        <v>409</v>
+        <v>1201</v>
       </c>
       <c r="D434" t="s">
-        <v>358</v>
+        <v>1149</v>
       </c>
       <c r="E434" t="s">
-        <v>776</v>
+        <v>1253</v>
       </c>
       <c r="F434" t="s">
         <v>792</v>
@@ -13154,13 +13595,13 @@
         <v>425</v>
       </c>
       <c r="B435" t="s">
-        <v>410</v>
+        <v>375</v>
       </c>
       <c r="D435" t="s">
-        <v>359</v>
+        <v>324</v>
       </c>
       <c r="E435" t="s">
-        <v>777</v>
+        <v>742</v>
       </c>
       <c r="F435" t="s">
         <v>792</v>
@@ -13174,13 +13615,13 @@
         <v>425</v>
       </c>
       <c r="B436" t="s">
-        <v>411</v>
+        <v>1492</v>
       </c>
       <c r="D436" t="s">
-        <v>360</v>
+        <v>1493</v>
       </c>
       <c r="E436" t="s">
-        <v>778</v>
+        <v>1494</v>
       </c>
       <c r="F436" t="s">
         <v>792</v>
@@ -13194,13 +13635,13 @@
         <v>425</v>
       </c>
       <c r="B437" t="s">
-        <v>412</v>
+        <v>376</v>
       </c>
       <c r="D437" t="s">
-        <v>361</v>
+        <v>325</v>
       </c>
       <c r="E437" t="s">
-        <v>779</v>
+        <v>743</v>
       </c>
       <c r="F437" t="s">
         <v>792</v>
@@ -13214,13 +13655,13 @@
         <v>425</v>
       </c>
       <c r="B438" t="s">
-        <v>413</v>
+        <v>377</v>
       </c>
       <c r="D438" t="s">
-        <v>362</v>
+        <v>326</v>
       </c>
       <c r="E438" t="s">
-        <v>780</v>
+        <v>744</v>
       </c>
       <c r="F438" t="s">
         <v>792</v>
@@ -13234,13 +13675,13 @@
         <v>425</v>
       </c>
       <c r="B439" t="s">
-        <v>414</v>
+        <v>378</v>
       </c>
       <c r="D439" t="s">
-        <v>363</v>
+        <v>327</v>
       </c>
       <c r="E439" t="s">
-        <v>781</v>
+        <v>745</v>
       </c>
       <c r="F439" t="s">
         <v>792</v>
@@ -13254,13 +13695,13 @@
         <v>425</v>
       </c>
       <c r="B440" t="s">
-        <v>415</v>
+        <v>379</v>
       </c>
       <c r="D440" t="s">
-        <v>364</v>
+        <v>328</v>
       </c>
       <c r="E440" t="s">
-        <v>782</v>
+        <v>746</v>
       </c>
       <c r="F440" t="s">
         <v>792</v>
@@ -13274,13 +13715,13 @@
         <v>425</v>
       </c>
       <c r="B441" t="s">
-        <v>416</v>
+        <v>380</v>
       </c>
       <c r="D441" t="s">
-        <v>365</v>
+        <v>329</v>
       </c>
       <c r="E441" t="s">
-        <v>783</v>
+        <v>747</v>
       </c>
       <c r="F441" t="s">
         <v>792</v>
@@ -13294,13 +13735,13 @@
         <v>425</v>
       </c>
       <c r="B442" t="s">
-        <v>1211</v>
+        <v>381</v>
       </c>
       <c r="D442" t="s">
-        <v>1158</v>
+        <v>330</v>
       </c>
       <c r="E442" t="s">
-        <v>1264</v>
+        <v>748</v>
       </c>
       <c r="F442" t="s">
         <v>792</v>
@@ -13314,13 +13755,13 @@
         <v>425</v>
       </c>
       <c r="B443" t="s">
-        <v>417</v>
+        <v>382</v>
       </c>
       <c r="D443" t="s">
-        <v>366</v>
+        <v>331</v>
       </c>
       <c r="E443" t="s">
-        <v>784</v>
+        <v>749</v>
       </c>
       <c r="F443" t="s">
         <v>792</v>
@@ -13334,13 +13775,13 @@
         <v>425</v>
       </c>
       <c r="B444" t="s">
-        <v>418</v>
+        <v>1351</v>
       </c>
       <c r="D444" t="s">
-        <v>367</v>
+        <v>1352</v>
       </c>
       <c r="E444" t="s">
-        <v>785</v>
+        <v>1353</v>
       </c>
       <c r="F444" t="s">
         <v>792</v>
@@ -13354,13 +13795,13 @@
         <v>425</v>
       </c>
       <c r="B445" t="s">
-        <v>1212</v>
+        <v>383</v>
       </c>
       <c r="D445" t="s">
-        <v>1159</v>
+        <v>332</v>
       </c>
       <c r="E445" t="s">
-        <v>1265</v>
+        <v>750</v>
       </c>
       <c r="F445" t="s">
         <v>792</v>
@@ -13374,13 +13815,13 @@
         <v>425</v>
       </c>
       <c r="B446" t="s">
-        <v>419</v>
+        <v>1202</v>
       </c>
       <c r="D446" t="s">
-        <v>368</v>
+        <v>1150</v>
       </c>
       <c r="E446" t="s">
-        <v>786</v>
+        <v>1254</v>
       </c>
       <c r="F446" t="s">
         <v>792</v>
@@ -13394,13 +13835,13 @@
         <v>425</v>
       </c>
       <c r="B447" t="s">
-        <v>1363</v>
+        <v>384</v>
       </c>
       <c r="D447" t="s">
-        <v>1364</v>
+        <v>333</v>
       </c>
       <c r="E447" t="s">
-        <v>1365</v>
+        <v>751</v>
       </c>
       <c r="F447" t="s">
         <v>792</v>
@@ -13414,13 +13855,13 @@
         <v>425</v>
       </c>
       <c r="B448" t="s">
-        <v>420</v>
+        <v>385</v>
       </c>
       <c r="D448" t="s">
-        <v>369</v>
+        <v>334</v>
       </c>
       <c r="E448" t="s">
-        <v>787</v>
+        <v>752</v>
       </c>
       <c r="F448" t="s">
         <v>792</v>
@@ -13434,13 +13875,13 @@
         <v>425</v>
       </c>
       <c r="B449" t="s">
-        <v>421</v>
+        <v>386</v>
       </c>
       <c r="D449" t="s">
-        <v>370</v>
+        <v>335</v>
       </c>
       <c r="E449" t="s">
-        <v>788</v>
+        <v>753</v>
       </c>
       <c r="F449" t="s">
         <v>792</v>
@@ -13454,13 +13895,13 @@
         <v>425</v>
       </c>
       <c r="B450" t="s">
-        <v>422</v>
+        <v>1203</v>
       </c>
       <c r="D450" t="s">
-        <v>371</v>
+        <v>1151</v>
       </c>
       <c r="E450" t="s">
-        <v>789</v>
+        <v>1255</v>
       </c>
       <c r="F450" t="s">
         <v>792</v>
@@ -13474,13 +13915,13 @@
         <v>425</v>
       </c>
       <c r="B451" t="s">
-        <v>423</v>
+        <v>387</v>
       </c>
       <c r="D451" t="s">
-        <v>372</v>
+        <v>336</v>
       </c>
       <c r="E451" t="s">
-        <v>790</v>
+        <v>754</v>
       </c>
       <c r="F451" t="s">
         <v>792</v>
@@ -13494,13 +13935,13 @@
         <v>425</v>
       </c>
       <c r="B452" t="s">
-        <v>424</v>
+        <v>388</v>
       </c>
       <c r="D452" t="s">
-        <v>373</v>
+        <v>337</v>
       </c>
       <c r="E452" t="s">
-        <v>791</v>
+        <v>755</v>
       </c>
       <c r="F452" t="s">
         <v>792</v>
@@ -13514,18 +13955,998 @@
         <v>425</v>
       </c>
       <c r="B453" t="s">
-        <v>1213</v>
+        <v>389</v>
       </c>
       <c r="D453" t="s">
-        <v>1160</v>
+        <v>338</v>
       </c>
       <c r="E453" t="s">
-        <v>1266</v>
+        <v>756</v>
       </c>
       <c r="F453" t="s">
         <v>792</v>
       </c>
       <c r="G453" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="454" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A454" t="s">
+        <v>425</v>
+      </c>
+      <c r="B454" t="s">
+        <v>1510</v>
+      </c>
+      <c r="D454" t="s">
+        <v>1511</v>
+      </c>
+      <c r="E454" t="s">
+        <v>1512</v>
+      </c>
+      <c r="F454" t="s">
+        <v>792</v>
+      </c>
+      <c r="G454" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="455" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A455" t="s">
+        <v>425</v>
+      </c>
+      <c r="B455" t="s">
+        <v>390</v>
+      </c>
+      <c r="D455" t="s">
+        <v>339</v>
+      </c>
+      <c r="E455" t="s">
+        <v>757</v>
+      </c>
+      <c r="F455" t="s">
+        <v>792</v>
+      </c>
+      <c r="G455" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="456" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A456" t="s">
+        <v>425</v>
+      </c>
+      <c r="B456" t="s">
+        <v>391</v>
+      </c>
+      <c r="D456" t="s">
+        <v>340</v>
+      </c>
+      <c r="E456" t="s">
+        <v>758</v>
+      </c>
+      <c r="F456" t="s">
+        <v>792</v>
+      </c>
+      <c r="G456" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="457" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A457" t="s">
+        <v>425</v>
+      </c>
+      <c r="B457" t="s">
+        <v>392</v>
+      </c>
+      <c r="D457" t="s">
+        <v>341</v>
+      </c>
+      <c r="E457" t="s">
+        <v>759</v>
+      </c>
+      <c r="F457" t="s">
+        <v>792</v>
+      </c>
+      <c r="G457" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="458" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A458" t="s">
+        <v>425</v>
+      </c>
+      <c r="B458" t="s">
+        <v>1204</v>
+      </c>
+      <c r="D458" t="s">
+        <v>1152</v>
+      </c>
+      <c r="E458" t="s">
+        <v>1256</v>
+      </c>
+      <c r="F458" t="s">
+        <v>792</v>
+      </c>
+      <c r="G458" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="459" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A459" t="s">
+        <v>425</v>
+      </c>
+      <c r="B459" t="s">
+        <v>393</v>
+      </c>
+      <c r="D459" t="s">
+        <v>342</v>
+      </c>
+      <c r="E459" t="s">
+        <v>760</v>
+      </c>
+      <c r="F459" t="s">
+        <v>792</v>
+      </c>
+      <c r="G459" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="460" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A460" t="s">
+        <v>425</v>
+      </c>
+      <c r="B460" t="s">
+        <v>394</v>
+      </c>
+      <c r="D460" t="s">
+        <v>343</v>
+      </c>
+      <c r="E460" t="s">
+        <v>761</v>
+      </c>
+      <c r="F460" t="s">
+        <v>792</v>
+      </c>
+      <c r="G460" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="461" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A461" t="s">
+        <v>425</v>
+      </c>
+      <c r="B461" t="s">
+        <v>395</v>
+      </c>
+      <c r="D461" t="s">
+        <v>344</v>
+      </c>
+      <c r="E461" t="s">
+        <v>762</v>
+      </c>
+      <c r="F461" t="s">
+        <v>792</v>
+      </c>
+      <c r="G461" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="462" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A462" t="s">
+        <v>425</v>
+      </c>
+      <c r="B462" t="s">
+        <v>1205</v>
+      </c>
+      <c r="D462" t="s">
+        <v>1153</v>
+      </c>
+      <c r="E462" t="s">
+        <v>1257</v>
+      </c>
+      <c r="F462" t="s">
+        <v>792</v>
+      </c>
+      <c r="G462" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="463" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A463" t="s">
+        <v>425</v>
+      </c>
+      <c r="B463" t="s">
+        <v>396</v>
+      </c>
+      <c r="D463" t="s">
+        <v>345</v>
+      </c>
+      <c r="E463" t="s">
+        <v>763</v>
+      </c>
+      <c r="F463" t="s">
+        <v>792</v>
+      </c>
+      <c r="G463" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="464" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A464" t="s">
+        <v>425</v>
+      </c>
+      <c r="B464" t="s">
+        <v>1206</v>
+      </c>
+      <c r="D464" t="s">
+        <v>1154</v>
+      </c>
+      <c r="E464" t="s">
+        <v>1258</v>
+      </c>
+      <c r="F464" t="s">
+        <v>792</v>
+      </c>
+      <c r="G464" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="465" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A465" t="s">
+        <v>425</v>
+      </c>
+      <c r="B465" t="s">
+        <v>397</v>
+      </c>
+      <c r="D465" t="s">
+        <v>346</v>
+      </c>
+      <c r="E465" t="s">
+        <v>764</v>
+      </c>
+      <c r="F465" t="s">
+        <v>792</v>
+      </c>
+      <c r="G465" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="466" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A466" t="s">
+        <v>425</v>
+      </c>
+      <c r="B466" t="s">
+        <v>398</v>
+      </c>
+      <c r="D466" t="s">
+        <v>347</v>
+      </c>
+      <c r="E466" t="s">
+        <v>765</v>
+      </c>
+      <c r="F466" t="s">
+        <v>792</v>
+      </c>
+      <c r="G466" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="467" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A467" t="s">
+        <v>425</v>
+      </c>
+      <c r="B467" t="s">
+        <v>399</v>
+      </c>
+      <c r="D467" t="s">
+        <v>348</v>
+      </c>
+      <c r="E467" t="s">
+        <v>766</v>
+      </c>
+      <c r="F467" t="s">
+        <v>792</v>
+      </c>
+      <c r="G467" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="468" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A468" t="s">
+        <v>425</v>
+      </c>
+      <c r="B468" t="s">
+        <v>400</v>
+      </c>
+      <c r="D468" t="s">
+        <v>349</v>
+      </c>
+      <c r="E468" t="s">
+        <v>767</v>
+      </c>
+      <c r="F468" t="s">
+        <v>792</v>
+      </c>
+      <c r="G468" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="469" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A469" t="s">
+        <v>425</v>
+      </c>
+      <c r="B469" t="s">
+        <v>1207</v>
+      </c>
+      <c r="D469" t="s">
+        <v>1155</v>
+      </c>
+      <c r="E469" t="s">
+        <v>1259</v>
+      </c>
+      <c r="F469" t="s">
+        <v>792</v>
+      </c>
+      <c r="G469" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="470" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A470" t="s">
+        <v>425</v>
+      </c>
+      <c r="B470" t="s">
+        <v>1495</v>
+      </c>
+      <c r="D470" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E470" t="s">
+        <v>1497</v>
+      </c>
+      <c r="F470" t="s">
+        <v>792</v>
+      </c>
+      <c r="G470" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="471" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A471" t="s">
+        <v>425</v>
+      </c>
+      <c r="B471" t="s">
+        <v>1354</v>
+      </c>
+      <c r="D471" t="s">
+        <v>1355</v>
+      </c>
+      <c r="E471" t="s">
+        <v>1356</v>
+      </c>
+      <c r="F471" t="s">
+        <v>792</v>
+      </c>
+      <c r="G471" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="472" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A472" t="s">
+        <v>425</v>
+      </c>
+      <c r="B472" t="s">
+        <v>401</v>
+      </c>
+      <c r="D472" t="s">
+        <v>350</v>
+      </c>
+      <c r="E472" t="s">
+        <v>768</v>
+      </c>
+      <c r="F472" t="s">
+        <v>792</v>
+      </c>
+      <c r="G472" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="473" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A473" t="s">
+        <v>425</v>
+      </c>
+      <c r="B473" t="s">
+        <v>1357</v>
+      </c>
+      <c r="D473" t="s">
+        <v>1358</v>
+      </c>
+      <c r="E473" t="s">
+        <v>1359</v>
+      </c>
+      <c r="F473" t="s">
+        <v>792</v>
+      </c>
+      <c r="G473" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="474" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A474" t="s">
+        <v>425</v>
+      </c>
+      <c r="B474" t="s">
+        <v>402</v>
+      </c>
+      <c r="D474" t="s">
+        <v>351</v>
+      </c>
+      <c r="E474" t="s">
+        <v>769</v>
+      </c>
+      <c r="F474" t="s">
+        <v>792</v>
+      </c>
+      <c r="G474" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="475" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A475" t="s">
+        <v>425</v>
+      </c>
+      <c r="B475" t="s">
+        <v>403</v>
+      </c>
+      <c r="D475" t="s">
+        <v>352</v>
+      </c>
+      <c r="E475" t="s">
+        <v>770</v>
+      </c>
+      <c r="F475" t="s">
+        <v>792</v>
+      </c>
+      <c r="G475" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="476" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A476" t="s">
+        <v>425</v>
+      </c>
+      <c r="B476" t="s">
+        <v>404</v>
+      </c>
+      <c r="D476" t="s">
+        <v>353</v>
+      </c>
+      <c r="E476" t="s">
+        <v>771</v>
+      </c>
+      <c r="F476" t="s">
+        <v>792</v>
+      </c>
+      <c r="G476" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="477" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A477" t="s">
+        <v>425</v>
+      </c>
+      <c r="B477" t="s">
+        <v>405</v>
+      </c>
+      <c r="D477" t="s">
+        <v>354</v>
+      </c>
+      <c r="E477" t="s">
+        <v>772</v>
+      </c>
+      <c r="F477" t="s">
+        <v>792</v>
+      </c>
+      <c r="G477" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="478" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A478" t="s">
+        <v>425</v>
+      </c>
+      <c r="B478" t="s">
+        <v>406</v>
+      </c>
+      <c r="D478" t="s">
+        <v>355</v>
+      </c>
+      <c r="E478" t="s">
+        <v>773</v>
+      </c>
+      <c r="F478" t="s">
+        <v>792</v>
+      </c>
+      <c r="G478" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="479" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A479" t="s">
+        <v>425</v>
+      </c>
+      <c r="B479" t="s">
+        <v>407</v>
+      </c>
+      <c r="D479" t="s">
+        <v>356</v>
+      </c>
+      <c r="E479" t="s">
+        <v>774</v>
+      </c>
+      <c r="F479" t="s">
+        <v>792</v>
+      </c>
+      <c r="G479" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="480" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A480" t="s">
+        <v>425</v>
+      </c>
+      <c r="B480" t="s">
+        <v>1208</v>
+      </c>
+      <c r="D480" t="s">
+        <v>1156</v>
+      </c>
+      <c r="E480" t="s">
+        <v>1260</v>
+      </c>
+      <c r="F480" t="s">
+        <v>792</v>
+      </c>
+      <c r="G480" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="481" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A481" t="s">
+        <v>425</v>
+      </c>
+      <c r="B481" t="s">
+        <v>1507</v>
+      </c>
+      <c r="D481" t="s">
+        <v>1508</v>
+      </c>
+      <c r="E481" t="s">
+        <v>1509</v>
+      </c>
+      <c r="F481" t="s">
+        <v>792</v>
+      </c>
+      <c r="G481" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="482" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A482" t="s">
+        <v>425</v>
+      </c>
+      <c r="B482" t="s">
+        <v>408</v>
+      </c>
+      <c r="D482" t="s">
+        <v>357</v>
+      </c>
+      <c r="E482" t="s">
+        <v>775</v>
+      </c>
+      <c r="F482" t="s">
+        <v>792</v>
+      </c>
+      <c r="G482" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="483" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A483" t="s">
+        <v>425</v>
+      </c>
+      <c r="B483" t="s">
+        <v>409</v>
+      </c>
+      <c r="D483" t="s">
+        <v>358</v>
+      </c>
+      <c r="E483" t="s">
+        <v>776</v>
+      </c>
+      <c r="F483" t="s">
+        <v>792</v>
+      </c>
+      <c r="G483" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="484" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A484" t="s">
+        <v>425</v>
+      </c>
+      <c r="B484" t="s">
+        <v>410</v>
+      </c>
+      <c r="D484" t="s">
+        <v>359</v>
+      </c>
+      <c r="E484" t="s">
+        <v>777</v>
+      </c>
+      <c r="F484" t="s">
+        <v>792</v>
+      </c>
+      <c r="G484" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="485" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A485" t="s">
+        <v>425</v>
+      </c>
+      <c r="B485" t="s">
+        <v>411</v>
+      </c>
+      <c r="D485" t="s">
+        <v>360</v>
+      </c>
+      <c r="E485" t="s">
+        <v>778</v>
+      </c>
+      <c r="F485" t="s">
+        <v>792</v>
+      </c>
+      <c r="G485" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="486" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A486" t="s">
+        <v>425</v>
+      </c>
+      <c r="B486" t="s">
+        <v>412</v>
+      </c>
+      <c r="D486" t="s">
+        <v>361</v>
+      </c>
+      <c r="E486" t="s">
+        <v>779</v>
+      </c>
+      <c r="F486" t="s">
+        <v>792</v>
+      </c>
+      <c r="G486" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="487" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A487" t="s">
+        <v>425</v>
+      </c>
+      <c r="B487" t="s">
+        <v>413</v>
+      </c>
+      <c r="D487" t="s">
+        <v>362</v>
+      </c>
+      <c r="E487" t="s">
+        <v>780</v>
+      </c>
+      <c r="F487" t="s">
+        <v>792</v>
+      </c>
+      <c r="G487" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="488" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A488" t="s">
+        <v>425</v>
+      </c>
+      <c r="B488" t="s">
+        <v>414</v>
+      </c>
+      <c r="D488" t="s">
+        <v>363</v>
+      </c>
+      <c r="E488" t="s">
+        <v>781</v>
+      </c>
+      <c r="F488" t="s">
+        <v>792</v>
+      </c>
+      <c r="G488" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="489" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A489" t="s">
+        <v>425</v>
+      </c>
+      <c r="B489" t="s">
+        <v>415</v>
+      </c>
+      <c r="D489" t="s">
+        <v>364</v>
+      </c>
+      <c r="E489" t="s">
+        <v>782</v>
+      </c>
+      <c r="F489" t="s">
+        <v>792</v>
+      </c>
+      <c r="G489" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="490" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A490" t="s">
+        <v>425</v>
+      </c>
+      <c r="B490" t="s">
+        <v>416</v>
+      </c>
+      <c r="D490" t="s">
+        <v>365</v>
+      </c>
+      <c r="E490" t="s">
+        <v>783</v>
+      </c>
+      <c r="F490" t="s">
+        <v>792</v>
+      </c>
+      <c r="G490" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="491" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A491" t="s">
+        <v>425</v>
+      </c>
+      <c r="B491" t="s">
+        <v>1209</v>
+      </c>
+      <c r="D491" t="s">
+        <v>1157</v>
+      </c>
+      <c r="E491" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F491" t="s">
+        <v>792</v>
+      </c>
+      <c r="G491" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="492" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A492" t="s">
+        <v>425</v>
+      </c>
+      <c r="B492" t="s">
+        <v>417</v>
+      </c>
+      <c r="D492" t="s">
+        <v>366</v>
+      </c>
+      <c r="E492" t="s">
+        <v>784</v>
+      </c>
+      <c r="F492" t="s">
+        <v>792</v>
+      </c>
+      <c r="G492" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="493" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A493" t="s">
+        <v>425</v>
+      </c>
+      <c r="B493" t="s">
+        <v>418</v>
+      </c>
+      <c r="D493" t="s">
+        <v>367</v>
+      </c>
+      <c r="E493" t="s">
+        <v>785</v>
+      </c>
+      <c r="F493" t="s">
+        <v>792</v>
+      </c>
+      <c r="G493" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="494" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A494" t="s">
+        <v>425</v>
+      </c>
+      <c r="B494" t="s">
+        <v>1210</v>
+      </c>
+      <c r="D494" t="s">
+        <v>1158</v>
+      </c>
+      <c r="E494" t="s">
+        <v>1262</v>
+      </c>
+      <c r="F494" t="s">
+        <v>792</v>
+      </c>
+      <c r="G494" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="495" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A495" t="s">
+        <v>425</v>
+      </c>
+      <c r="B495" t="s">
+        <v>419</v>
+      </c>
+      <c r="D495" t="s">
+        <v>368</v>
+      </c>
+      <c r="E495" t="s">
+        <v>786</v>
+      </c>
+      <c r="F495" t="s">
+        <v>792</v>
+      </c>
+      <c r="G495" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="496" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A496" t="s">
+        <v>425</v>
+      </c>
+      <c r="B496" t="s">
+        <v>1360</v>
+      </c>
+      <c r="D496" t="s">
+        <v>1361</v>
+      </c>
+      <c r="E496" t="s">
+        <v>1362</v>
+      </c>
+      <c r="F496" t="s">
+        <v>792</v>
+      </c>
+      <c r="G496" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="497" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A497" t="s">
+        <v>425</v>
+      </c>
+      <c r="B497" t="s">
+        <v>420</v>
+      </c>
+      <c r="D497" t="s">
+        <v>369</v>
+      </c>
+      <c r="E497" t="s">
+        <v>787</v>
+      </c>
+      <c r="F497" t="s">
+        <v>792</v>
+      </c>
+      <c r="G497" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="498" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A498" t="s">
+        <v>425</v>
+      </c>
+      <c r="B498" t="s">
+        <v>421</v>
+      </c>
+      <c r="D498" t="s">
+        <v>370</v>
+      </c>
+      <c r="E498" t="s">
+        <v>788</v>
+      </c>
+      <c r="F498" t="s">
+        <v>792</v>
+      </c>
+      <c r="G498" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="499" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A499" t="s">
+        <v>425</v>
+      </c>
+      <c r="B499" t="s">
+        <v>422</v>
+      </c>
+      <c r="D499" t="s">
+        <v>371</v>
+      </c>
+      <c r="E499" t="s">
+        <v>789</v>
+      </c>
+      <c r="F499" t="s">
+        <v>792</v>
+      </c>
+      <c r="G499" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="500" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A500" t="s">
+        <v>425</v>
+      </c>
+      <c r="B500" t="s">
+        <v>423</v>
+      </c>
+      <c r="D500" t="s">
+        <v>372</v>
+      </c>
+      <c r="E500" t="s">
+        <v>790</v>
+      </c>
+      <c r="F500" t="s">
+        <v>792</v>
+      </c>
+      <c r="G500" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="501" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A501" t="s">
+        <v>425</v>
+      </c>
+      <c r="B501" t="s">
+        <v>424</v>
+      </c>
+      <c r="D501" t="s">
+        <v>373</v>
+      </c>
+      <c r="E501" t="s">
+        <v>791</v>
+      </c>
+      <c r="F501" t="s">
+        <v>792</v>
+      </c>
+      <c r="G501" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="502" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A502" t="s">
+        <v>425</v>
+      </c>
+      <c r="B502" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D502" t="s">
+        <v>1159</v>
+      </c>
+      <c r="E502" t="s">
+        <v>1263</v>
+      </c>
+      <c r="F502" t="s">
+        <v>792</v>
+      </c>
+      <c r="G502" t="s">
         <v>7</v>
       </c>
     </row>

--- a/Bibsam_tidskriftslistor/scifree_data_mdpi.xlsx
+++ b/Bibsam_tidskriftslistor/scifree_data_mdpi.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34E955A1-A6A9-46DB-A3CC-FC087901CAFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB9CBD60-3BDA-4E66-B409-6754B8F0AF9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3013" uniqueCount="1513">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3109" uniqueCount="1561">
   <si>
     <t>ISSN Electronic</t>
   </si>
@@ -4559,6 +4559,150 @@
   </si>
   <si>
     <t>https://www.mdpi.com/journal/stratsediment</t>
+  </si>
+  <si>
+    <t>3043-0429</t>
+  </si>
+  <si>
+    <t>Addiction &amp; Prevention</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/addictprev</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3043-0259 </t>
+  </si>
+  <si>
+    <t>Archaeological Studies</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/archaeolstud</t>
+  </si>
+  <si>
+    <t>3043-100X</t>
+  </si>
+  <si>
+    <t>Breast Cancer Research and Care</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/bcrc</t>
+  </si>
+  <si>
+    <t>3042-8718</t>
+  </si>
+  <si>
+    <t>Crafts</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/crafts</t>
+  </si>
+  <si>
+    <t>3042-9315</t>
+  </si>
+  <si>
+    <t>Digital Health and Innovation</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/dhi</t>
+  </si>
+  <si>
+    <t>3042-903X</t>
+  </si>
+  <si>
+    <t>Environmental Remediation</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/environremediat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3043-0569 </t>
+  </si>
+  <si>
+    <t>Freshwater</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/freshwater</t>
+  </si>
+  <si>
+    <t>3042-9242</t>
+  </si>
+  <si>
+    <t>Green</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/green</t>
+  </si>
+  <si>
+    <t>3042-9021</t>
+  </si>
+  <si>
+    <t>Industries</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/industries</t>
+  </si>
+  <si>
+    <t>3043-0348</t>
+  </si>
+  <si>
+    <t>Inflammation Journal</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/inflammj</t>
+  </si>
+  <si>
+    <t>3042-8890</t>
+  </si>
+  <si>
+    <t>International Journal of Medical Devices</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/ijmd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3042-8424 </t>
+  </si>
+  <si>
+    <t>Journal of Genome Biotechnology and Genetics</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/jgbg</t>
+  </si>
+  <si>
+    <t>3043-0097</t>
+  </si>
+  <si>
+    <t>Journal of Superintelligence</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/superintelligence</t>
+  </si>
+  <si>
+    <t>3042-9323</t>
+  </si>
+  <si>
+    <t>Pandemics</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/pandemics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3043-002X </t>
+  </si>
+  <si>
+    <t>Smart Fisheries</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/smartfish</t>
+  </si>
+  <si>
+    <t>3042-9617</t>
+  </si>
+  <si>
+    <t>Welding</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/welding</t>
   </si>
 </sst>
 </file>
@@ -4614,10 +4758,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{CE28C0A4-819D-4EF0-9CDA-5E28E0FCFC65}" name="Table2" displayName="Table2" ref="A1:G502" totalsRowShown="0">
-  <autoFilter ref="A1:G502" xr:uid="{CE28C0A4-819D-4EF0-9CDA-5E28E0FCFC65}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G502">
-    <sortCondition ref="D1:D502"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{CE28C0A4-819D-4EF0-9CDA-5E28E0FCFC65}" name="Table2" displayName="Table2" ref="A1:G518" totalsRowShown="0">
+  <autoFilter ref="A1:G518" xr:uid="{CE28C0A4-819D-4EF0-9CDA-5E28E0FCFC65}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G518">
+    <sortCondition ref="D1:D518"/>
   </sortState>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{475A72F7-1A1D-4F9A-8D5B-FCE65FA3E5BF}" name="Imprint"/>
@@ -4895,13 +5039,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5117B6EE-D8F2-49E5-ACBB-C4662ACB3D37}">
-  <dimension ref="A1:G502"/>
+  <dimension ref="A1:G518"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" customWidth="1"/>
     <col min="2" max="2" width="16.28515625" customWidth="1"/>
     <col min="3" max="3" width="11.85546875" customWidth="1"/>
-    <col min="4" max="4" width="15.28515625" customWidth="1"/>
+    <col min="4" max="4" width="26" customWidth="1"/>
     <col min="5" max="5" width="12.85546875" customWidth="1"/>
     <col min="6" max="6" width="18.5703125" customWidth="1"/>
     <col min="7" max="7" width="19.5703125" customWidth="1"/>
@@ -5015,13 +5159,13 @@
         <v>425</v>
       </c>
       <c r="B6" t="s">
-        <v>1366</v>
+        <v>1513</v>
       </c>
       <c r="D6" t="s">
-        <v>1367</v>
+        <v>1514</v>
       </c>
       <c r="E6" t="s">
-        <v>1368</v>
+        <v>1515</v>
       </c>
       <c r="F6" t="s">
         <v>792</v>
@@ -5035,13 +5179,13 @@
         <v>425</v>
       </c>
       <c r="B7" t="s">
-        <v>795</v>
+        <v>1366</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>1367</v>
       </c>
       <c r="E7" t="s">
-        <v>428</v>
+        <v>1368</v>
       </c>
       <c r="F7" t="s">
         <v>792</v>
@@ -5055,13 +5199,13 @@
         <v>425</v>
       </c>
       <c r="B8" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="D8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E8" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="F8" t="s">
         <v>792</v>
@@ -5075,13 +5219,13 @@
         <v>425</v>
       </c>
       <c r="B9" t="s">
-        <v>1160</v>
+        <v>796</v>
       </c>
       <c r="D9" t="s">
-        <v>1108</v>
+        <v>11</v>
       </c>
       <c r="E9" t="s">
-        <v>1212</v>
+        <v>429</v>
       </c>
       <c r="F9" t="s">
         <v>792</v>
@@ -5095,13 +5239,13 @@
         <v>425</v>
       </c>
       <c r="B10" t="s">
-        <v>1264</v>
+        <v>1160</v>
       </c>
       <c r="D10" t="s">
-        <v>1265</v>
+        <v>1108</v>
       </c>
       <c r="E10" t="s">
-        <v>1266</v>
+        <v>1212</v>
       </c>
       <c r="F10" t="s">
         <v>792</v>
@@ -5115,13 +5259,13 @@
         <v>425</v>
       </c>
       <c r="B11" t="s">
-        <v>797</v>
+        <v>1264</v>
       </c>
       <c r="D11" t="s">
-        <v>12</v>
+        <v>1265</v>
       </c>
       <c r="E11" t="s">
-        <v>430</v>
+        <v>1266</v>
       </c>
       <c r="F11" t="s">
         <v>792</v>
@@ -5135,13 +5279,13 @@
         <v>425</v>
       </c>
       <c r="B12" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="D12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E12" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F12" t="s">
         <v>792</v>
@@ -5155,13 +5299,13 @@
         <v>425</v>
       </c>
       <c r="B13" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="D13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E13" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F13" t="s">
         <v>792</v>
@@ -5175,13 +5319,13 @@
         <v>425</v>
       </c>
       <c r="B14" t="s">
-        <v>1161</v>
+        <v>799</v>
       </c>
       <c r="D14" t="s">
-        <v>1109</v>
+        <v>14</v>
       </c>
       <c r="E14" t="s">
-        <v>1213</v>
+        <v>432</v>
       </c>
       <c r="F14" t="s">
         <v>792</v>
@@ -5195,13 +5339,13 @@
         <v>425</v>
       </c>
       <c r="B15" t="s">
-        <v>800</v>
+        <v>1161</v>
       </c>
       <c r="D15" t="s">
-        <v>15</v>
+        <v>1109</v>
       </c>
       <c r="E15" t="s">
-        <v>433</v>
+        <v>1213</v>
       </c>
       <c r="F15" t="s">
         <v>792</v>
@@ -5215,13 +5359,13 @@
         <v>425</v>
       </c>
       <c r="B16" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="D16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E16" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="F16" t="s">
         <v>792</v>
@@ -5235,13 +5379,13 @@
         <v>425</v>
       </c>
       <c r="B17" t="s">
-        <v>1369</v>
+        <v>801</v>
       </c>
       <c r="D17" t="s">
-        <v>1370</v>
+        <v>16</v>
       </c>
       <c r="E17" t="s">
-        <v>1371</v>
+        <v>434</v>
       </c>
       <c r="F17" t="s">
         <v>792</v>
@@ -5255,13 +5399,13 @@
         <v>425</v>
       </c>
       <c r="B18" t="s">
-        <v>1372</v>
+        <v>1369</v>
       </c>
       <c r="D18" t="s">
-        <v>1373</v>
+        <v>1370</v>
       </c>
       <c r="E18" t="s">
-        <v>1374</v>
+        <v>1371</v>
       </c>
       <c r="F18" t="s">
         <v>792</v>
@@ -5275,13 +5419,13 @@
         <v>425</v>
       </c>
       <c r="B19" t="s">
-        <v>1375</v>
+        <v>1372</v>
       </c>
       <c r="D19" t="s">
-        <v>1376</v>
+        <v>1373</v>
       </c>
       <c r="E19" t="s">
-        <v>1377</v>
+        <v>1374</v>
       </c>
       <c r="F19" t="s">
         <v>792</v>
@@ -5295,13 +5439,13 @@
         <v>425</v>
       </c>
       <c r="B20" t="s">
-        <v>1378</v>
+        <v>1375</v>
       </c>
       <c r="D20" t="s">
-        <v>1379</v>
+        <v>1376</v>
       </c>
       <c r="E20" t="s">
-        <v>1380</v>
+        <v>1377</v>
       </c>
       <c r="F20" t="s">
         <v>792</v>
@@ -5315,13 +5459,13 @@
         <v>425</v>
       </c>
       <c r="B21" t="s">
-        <v>1381</v>
+        <v>1378</v>
       </c>
       <c r="D21" t="s">
-        <v>1382</v>
+        <v>1379</v>
       </c>
       <c r="E21" t="s">
-        <v>1383</v>
+        <v>1380</v>
       </c>
       <c r="F21" t="s">
         <v>792</v>
@@ -5335,13 +5479,13 @@
         <v>425</v>
       </c>
       <c r="B22" t="s">
-        <v>1384</v>
+        <v>1381</v>
       </c>
       <c r="D22" t="s">
-        <v>1385</v>
+        <v>1382</v>
       </c>
       <c r="E22" t="s">
-        <v>1386</v>
+        <v>1383</v>
       </c>
       <c r="F22" t="s">
         <v>792</v>
@@ -5355,13 +5499,13 @@
         <v>425</v>
       </c>
       <c r="B23" t="s">
-        <v>1162</v>
+        <v>1384</v>
       </c>
       <c r="D23" t="s">
-        <v>1110</v>
+        <v>1385</v>
       </c>
       <c r="E23" t="s">
-        <v>1214</v>
+        <v>1386</v>
       </c>
       <c r="F23" t="s">
         <v>792</v>
@@ -5375,13 +5519,13 @@
         <v>425</v>
       </c>
       <c r="B24" t="s">
-        <v>802</v>
+        <v>1162</v>
       </c>
       <c r="D24" t="s">
-        <v>17</v>
+        <v>1110</v>
       </c>
       <c r="E24" t="s">
-        <v>435</v>
+        <v>1214</v>
       </c>
       <c r="F24" t="s">
         <v>792</v>
@@ -5395,13 +5539,13 @@
         <v>425</v>
       </c>
       <c r="B25" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="D25" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E25" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="F25" t="s">
         <v>792</v>
@@ -5415,13 +5559,13 @@
         <v>425</v>
       </c>
       <c r="B26" t="s">
-        <v>1163</v>
+        <v>803</v>
       </c>
       <c r="D26" t="s">
-        <v>1111</v>
+        <v>18</v>
       </c>
       <c r="E26" t="s">
-        <v>1215</v>
+        <v>436</v>
       </c>
       <c r="F26" t="s">
         <v>792</v>
@@ -5435,13 +5579,13 @@
         <v>425</v>
       </c>
       <c r="B27" t="s">
-        <v>1387</v>
+        <v>1163</v>
       </c>
       <c r="D27" t="s">
-        <v>1388</v>
+        <v>1111</v>
       </c>
       <c r="E27" t="s">
-        <v>1389</v>
+        <v>1215</v>
       </c>
       <c r="F27" t="s">
         <v>792</v>
@@ -5455,13 +5599,13 @@
         <v>425</v>
       </c>
       <c r="B28" t="s">
-        <v>804</v>
+        <v>1387</v>
       </c>
       <c r="D28" t="s">
-        <v>19</v>
+        <v>1388</v>
       </c>
       <c r="E28" t="s">
-        <v>437</v>
+        <v>1389</v>
       </c>
       <c r="F28" t="s">
         <v>792</v>
@@ -5475,13 +5619,13 @@
         <v>425</v>
       </c>
       <c r="B29" t="s">
-        <v>1164</v>
+        <v>804</v>
       </c>
       <c r="D29" t="s">
-        <v>1112</v>
+        <v>19</v>
       </c>
       <c r="E29" t="s">
-        <v>1216</v>
+        <v>437</v>
       </c>
       <c r="F29" t="s">
         <v>792</v>
@@ -5495,13 +5639,13 @@
         <v>425</v>
       </c>
       <c r="B30" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="D30" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="E30" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="F30" t="s">
         <v>792</v>
@@ -5515,13 +5659,13 @@
         <v>425</v>
       </c>
       <c r="B31" t="s">
-        <v>1267</v>
+        <v>1165</v>
       </c>
       <c r="D31" t="s">
-        <v>1268</v>
+        <v>1113</v>
       </c>
       <c r="E31" t="s">
-        <v>1269</v>
+        <v>1217</v>
       </c>
       <c r="F31" t="s">
         <v>792</v>
@@ -5535,13 +5679,13 @@
         <v>425</v>
       </c>
       <c r="B32" t="s">
-        <v>805</v>
+        <v>1267</v>
       </c>
       <c r="D32" t="s">
-        <v>20</v>
+        <v>1268</v>
       </c>
       <c r="E32" t="s">
-        <v>438</v>
+        <v>1269</v>
       </c>
       <c r="F32" t="s">
         <v>792</v>
@@ -5555,13 +5699,13 @@
         <v>425</v>
       </c>
       <c r="B33" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="D33" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E33" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="F33" t="s">
         <v>792</v>
@@ -5575,13 +5719,13 @@
         <v>425</v>
       </c>
       <c r="B34" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="D34" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E34" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F34" t="s">
         <v>792</v>
@@ -5595,13 +5739,13 @@
         <v>425</v>
       </c>
       <c r="B35" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="D35" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E35" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="F35" t="s">
         <v>792</v>
@@ -5615,13 +5759,13 @@
         <v>425</v>
       </c>
       <c r="B36" t="s">
-        <v>1166</v>
+        <v>808</v>
       </c>
       <c r="D36" t="s">
-        <v>1114</v>
+        <v>23</v>
       </c>
       <c r="E36" t="s">
-        <v>1218</v>
+        <v>441</v>
       </c>
       <c r="F36" t="s">
         <v>792</v>
@@ -5635,13 +5779,13 @@
         <v>425</v>
       </c>
       <c r="B37" t="s">
-        <v>809</v>
+        <v>1166</v>
       </c>
       <c r="D37" t="s">
-        <v>24</v>
+        <v>1114</v>
       </c>
       <c r="E37" t="s">
-        <v>442</v>
+        <v>1218</v>
       </c>
       <c r="F37" t="s">
         <v>792</v>
@@ -5655,13 +5799,13 @@
         <v>425</v>
       </c>
       <c r="B38" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="D38" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E38" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="F38" t="s">
         <v>792</v>
@@ -5675,13 +5819,13 @@
         <v>425</v>
       </c>
       <c r="B39" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="D39" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E39" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F39" t="s">
         <v>792</v>
@@ -5695,13 +5839,13 @@
         <v>425</v>
       </c>
       <c r="B40" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="D40" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E40" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="F40" t="s">
         <v>792</v>
@@ -5715,13 +5859,13 @@
         <v>425</v>
       </c>
       <c r="B41" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="D41" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E41" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F41" t="s">
         <v>792</v>
@@ -5735,13 +5879,13 @@
         <v>425</v>
       </c>
       <c r="B42" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="D42" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E42" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="F42" t="s">
         <v>792</v>
@@ -5755,13 +5899,13 @@
         <v>425</v>
       </c>
       <c r="B43" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="D43" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E43" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="F43" t="s">
         <v>792</v>
@@ -5775,13 +5919,13 @@
         <v>425</v>
       </c>
       <c r="B44" t="s">
-        <v>1390</v>
+        <v>815</v>
       </c>
       <c r="D44" t="s">
-        <v>1391</v>
+        <v>30</v>
       </c>
       <c r="E44" t="s">
-        <v>1392</v>
+        <v>448</v>
       </c>
       <c r="F44" t="s">
         <v>792</v>
@@ -5795,13 +5939,13 @@
         <v>425</v>
       </c>
       <c r="B45" t="s">
-        <v>816</v>
+        <v>1390</v>
       </c>
       <c r="D45" t="s">
-        <v>31</v>
+        <v>1391</v>
       </c>
       <c r="E45" t="s">
-        <v>449</v>
+        <v>1392</v>
       </c>
       <c r="F45" t="s">
         <v>792</v>
@@ -5815,13 +5959,13 @@
         <v>425</v>
       </c>
       <c r="B46" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="D46" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E46" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F46" t="s">
         <v>792</v>
@@ -5835,13 +5979,13 @@
         <v>425</v>
       </c>
       <c r="B47" t="s">
-        <v>1167</v>
+        <v>1516</v>
       </c>
       <c r="D47" t="s">
-        <v>1115</v>
+        <v>1517</v>
       </c>
       <c r="E47" t="s">
-        <v>1219</v>
+        <v>1518</v>
       </c>
       <c r="F47" t="s">
         <v>792</v>
@@ -5855,13 +5999,13 @@
         <v>425</v>
       </c>
       <c r="B48" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="D48" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E48" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="F48" t="s">
         <v>792</v>
@@ -5875,13 +6019,13 @@
         <v>425</v>
       </c>
       <c r="B49" t="s">
-        <v>1393</v>
+        <v>1167</v>
       </c>
       <c r="D49" t="s">
-        <v>1394</v>
+        <v>1115</v>
       </c>
       <c r="E49" t="s">
-        <v>1395</v>
+        <v>1219</v>
       </c>
       <c r="F49" t="s">
         <v>792</v>
@@ -5895,13 +6039,13 @@
         <v>425</v>
       </c>
       <c r="B50" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="D50" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E50" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F50" t="s">
         <v>792</v>
@@ -5915,13 +6059,13 @@
         <v>425</v>
       </c>
       <c r="B51" t="s">
-        <v>820</v>
+        <v>1393</v>
       </c>
       <c r="D51" t="s">
-        <v>35</v>
+        <v>1394</v>
       </c>
       <c r="E51" t="s">
-        <v>453</v>
+        <v>1395</v>
       </c>
       <c r="F51" t="s">
         <v>792</v>
@@ -5935,13 +6079,13 @@
         <v>425</v>
       </c>
       <c r="B52" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="D52" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E52" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="F52" t="s">
         <v>792</v>
@@ -5955,13 +6099,13 @@
         <v>425</v>
       </c>
       <c r="B53" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="D53" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E53" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="F53" t="s">
         <v>792</v>
@@ -5975,13 +6119,13 @@
         <v>425</v>
       </c>
       <c r="B54" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="D54" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E54" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="F54" t="s">
         <v>792</v>
@@ -5995,13 +6139,13 @@
         <v>425</v>
       </c>
       <c r="B55" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="D55" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E55" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="F55" t="s">
         <v>792</v>
@@ -6015,13 +6159,13 @@
         <v>425</v>
       </c>
       <c r="B56" t="s">
-        <v>1168</v>
+        <v>823</v>
       </c>
       <c r="D56" t="s">
-        <v>1116</v>
+        <v>38</v>
       </c>
       <c r="E56" t="s">
-        <v>1220</v>
+        <v>456</v>
       </c>
       <c r="F56" t="s">
         <v>792</v>
@@ -6035,13 +6179,13 @@
         <v>425</v>
       </c>
       <c r="B57" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="D57" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E57" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="F57" t="s">
         <v>792</v>
@@ -6055,13 +6199,13 @@
         <v>425</v>
       </c>
       <c r="B58" t="s">
-        <v>826</v>
+        <v>1168</v>
       </c>
       <c r="D58" t="s">
-        <v>41</v>
+        <v>1116</v>
       </c>
       <c r="E58" t="s">
-        <v>459</v>
+        <v>1220</v>
       </c>
       <c r="F58" t="s">
         <v>792</v>
@@ -6075,13 +6219,13 @@
         <v>425</v>
       </c>
       <c r="B59" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="D59" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E59" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="F59" t="s">
         <v>792</v>
@@ -6095,13 +6239,13 @@
         <v>425</v>
       </c>
       <c r="B60" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="D60" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E60" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="F60" t="s">
         <v>792</v>
@@ -6115,13 +6259,13 @@
         <v>425</v>
       </c>
       <c r="B61" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="D61" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E61" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="F61" t="s">
         <v>792</v>
@@ -6135,13 +6279,13 @@
         <v>425</v>
       </c>
       <c r="B62" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="D62" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E62" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="F62" t="s">
         <v>792</v>
@@ -6155,13 +6299,13 @@
         <v>425</v>
       </c>
       <c r="B63" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="D63" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E63" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="F63" t="s">
         <v>792</v>
@@ -6175,13 +6319,13 @@
         <v>425</v>
       </c>
       <c r="B64" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="D64" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E64" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="F64" t="s">
         <v>792</v>
@@ -6195,13 +6339,13 @@
         <v>425</v>
       </c>
       <c r="B65" t="s">
-        <v>1169</v>
+        <v>831</v>
       </c>
       <c r="D65" t="s">
-        <v>1117</v>
+        <v>46</v>
       </c>
       <c r="E65" t="s">
-        <v>1221</v>
+        <v>464</v>
       </c>
       <c r="F65" t="s">
         <v>792</v>
@@ -6215,13 +6359,13 @@
         <v>425</v>
       </c>
       <c r="B66" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="D66" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E66" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="F66" t="s">
         <v>792</v>
@@ -6235,13 +6379,13 @@
         <v>425</v>
       </c>
       <c r="B67" t="s">
-        <v>834</v>
+        <v>1169</v>
       </c>
       <c r="D67" t="s">
-        <v>49</v>
+        <v>1117</v>
       </c>
       <c r="E67" t="s">
-        <v>467</v>
+        <v>1221</v>
       </c>
       <c r="F67" t="s">
         <v>792</v>
@@ -6255,13 +6399,13 @@
         <v>425</v>
       </c>
       <c r="B68" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="D68" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E68" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="F68" t="s">
         <v>792</v>
@@ -6275,13 +6419,13 @@
         <v>425</v>
       </c>
       <c r="B69" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="D69" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E69" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="F69" t="s">
         <v>792</v>
@@ -6295,13 +6439,13 @@
         <v>425</v>
       </c>
       <c r="B70" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="D70" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E70" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="F70" t="s">
         <v>792</v>
@@ -6315,13 +6459,13 @@
         <v>425</v>
       </c>
       <c r="B71" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="D71" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E71" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="F71" t="s">
         <v>792</v>
@@ -6335,13 +6479,13 @@
         <v>425</v>
       </c>
       <c r="B72" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="D72" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E72" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="F72" t="s">
         <v>792</v>
@@ -6355,13 +6499,13 @@
         <v>425</v>
       </c>
       <c r="B73" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="D73" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E73" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="F73" t="s">
         <v>792</v>
@@ -6375,13 +6519,13 @@
         <v>425</v>
       </c>
       <c r="B74" t="s">
-        <v>1396</v>
+        <v>839</v>
       </c>
       <c r="D74" t="s">
-        <v>1397</v>
+        <v>54</v>
       </c>
       <c r="E74" t="s">
-        <v>1398</v>
+        <v>472</v>
       </c>
       <c r="F74" t="s">
         <v>792</v>
@@ -6395,13 +6539,13 @@
         <v>425</v>
       </c>
       <c r="B75" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="D75" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E75" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="F75" t="s">
         <v>792</v>
@@ -6415,13 +6559,13 @@
         <v>425</v>
       </c>
       <c r="B76" t="s">
-        <v>1399</v>
+        <v>1396</v>
       </c>
       <c r="D76" t="s">
-        <v>1400</v>
+        <v>1397</v>
       </c>
       <c r="E76" t="s">
-        <v>1401</v>
+        <v>1398</v>
       </c>
       <c r="F76" t="s">
         <v>792</v>
@@ -6435,13 +6579,13 @@
         <v>425</v>
       </c>
       <c r="B77" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="D77" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E77" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="F77" t="s">
         <v>792</v>
@@ -6455,13 +6599,13 @@
         <v>425</v>
       </c>
       <c r="B78" t="s">
-        <v>843</v>
+        <v>1399</v>
       </c>
       <c r="D78" t="s">
-        <v>58</v>
+        <v>1400</v>
       </c>
       <c r="E78" t="s">
-        <v>476</v>
+        <v>1401</v>
       </c>
       <c r="F78" t="s">
         <v>792</v>
@@ -6475,13 +6619,13 @@
         <v>425</v>
       </c>
       <c r="B79" t="s">
-        <v>1270</v>
+        <v>842</v>
       </c>
       <c r="D79" t="s">
-        <v>1271</v>
+        <v>57</v>
       </c>
       <c r="E79" t="s">
-        <v>1272</v>
+        <v>475</v>
       </c>
       <c r="F79" t="s">
         <v>792</v>
@@ -6495,13 +6639,13 @@
         <v>425</v>
       </c>
       <c r="B80" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="D80" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E80" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="F80" t="s">
         <v>792</v>
@@ -6515,13 +6659,13 @@
         <v>425</v>
       </c>
       <c r="B81" t="s">
-        <v>845</v>
+        <v>1270</v>
       </c>
       <c r="D81" t="s">
-        <v>60</v>
+        <v>1271</v>
       </c>
       <c r="E81" t="s">
-        <v>478</v>
+        <v>1272</v>
       </c>
       <c r="F81" t="s">
         <v>792</v>
@@ -6535,13 +6679,13 @@
         <v>425</v>
       </c>
       <c r="B82" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="D82" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E82" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="F82" t="s">
         <v>792</v>
@@ -6555,13 +6699,13 @@
         <v>425</v>
       </c>
       <c r="B83" t="s">
-        <v>847</v>
+        <v>1519</v>
       </c>
       <c r="D83" t="s">
-        <v>62</v>
+        <v>1520</v>
       </c>
       <c r="E83" t="s">
-        <v>480</v>
+        <v>1521</v>
       </c>
       <c r="F83" t="s">
         <v>792</v>
@@ -6575,13 +6719,13 @@
         <v>425</v>
       </c>
       <c r="B84" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="D84" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E84" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="F84" t="s">
         <v>792</v>
@@ -6595,13 +6739,13 @@
         <v>425</v>
       </c>
       <c r="B85" t="s">
-        <v>849</v>
+        <v>846</v>
       </c>
       <c r="D85" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E85" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="F85" t="s">
         <v>792</v>
@@ -6615,13 +6759,13 @@
         <v>425</v>
       </c>
       <c r="B86" t="s">
-        <v>1402</v>
+        <v>847</v>
       </c>
       <c r="D86" t="s">
-        <v>1403</v>
+        <v>62</v>
       </c>
       <c r="E86" t="s">
-        <v>1404</v>
+        <v>480</v>
       </c>
       <c r="F86" t="s">
         <v>792</v>
@@ -6635,13 +6779,13 @@
         <v>425</v>
       </c>
       <c r="B87" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="D87" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E87" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="F87" t="s">
         <v>792</v>
@@ -6655,13 +6799,13 @@
         <v>425</v>
       </c>
       <c r="B88" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="D88" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E88" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="F88" t="s">
         <v>792</v>
@@ -6675,13 +6819,13 @@
         <v>425</v>
       </c>
       <c r="B89" t="s">
-        <v>852</v>
+        <v>1402</v>
       </c>
       <c r="D89" t="s">
-        <v>67</v>
+        <v>1403</v>
       </c>
       <c r="E89" t="s">
-        <v>485</v>
+        <v>1404</v>
       </c>
       <c r="F89" t="s">
         <v>792</v>
@@ -6695,13 +6839,13 @@
         <v>425</v>
       </c>
       <c r="B90" t="s">
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="D90" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E90" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="F90" t="s">
         <v>792</v>
@@ -6715,13 +6859,13 @@
         <v>425</v>
       </c>
       <c r="B91" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="D91" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E91" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="F91" t="s">
         <v>792</v>
@@ -6735,13 +6879,13 @@
         <v>425</v>
       </c>
       <c r="B92" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="D92" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E92" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="F92" t="s">
         <v>792</v>
@@ -6755,13 +6899,13 @@
         <v>425</v>
       </c>
       <c r="B93" t="s">
-        <v>1170</v>
+        <v>853</v>
       </c>
       <c r="D93" t="s">
-        <v>1118</v>
+        <v>68</v>
       </c>
       <c r="E93" t="s">
-        <v>1222</v>
+        <v>486</v>
       </c>
       <c r="F93" t="s">
         <v>792</v>
@@ -6775,13 +6919,13 @@
         <v>425</v>
       </c>
       <c r="B94" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="D94" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E94" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="F94" t="s">
         <v>792</v>
@@ -6795,13 +6939,13 @@
         <v>425</v>
       </c>
       <c r="B95" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="D95" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E95" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="F95" t="s">
         <v>792</v>
@@ -6815,13 +6959,13 @@
         <v>425</v>
       </c>
       <c r="B96" t="s">
-        <v>858</v>
+        <v>1170</v>
       </c>
       <c r="D96" t="s">
-        <v>73</v>
+        <v>1118</v>
       </c>
       <c r="E96" t="s">
-        <v>491</v>
+        <v>1222</v>
       </c>
       <c r="F96" t="s">
         <v>792</v>
@@ -6835,13 +6979,13 @@
         <v>425</v>
       </c>
       <c r="B97" t="s">
-        <v>859</v>
+        <v>856</v>
       </c>
       <c r="D97" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E97" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="F97" t="s">
         <v>792</v>
@@ -6855,13 +6999,13 @@
         <v>425</v>
       </c>
       <c r="B98" t="s">
-        <v>860</v>
+        <v>857</v>
       </c>
       <c r="D98" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E98" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="F98" t="s">
         <v>792</v>
@@ -6875,13 +7019,13 @@
         <v>425</v>
       </c>
       <c r="B99" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
       <c r="D99" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E99" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="F99" t="s">
         <v>792</v>
@@ -6895,13 +7039,13 @@
         <v>425</v>
       </c>
       <c r="B100" t="s">
-        <v>862</v>
+        <v>859</v>
       </c>
       <c r="D100" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E100" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="F100" t="s">
         <v>792</v>
@@ -6915,13 +7059,13 @@
         <v>425</v>
       </c>
       <c r="B101" t="s">
-        <v>1405</v>
+        <v>860</v>
       </c>
       <c r="D101" t="s">
-        <v>1406</v>
+        <v>75</v>
       </c>
       <c r="E101" t="s">
-        <v>1407</v>
+        <v>493</v>
       </c>
       <c r="F101" t="s">
         <v>792</v>
@@ -6935,13 +7079,13 @@
         <v>425</v>
       </c>
       <c r="B102" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="D102" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E102" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="F102" t="s">
         <v>792</v>
@@ -6955,13 +7099,13 @@
         <v>425</v>
       </c>
       <c r="B103" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="D103" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E103" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="F103" t="s">
         <v>792</v>
@@ -6975,13 +7119,13 @@
         <v>425</v>
       </c>
       <c r="B104" t="s">
-        <v>865</v>
+        <v>1405</v>
       </c>
       <c r="D104" t="s">
-        <v>80</v>
+        <v>1406</v>
       </c>
       <c r="E104" t="s">
-        <v>498</v>
+        <v>1407</v>
       </c>
       <c r="F104" t="s">
         <v>792</v>
@@ -6995,13 +7139,13 @@
         <v>425</v>
       </c>
       <c r="B105" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="D105" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E105" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="F105" t="s">
         <v>792</v>
@@ -7015,13 +7159,13 @@
         <v>425</v>
       </c>
       <c r="B106" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="D106" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E106" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="F106" t="s">
         <v>792</v>
@@ -7035,13 +7179,13 @@
         <v>425</v>
       </c>
       <c r="B107" t="s">
-        <v>868</v>
+        <v>865</v>
       </c>
       <c r="D107" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E107" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="F107" t="s">
         <v>792</v>
@@ -7055,13 +7199,13 @@
         <v>425</v>
       </c>
       <c r="B108" t="s">
-        <v>1171</v>
+        <v>866</v>
       </c>
       <c r="D108" t="s">
-        <v>1119</v>
+        <v>81</v>
       </c>
       <c r="E108" t="s">
-        <v>1223</v>
+        <v>499</v>
       </c>
       <c r="F108" t="s">
         <v>792</v>
@@ -7075,13 +7219,13 @@
         <v>425</v>
       </c>
       <c r="B109" t="s">
-        <v>1408</v>
+        <v>867</v>
       </c>
       <c r="D109" t="s">
-        <v>1409</v>
+        <v>82</v>
       </c>
       <c r="E109" t="s">
-        <v>1410</v>
+        <v>500</v>
       </c>
       <c r="F109" t="s">
         <v>792</v>
@@ -7095,13 +7239,13 @@
         <v>425</v>
       </c>
       <c r="B110" t="s">
-        <v>1172</v>
+        <v>868</v>
       </c>
       <c r="D110" t="s">
-        <v>1120</v>
+        <v>83</v>
       </c>
       <c r="E110" t="s">
-        <v>1224</v>
+        <v>501</v>
       </c>
       <c r="F110" t="s">
         <v>792</v>
@@ -7115,13 +7259,13 @@
         <v>425</v>
       </c>
       <c r="B111" t="s">
-        <v>869</v>
+        <v>1171</v>
       </c>
       <c r="D111" t="s">
-        <v>84</v>
+        <v>1119</v>
       </c>
       <c r="E111" t="s">
-        <v>502</v>
+        <v>1223</v>
       </c>
       <c r="F111" t="s">
         <v>792</v>
@@ -7135,13 +7279,13 @@
         <v>425</v>
       </c>
       <c r="B112" t="s">
-        <v>870</v>
+        <v>1408</v>
       </c>
       <c r="D112" t="s">
-        <v>85</v>
+        <v>1409</v>
       </c>
       <c r="E112" t="s">
-        <v>503</v>
+        <v>1410</v>
       </c>
       <c r="F112" t="s">
         <v>792</v>
@@ -7155,13 +7299,13 @@
         <v>425</v>
       </c>
       <c r="B113" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="D113" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="E113" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="F113" t="s">
         <v>792</v>
@@ -7175,13 +7319,13 @@
         <v>425</v>
       </c>
       <c r="B114" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="D114" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E114" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="F114" t="s">
         <v>792</v>
@@ -7195,13 +7339,13 @@
         <v>425</v>
       </c>
       <c r="B115" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="D115" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E115" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="F115" t="s">
         <v>792</v>
@@ -7215,13 +7359,13 @@
         <v>425</v>
       </c>
       <c r="B116" t="s">
-        <v>873</v>
+        <v>1173</v>
       </c>
       <c r="D116" t="s">
-        <v>88</v>
+        <v>1121</v>
       </c>
       <c r="E116" t="s">
-        <v>506</v>
+        <v>1225</v>
       </c>
       <c r="F116" t="s">
         <v>792</v>
@@ -7235,13 +7379,13 @@
         <v>425</v>
       </c>
       <c r="B117" t="s">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="D117" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E117" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="F117" t="s">
         <v>792</v>
@@ -7255,13 +7399,13 @@
         <v>425</v>
       </c>
       <c r="B118" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="D118" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E118" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="F118" t="s">
         <v>792</v>
@@ -7275,13 +7419,13 @@
         <v>425</v>
       </c>
       <c r="B119" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="D119" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E119" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="F119" t="s">
         <v>792</v>
@@ -7295,13 +7439,13 @@
         <v>425</v>
       </c>
       <c r="B120" t="s">
-        <v>877</v>
+        <v>874</v>
       </c>
       <c r="D120" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E120" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="F120" t="s">
         <v>792</v>
@@ -7315,13 +7459,13 @@
         <v>425</v>
       </c>
       <c r="B121" t="s">
-        <v>1411</v>
+        <v>875</v>
       </c>
       <c r="D121" t="s">
-        <v>1412</v>
+        <v>90</v>
       </c>
       <c r="E121" t="s">
-        <v>1413</v>
+        <v>508</v>
       </c>
       <c r="F121" t="s">
         <v>792</v>
@@ -7335,13 +7479,13 @@
         <v>425</v>
       </c>
       <c r="B122" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="D122" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E122" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="F122" t="s">
         <v>792</v>
@@ -7355,13 +7499,13 @@
         <v>425</v>
       </c>
       <c r="B123" t="s">
-        <v>1300</v>
+        <v>877</v>
       </c>
       <c r="D123" t="s">
-        <v>1301</v>
+        <v>92</v>
       </c>
       <c r="E123" t="s">
-        <v>1302</v>
+        <v>510</v>
       </c>
       <c r="F123" t="s">
         <v>792</v>
@@ -7375,13 +7519,13 @@
         <v>425</v>
       </c>
       <c r="B124" t="s">
-        <v>879</v>
+        <v>1522</v>
       </c>
       <c r="D124" t="s">
-        <v>94</v>
+        <v>1523</v>
       </c>
       <c r="E124" t="s">
-        <v>512</v>
+        <v>1524</v>
       </c>
       <c r="F124" t="s">
         <v>792</v>
@@ -7395,13 +7539,13 @@
         <v>425</v>
       </c>
       <c r="B125" t="s">
-        <v>880</v>
+        <v>1411</v>
       </c>
       <c r="D125" t="s">
-        <v>95</v>
+        <v>1412</v>
       </c>
       <c r="E125" t="s">
-        <v>513</v>
+        <v>1413</v>
       </c>
       <c r="F125" t="s">
         <v>792</v>
@@ -7415,13 +7559,13 @@
         <v>425</v>
       </c>
       <c r="B126" t="s">
-        <v>1414</v>
+        <v>878</v>
       </c>
       <c r="D126" t="s">
-        <v>1415</v>
+        <v>93</v>
       </c>
       <c r="E126" t="s">
-        <v>1416</v>
+        <v>511</v>
       </c>
       <c r="F126" t="s">
         <v>792</v>
@@ -7435,13 +7579,13 @@
         <v>425</v>
       </c>
       <c r="B127" t="s">
-        <v>881</v>
+        <v>1300</v>
       </c>
       <c r="D127" t="s">
-        <v>96</v>
+        <v>1301</v>
       </c>
       <c r="E127" t="s">
-        <v>514</v>
+        <v>1302</v>
       </c>
       <c r="F127" t="s">
         <v>792</v>
@@ -7455,13 +7599,13 @@
         <v>425</v>
       </c>
       <c r="B128" t="s">
-        <v>882</v>
+        <v>879</v>
       </c>
       <c r="D128" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E128" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="F128" t="s">
         <v>792</v>
@@ -7475,13 +7619,13 @@
         <v>425</v>
       </c>
       <c r="B129" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="D129" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E129" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="F129" t="s">
         <v>792</v>
@@ -7495,13 +7639,13 @@
         <v>425</v>
       </c>
       <c r="B130" t="s">
-        <v>884</v>
+        <v>1414</v>
       </c>
       <c r="D130" t="s">
-        <v>99</v>
+        <v>1415</v>
       </c>
       <c r="E130" t="s">
-        <v>517</v>
+        <v>1416</v>
       </c>
       <c r="F130" t="s">
         <v>792</v>
@@ -7515,13 +7659,13 @@
         <v>425</v>
       </c>
       <c r="B131" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="D131" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E131" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="F131" t="s">
         <v>792</v>
@@ -7535,13 +7679,13 @@
         <v>425</v>
       </c>
       <c r="B132" t="s">
-        <v>886</v>
+        <v>882</v>
       </c>
       <c r="D132" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E132" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="F132" t="s">
         <v>792</v>
@@ -7555,13 +7699,13 @@
         <v>425</v>
       </c>
       <c r="B133" t="s">
-        <v>887</v>
+        <v>883</v>
       </c>
       <c r="D133" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E133" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="F133" t="s">
         <v>792</v>
@@ -7575,13 +7719,13 @@
         <v>425</v>
       </c>
       <c r="B134" t="s">
-        <v>888</v>
+        <v>884</v>
       </c>
       <c r="D134" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E134" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="F134" t="s">
         <v>792</v>
@@ -7595,13 +7739,13 @@
         <v>425</v>
       </c>
       <c r="B135" t="s">
-        <v>889</v>
+        <v>885</v>
       </c>
       <c r="D135" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="E135" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="F135" t="s">
         <v>792</v>
@@ -7615,13 +7759,13 @@
         <v>425</v>
       </c>
       <c r="B136" t="s">
-        <v>890</v>
+        <v>886</v>
       </c>
       <c r="D136" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="E136" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="F136" t="s">
         <v>792</v>
@@ -7635,13 +7779,13 @@
         <v>425</v>
       </c>
       <c r="B137" t="s">
-        <v>891</v>
+        <v>887</v>
       </c>
       <c r="D137" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E137" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="F137" t="s">
         <v>792</v>
@@ -7655,13 +7799,13 @@
         <v>425</v>
       </c>
       <c r="B138" t="s">
-        <v>892</v>
+        <v>888</v>
       </c>
       <c r="D138" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="E138" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="F138" t="s">
         <v>792</v>
@@ -7675,13 +7819,13 @@
         <v>425</v>
       </c>
       <c r="B139" t="s">
-        <v>893</v>
+        <v>889</v>
       </c>
       <c r="D139" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="E139" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="F139" t="s">
         <v>792</v>
@@ -7695,13 +7839,13 @@
         <v>425</v>
       </c>
       <c r="B140" t="s">
-        <v>894</v>
+        <v>890</v>
       </c>
       <c r="D140" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E140" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="F140" t="s">
         <v>792</v>
@@ -7715,13 +7859,13 @@
         <v>425</v>
       </c>
       <c r="B141" t="s">
-        <v>895</v>
+        <v>891</v>
       </c>
       <c r="D141" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E141" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="F141" t="s">
         <v>792</v>
@@ -7735,13 +7879,13 @@
         <v>425</v>
       </c>
       <c r="B142" t="s">
-        <v>896</v>
+        <v>892</v>
       </c>
       <c r="D142" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E142" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="F142" t="s">
         <v>792</v>
@@ -7755,13 +7899,13 @@
         <v>425</v>
       </c>
       <c r="B143" t="s">
-        <v>897</v>
+        <v>1525</v>
       </c>
       <c r="D143" t="s">
-        <v>112</v>
+        <v>1526</v>
       </c>
       <c r="E143" t="s">
-        <v>530</v>
+        <v>1527</v>
       </c>
       <c r="F143" t="s">
         <v>792</v>
@@ -7775,13 +7919,13 @@
         <v>425</v>
       </c>
       <c r="B144" t="s">
-        <v>1174</v>
+        <v>893</v>
       </c>
       <c r="D144" t="s">
-        <v>1122</v>
+        <v>108</v>
       </c>
       <c r="E144" t="s">
-        <v>1226</v>
+        <v>526</v>
       </c>
       <c r="F144" t="s">
         <v>792</v>
@@ -7795,13 +7939,13 @@
         <v>425</v>
       </c>
       <c r="B145" t="s">
-        <v>898</v>
+        <v>894</v>
       </c>
       <c r="D145" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E145" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="F145" t="s">
         <v>792</v>
@@ -7815,13 +7959,13 @@
         <v>425</v>
       </c>
       <c r="B146" t="s">
-        <v>899</v>
+        <v>895</v>
       </c>
       <c r="D146" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E146" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="F146" t="s">
         <v>792</v>
@@ -7835,13 +7979,13 @@
         <v>425</v>
       </c>
       <c r="B147" t="s">
-        <v>900</v>
+        <v>896</v>
       </c>
       <c r="D147" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="E147" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="F147" t="s">
         <v>792</v>
@@ -7855,13 +7999,13 @@
         <v>425</v>
       </c>
       <c r="B148" t="s">
-        <v>901</v>
+        <v>897</v>
       </c>
       <c r="D148" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="E148" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="F148" t="s">
         <v>792</v>
@@ -7875,13 +8019,13 @@
         <v>425</v>
       </c>
       <c r="B149" t="s">
-        <v>902</v>
+        <v>1174</v>
       </c>
       <c r="D149" t="s">
-        <v>117</v>
+        <v>1122</v>
       </c>
       <c r="E149" t="s">
-        <v>535</v>
+        <v>1226</v>
       </c>
       <c r="F149" t="s">
         <v>792</v>
@@ -7895,13 +8039,13 @@
         <v>425</v>
       </c>
       <c r="B150" t="s">
-        <v>903</v>
+        <v>898</v>
       </c>
       <c r="D150" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="E150" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="F150" t="s">
         <v>792</v>
@@ -7915,13 +8059,13 @@
         <v>425</v>
       </c>
       <c r="B151" t="s">
-        <v>904</v>
+        <v>899</v>
       </c>
       <c r="D151" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="E151" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="F151" t="s">
         <v>792</v>
@@ -7935,13 +8079,13 @@
         <v>425</v>
       </c>
       <c r="B152" t="s">
-        <v>905</v>
+        <v>900</v>
       </c>
       <c r="D152" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="E152" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="F152" t="s">
         <v>792</v>
@@ -7955,13 +8099,13 @@
         <v>425</v>
       </c>
       <c r="B153" t="s">
-        <v>906</v>
+        <v>901</v>
       </c>
       <c r="D153" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="E153" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="F153" t="s">
         <v>792</v>
@@ -7975,13 +8119,13 @@
         <v>425</v>
       </c>
       <c r="B154" t="s">
-        <v>907</v>
+        <v>902</v>
       </c>
       <c r="D154" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="E154" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="F154" t="s">
         <v>792</v>
@@ -7995,13 +8139,13 @@
         <v>425</v>
       </c>
       <c r="B155" t="s">
-        <v>1273</v>
+        <v>903</v>
       </c>
       <c r="D155" t="s">
-        <v>1274</v>
+        <v>118</v>
       </c>
       <c r="E155" t="s">
-        <v>1275</v>
+        <v>536</v>
       </c>
       <c r="F155" t="s">
         <v>792</v>
@@ -8015,13 +8159,13 @@
         <v>425</v>
       </c>
       <c r="B156" t="s">
-        <v>908</v>
+        <v>904</v>
       </c>
       <c r="D156" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E156" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="F156" t="s">
         <v>792</v>
@@ -8035,13 +8179,13 @@
         <v>425</v>
       </c>
       <c r="B157" t="s">
-        <v>909</v>
+        <v>905</v>
       </c>
       <c r="D157" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E157" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="F157" t="s">
         <v>792</v>
@@ -8055,13 +8199,13 @@
         <v>425</v>
       </c>
       <c r="B158" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="D158" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="E158" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="F158" t="s">
         <v>792</v>
@@ -8075,13 +8219,13 @@
         <v>425</v>
       </c>
       <c r="B159" t="s">
-        <v>1303</v>
+        <v>907</v>
       </c>
       <c r="D159" t="s">
-        <v>1304</v>
+        <v>122</v>
       </c>
       <c r="E159" t="s">
-        <v>1305</v>
+        <v>540</v>
       </c>
       <c r="F159" t="s">
         <v>792</v>
@@ -8095,13 +8239,13 @@
         <v>425</v>
       </c>
       <c r="B160" t="s">
-        <v>911</v>
+        <v>1273</v>
       </c>
       <c r="D160" t="s">
-        <v>126</v>
+        <v>1274</v>
       </c>
       <c r="E160" t="s">
-        <v>544</v>
+        <v>1275</v>
       </c>
       <c r="F160" t="s">
         <v>792</v>
@@ -8115,13 +8259,13 @@
         <v>425</v>
       </c>
       <c r="B161" t="s">
-        <v>1175</v>
+        <v>908</v>
       </c>
       <c r="D161" t="s">
-        <v>1123</v>
+        <v>123</v>
       </c>
       <c r="E161" t="s">
-        <v>1227</v>
+        <v>541</v>
       </c>
       <c r="F161" t="s">
         <v>792</v>
@@ -8135,13 +8279,13 @@
         <v>425</v>
       </c>
       <c r="B162" t="s">
-        <v>1417</v>
+        <v>909</v>
       </c>
       <c r="D162" t="s">
-        <v>1418</v>
+        <v>124</v>
       </c>
       <c r="E162" t="s">
-        <v>1419</v>
+        <v>542</v>
       </c>
       <c r="F162" t="s">
         <v>792</v>
@@ -8155,13 +8299,13 @@
         <v>425</v>
       </c>
       <c r="B163" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="D163" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E163" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="F163" t="s">
         <v>792</v>
@@ -8175,13 +8319,13 @@
         <v>425</v>
       </c>
       <c r="B164" t="s">
-        <v>1420</v>
+        <v>1303</v>
       </c>
       <c r="D164" t="s">
-        <v>1421</v>
+        <v>1304</v>
       </c>
       <c r="E164" t="s">
-        <v>1422</v>
+        <v>1305</v>
       </c>
       <c r="F164" t="s">
         <v>792</v>
@@ -8195,13 +8339,13 @@
         <v>425</v>
       </c>
       <c r="B165" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="D165" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E165" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="F165" t="s">
         <v>792</v>
@@ -8215,13 +8359,13 @@
         <v>425</v>
       </c>
       <c r="B166" t="s">
-        <v>914</v>
+        <v>1175</v>
       </c>
       <c r="D166" t="s">
-        <v>129</v>
+        <v>1123</v>
       </c>
       <c r="E166" t="s">
-        <v>547</v>
+        <v>1227</v>
       </c>
       <c r="F166" t="s">
         <v>792</v>
@@ -8235,13 +8379,13 @@
         <v>425</v>
       </c>
       <c r="B167" t="s">
-        <v>915</v>
+        <v>1417</v>
       </c>
       <c r="D167" t="s">
-        <v>130</v>
+        <v>1418</v>
       </c>
       <c r="E167" t="s">
-        <v>548</v>
+        <v>1419</v>
       </c>
       <c r="F167" t="s">
         <v>792</v>
@@ -8255,13 +8399,13 @@
         <v>425</v>
       </c>
       <c r="B168" t="s">
-        <v>916</v>
+        <v>912</v>
       </c>
       <c r="D168" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E168" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="F168" t="s">
         <v>792</v>
@@ -8275,13 +8419,13 @@
         <v>425</v>
       </c>
       <c r="B169" t="s">
-        <v>917</v>
+        <v>1420</v>
       </c>
       <c r="D169" t="s">
-        <v>132</v>
+        <v>1421</v>
       </c>
       <c r="E169" t="s">
-        <v>550</v>
+        <v>1422</v>
       </c>
       <c r="F169" t="s">
         <v>792</v>
@@ -8295,13 +8439,13 @@
         <v>425</v>
       </c>
       <c r="B170" t="s">
-        <v>1423</v>
+        <v>1528</v>
       </c>
       <c r="D170" t="s">
-        <v>1424</v>
+        <v>1529</v>
       </c>
       <c r="E170" t="s">
-        <v>1425</v>
+        <v>1530</v>
       </c>
       <c r="F170" t="s">
         <v>792</v>
@@ -8315,13 +8459,13 @@
         <v>425</v>
       </c>
       <c r="B171" t="s">
-        <v>918</v>
+        <v>913</v>
       </c>
       <c r="D171" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="E171" t="s">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="F171" t="s">
         <v>792</v>
@@ -8335,13 +8479,13 @@
         <v>425</v>
       </c>
       <c r="B172" t="s">
-        <v>919</v>
+        <v>914</v>
       </c>
       <c r="D172" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="E172" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="F172" t="s">
         <v>792</v>
@@ -8355,13 +8499,13 @@
         <v>425</v>
       </c>
       <c r="B173" t="s">
-        <v>1176</v>
+        <v>915</v>
       </c>
       <c r="D173" t="s">
-        <v>1124</v>
+        <v>130</v>
       </c>
       <c r="E173" t="s">
-        <v>1228</v>
+        <v>548</v>
       </c>
       <c r="F173" t="s">
         <v>792</v>
@@ -8375,13 +8519,13 @@
         <v>425</v>
       </c>
       <c r="B174" t="s">
-        <v>920</v>
+        <v>916</v>
       </c>
       <c r="D174" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E174" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="F174" t="s">
         <v>792</v>
@@ -8395,13 +8539,13 @@
         <v>425</v>
       </c>
       <c r="B175" t="s">
-        <v>921</v>
+        <v>917</v>
       </c>
       <c r="D175" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E175" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="F175" t="s">
         <v>792</v>
@@ -8415,13 +8559,13 @@
         <v>425</v>
       </c>
       <c r="B176" t="s">
-        <v>922</v>
+        <v>1423</v>
       </c>
       <c r="D176" t="s">
-        <v>137</v>
+        <v>1424</v>
       </c>
       <c r="E176" t="s">
-        <v>555</v>
+        <v>1425</v>
       </c>
       <c r="F176" t="s">
         <v>792</v>
@@ -8435,13 +8579,13 @@
         <v>425</v>
       </c>
       <c r="B177" t="s">
-        <v>923</v>
+        <v>918</v>
       </c>
       <c r="D177" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="E177" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="F177" t="s">
         <v>792</v>
@@ -8455,13 +8599,13 @@
         <v>425</v>
       </c>
       <c r="B178" t="s">
-        <v>924</v>
+        <v>919</v>
       </c>
       <c r="D178" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="E178" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="F178" t="s">
         <v>792</v>
@@ -8475,13 +8619,13 @@
         <v>425</v>
       </c>
       <c r="B179" t="s">
-        <v>925</v>
+        <v>1176</v>
       </c>
       <c r="D179" t="s">
-        <v>140</v>
+        <v>1124</v>
       </c>
       <c r="E179" t="s">
-        <v>558</v>
+        <v>1228</v>
       </c>
       <c r="F179" t="s">
         <v>792</v>
@@ -8495,13 +8639,13 @@
         <v>425</v>
       </c>
       <c r="B180" t="s">
-        <v>926</v>
+        <v>920</v>
       </c>
       <c r="D180" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="E180" t="s">
-        <v>559</v>
+        <v>553</v>
       </c>
       <c r="F180" t="s">
         <v>792</v>
@@ -8515,13 +8659,13 @@
         <v>425</v>
       </c>
       <c r="B181" t="s">
-        <v>1276</v>
+        <v>921</v>
       </c>
       <c r="D181" t="s">
-        <v>1277</v>
+        <v>136</v>
       </c>
       <c r="E181" t="s">
-        <v>1278</v>
+        <v>554</v>
       </c>
       <c r="F181" t="s">
         <v>792</v>
@@ -8535,13 +8679,13 @@
         <v>425</v>
       </c>
       <c r="B182" t="s">
-        <v>927</v>
+        <v>922</v>
       </c>
       <c r="D182" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="E182" t="s">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="F182" t="s">
         <v>792</v>
@@ -8555,13 +8699,13 @@
         <v>425</v>
       </c>
       <c r="B183" t="s">
-        <v>928</v>
+        <v>923</v>
       </c>
       <c r="D183" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="E183" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="F183" t="s">
         <v>792</v>
@@ -8575,13 +8719,13 @@
         <v>425</v>
       </c>
       <c r="B184" t="s">
-        <v>929</v>
+        <v>924</v>
       </c>
       <c r="D184" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="E184" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="F184" t="s">
         <v>792</v>
@@ -8595,13 +8739,13 @@
         <v>425</v>
       </c>
       <c r="B185" t="s">
-        <v>1177</v>
+        <v>925</v>
       </c>
       <c r="D185" t="s">
-        <v>1125</v>
+        <v>140</v>
       </c>
       <c r="E185" t="s">
-        <v>1229</v>
+        <v>558</v>
       </c>
       <c r="F185" t="s">
         <v>792</v>
@@ -8615,13 +8759,13 @@
         <v>425</v>
       </c>
       <c r="B186" t="s">
-        <v>930</v>
+        <v>926</v>
       </c>
       <c r="D186" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="E186" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="F186" t="s">
         <v>792</v>
@@ -8635,13 +8779,13 @@
         <v>425</v>
       </c>
       <c r="B187" t="s">
-        <v>931</v>
+        <v>1276</v>
       </c>
       <c r="D187" t="s">
-        <v>146</v>
+        <v>1277</v>
       </c>
       <c r="E187" t="s">
-        <v>564</v>
+        <v>1278</v>
       </c>
       <c r="F187" t="s">
         <v>792</v>
@@ -8655,13 +8799,13 @@
         <v>425</v>
       </c>
       <c r="B188" t="s">
-        <v>932</v>
+        <v>927</v>
       </c>
       <c r="D188" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="E188" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="F188" t="s">
         <v>792</v>
@@ -8675,13 +8819,13 @@
         <v>425</v>
       </c>
       <c r="B189" t="s">
-        <v>933</v>
+        <v>928</v>
       </c>
       <c r="D189" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="E189" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="F189" t="s">
         <v>792</v>
@@ -8695,13 +8839,13 @@
         <v>425</v>
       </c>
       <c r="B190" t="s">
-        <v>934</v>
+        <v>1531</v>
       </c>
       <c r="D190" t="s">
-        <v>149</v>
+        <v>1532</v>
       </c>
       <c r="E190" t="s">
-        <v>567</v>
+        <v>1533</v>
       </c>
       <c r="F190" t="s">
         <v>792</v>
@@ -8715,13 +8859,13 @@
         <v>425</v>
       </c>
       <c r="B191" t="s">
-        <v>935</v>
+        <v>929</v>
       </c>
       <c r="D191" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="E191" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="F191" t="s">
         <v>792</v>
@@ -8735,13 +8879,13 @@
         <v>425</v>
       </c>
       <c r="B192" t="s">
-        <v>936</v>
+        <v>1177</v>
       </c>
       <c r="D192" t="s">
-        <v>151</v>
+        <v>1125</v>
       </c>
       <c r="E192" t="s">
-        <v>569</v>
+        <v>1229</v>
       </c>
       <c r="F192" t="s">
         <v>792</v>
@@ -8755,13 +8899,13 @@
         <v>425</v>
       </c>
       <c r="B193" t="s">
-        <v>937</v>
+        <v>930</v>
       </c>
       <c r="D193" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="E193" t="s">
-        <v>570</v>
+        <v>563</v>
       </c>
       <c r="F193" t="s">
         <v>792</v>
@@ -8775,13 +8919,13 @@
         <v>425</v>
       </c>
       <c r="B194" t="s">
-        <v>1279</v>
+        <v>931</v>
       </c>
       <c r="D194" t="s">
-        <v>1280</v>
+        <v>146</v>
       </c>
       <c r="E194" t="s">
-        <v>1281</v>
+        <v>564</v>
       </c>
       <c r="F194" t="s">
         <v>792</v>
@@ -8795,13 +8939,13 @@
         <v>425</v>
       </c>
       <c r="B195" t="s">
-        <v>938</v>
+        <v>932</v>
       </c>
       <c r="D195" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="E195" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="F195" t="s">
         <v>792</v>
@@ -8815,13 +8959,13 @@
         <v>425</v>
       </c>
       <c r="B196" t="s">
-        <v>939</v>
+        <v>933</v>
       </c>
       <c r="D196" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="E196" t="s">
-        <v>572</v>
+        <v>566</v>
       </c>
       <c r="F196" t="s">
         <v>792</v>
@@ -8835,13 +8979,13 @@
         <v>425</v>
       </c>
       <c r="B197" t="s">
-        <v>940</v>
+        <v>934</v>
       </c>
       <c r="D197" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="E197" t="s">
-        <v>573</v>
+        <v>567</v>
       </c>
       <c r="F197" t="s">
         <v>792</v>
@@ -8855,13 +8999,13 @@
         <v>425</v>
       </c>
       <c r="B198" t="s">
-        <v>941</v>
+        <v>935</v>
       </c>
       <c r="D198" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="E198" t="s">
-        <v>574</v>
+        <v>568</v>
       </c>
       <c r="F198" t="s">
         <v>792</v>
@@ -8875,13 +9019,13 @@
         <v>425</v>
       </c>
       <c r="B199" t="s">
-        <v>942</v>
+        <v>936</v>
       </c>
       <c r="D199" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="E199" t="s">
-        <v>575</v>
+        <v>569</v>
       </c>
       <c r="F199" t="s">
         <v>792</v>
@@ -8895,13 +9039,13 @@
         <v>425</v>
       </c>
       <c r="B200" t="s">
-        <v>943</v>
+        <v>937</v>
       </c>
       <c r="D200" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="E200" t="s">
-        <v>576</v>
+        <v>570</v>
       </c>
       <c r="F200" t="s">
         <v>792</v>
@@ -8915,13 +9059,13 @@
         <v>425</v>
       </c>
       <c r="B201" t="s">
-        <v>1306</v>
+        <v>1279</v>
       </c>
       <c r="D201" t="s">
-        <v>1307</v>
+        <v>1280</v>
       </c>
       <c r="E201" t="s">
-        <v>1308</v>
+        <v>1281</v>
       </c>
       <c r="F201" t="s">
         <v>792</v>
@@ -8935,13 +9079,13 @@
         <v>425</v>
       </c>
       <c r="B202" t="s">
-        <v>944</v>
+        <v>938</v>
       </c>
       <c r="D202" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="E202" t="s">
-        <v>577</v>
+        <v>571</v>
       </c>
       <c r="F202" t="s">
         <v>792</v>
@@ -8955,13 +9099,13 @@
         <v>425</v>
       </c>
       <c r="B203" t="s">
-        <v>945</v>
+        <v>939</v>
       </c>
       <c r="D203" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="E203" t="s">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="F203" t="s">
         <v>792</v>
@@ -8975,13 +9119,13 @@
         <v>425</v>
       </c>
       <c r="B204" t="s">
-        <v>946</v>
+        <v>940</v>
       </c>
       <c r="D204" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="E204" t="s">
-        <v>579</v>
+        <v>573</v>
       </c>
       <c r="F204" t="s">
         <v>792</v>
@@ -8995,13 +9139,13 @@
         <v>425</v>
       </c>
       <c r="B205" t="s">
-        <v>1426</v>
+        <v>941</v>
       </c>
       <c r="D205" t="s">
-        <v>1427</v>
+        <v>156</v>
       </c>
       <c r="E205" t="s">
-        <v>1428</v>
+        <v>574</v>
       </c>
       <c r="F205" t="s">
         <v>792</v>
@@ -9015,13 +9159,13 @@
         <v>425</v>
       </c>
       <c r="B206" t="s">
-        <v>1309</v>
+        <v>942</v>
       </c>
       <c r="D206" t="s">
-        <v>1310</v>
+        <v>157</v>
       </c>
       <c r="E206" t="s">
-        <v>1311</v>
+        <v>575</v>
       </c>
       <c r="F206" t="s">
         <v>792</v>
@@ -9035,13 +9179,13 @@
         <v>425</v>
       </c>
       <c r="B207" t="s">
-        <v>1178</v>
+        <v>943</v>
       </c>
       <c r="D207" t="s">
-        <v>1126</v>
+        <v>158</v>
       </c>
       <c r="E207" t="s">
-        <v>1230</v>
+        <v>576</v>
       </c>
       <c r="F207" t="s">
         <v>792</v>
@@ -9055,13 +9199,13 @@
         <v>425</v>
       </c>
       <c r="B208" t="s">
-        <v>1179</v>
+        <v>1306</v>
       </c>
       <c r="D208" t="s">
-        <v>1127</v>
+        <v>1307</v>
       </c>
       <c r="E208" t="s">
-        <v>1231</v>
+        <v>1308</v>
       </c>
       <c r="F208" t="s">
         <v>792</v>
@@ -9075,13 +9219,13 @@
         <v>425</v>
       </c>
       <c r="B209" t="s">
-        <v>1429</v>
+        <v>944</v>
       </c>
       <c r="D209" t="s">
-        <v>1430</v>
+        <v>159</v>
       </c>
       <c r="E209" t="s">
-        <v>1431</v>
+        <v>577</v>
       </c>
       <c r="F209" t="s">
         <v>792</v>
@@ -9095,13 +9239,13 @@
         <v>425</v>
       </c>
       <c r="B210" t="s">
-        <v>1282</v>
+        <v>945</v>
       </c>
       <c r="D210" t="s">
-        <v>1283</v>
+        <v>160</v>
       </c>
       <c r="E210" t="s">
-        <v>1284</v>
+        <v>578</v>
       </c>
       <c r="F210" t="s">
         <v>792</v>
@@ -9115,13 +9259,13 @@
         <v>425</v>
       </c>
       <c r="B211" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="D211" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E211" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="F211" t="s">
         <v>792</v>
@@ -9135,13 +9279,13 @@
         <v>425</v>
       </c>
       <c r="B212" t="s">
-        <v>948</v>
+        <v>1426</v>
       </c>
       <c r="D212" t="s">
-        <v>163</v>
+        <v>1427</v>
       </c>
       <c r="E212" t="s">
-        <v>581</v>
+        <v>1428</v>
       </c>
       <c r="F212" t="s">
         <v>792</v>
@@ -9155,13 +9299,13 @@
         <v>425</v>
       </c>
       <c r="B213" t="s">
-        <v>949</v>
+        <v>1309</v>
       </c>
       <c r="D213" t="s">
-        <v>164</v>
+        <v>1310</v>
       </c>
       <c r="E213" t="s">
-        <v>582</v>
+        <v>1311</v>
       </c>
       <c r="F213" t="s">
         <v>792</v>
@@ -9175,13 +9319,13 @@
         <v>425</v>
       </c>
       <c r="B214" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
       <c r="D214" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="E214" t="s">
-        <v>1232</v>
+        <v>1230</v>
       </c>
       <c r="F214" t="s">
         <v>792</v>
@@ -9195,13 +9339,13 @@
         <v>425</v>
       </c>
       <c r="B215" t="s">
-        <v>950</v>
+        <v>1179</v>
       </c>
       <c r="D215" t="s">
-        <v>165</v>
+        <v>1127</v>
       </c>
       <c r="E215" t="s">
-        <v>583</v>
+        <v>1231</v>
       </c>
       <c r="F215" t="s">
         <v>792</v>
@@ -9215,13 +9359,13 @@
         <v>425</v>
       </c>
       <c r="B216" t="s">
-        <v>951</v>
+        <v>1534</v>
       </c>
       <c r="D216" t="s">
-        <v>166</v>
+        <v>1535</v>
       </c>
       <c r="E216" t="s">
-        <v>584</v>
+        <v>1536</v>
       </c>
       <c r="F216" t="s">
         <v>792</v>
@@ -9235,13 +9379,13 @@
         <v>425</v>
       </c>
       <c r="B217" t="s">
-        <v>952</v>
+        <v>1429</v>
       </c>
       <c r="D217" t="s">
-        <v>167</v>
+        <v>1430</v>
       </c>
       <c r="E217" t="s">
-        <v>585</v>
+        <v>1431</v>
       </c>
       <c r="F217" t="s">
         <v>792</v>
@@ -9255,13 +9399,13 @@
         <v>425</v>
       </c>
       <c r="B218" t="s">
-        <v>1181</v>
+        <v>1282</v>
       </c>
       <c r="D218" t="s">
-        <v>1129</v>
+        <v>1283</v>
       </c>
       <c r="E218" t="s">
-        <v>1233</v>
+        <v>1284</v>
       </c>
       <c r="F218" t="s">
         <v>792</v>
@@ -9275,13 +9419,13 @@
         <v>425</v>
       </c>
       <c r="B219" t="s">
-        <v>953</v>
+        <v>947</v>
       </c>
       <c r="D219" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="E219" t="s">
-        <v>586</v>
+        <v>580</v>
       </c>
       <c r="F219" t="s">
         <v>792</v>
@@ -9295,13 +9439,13 @@
         <v>425</v>
       </c>
       <c r="B220" t="s">
-        <v>954</v>
+        <v>948</v>
       </c>
       <c r="D220" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="E220" t="s">
-        <v>587</v>
+        <v>581</v>
       </c>
       <c r="F220" t="s">
         <v>792</v>
@@ -9315,13 +9459,13 @@
         <v>425</v>
       </c>
       <c r="B221" t="s">
-        <v>955</v>
+        <v>949</v>
       </c>
       <c r="D221" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E221" t="s">
-        <v>588</v>
+        <v>582</v>
       </c>
       <c r="F221" t="s">
         <v>792</v>
@@ -9335,13 +9479,13 @@
         <v>425</v>
       </c>
       <c r="B222" t="s">
-        <v>956</v>
+        <v>1180</v>
       </c>
       <c r="D222" t="s">
-        <v>171</v>
+        <v>1128</v>
       </c>
       <c r="E222" t="s">
-        <v>589</v>
+        <v>1232</v>
       </c>
       <c r="F222" t="s">
         <v>792</v>
@@ -9355,13 +9499,13 @@
         <v>425</v>
       </c>
       <c r="B223" t="s">
-        <v>957</v>
+        <v>950</v>
       </c>
       <c r="D223" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="E223" t="s">
-        <v>590</v>
+        <v>583</v>
       </c>
       <c r="F223" t="s">
         <v>792</v>
@@ -9375,13 +9519,13 @@
         <v>425</v>
       </c>
       <c r="B224" t="s">
-        <v>1432</v>
+        <v>951</v>
       </c>
       <c r="D224" t="s">
-        <v>1433</v>
+        <v>166</v>
       </c>
       <c r="E224" t="s">
-        <v>1434</v>
+        <v>584</v>
       </c>
       <c r="F224" t="s">
         <v>792</v>
@@ -9395,13 +9539,13 @@
         <v>425</v>
       </c>
       <c r="B225" t="s">
-        <v>958</v>
+        <v>952</v>
       </c>
       <c r="D225" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="E225" t="s">
-        <v>591</v>
+        <v>585</v>
       </c>
       <c r="F225" t="s">
         <v>792</v>
@@ -9415,13 +9559,13 @@
         <v>425</v>
       </c>
       <c r="B226" t="s">
-        <v>959</v>
+        <v>1181</v>
       </c>
       <c r="D226" t="s">
-        <v>174</v>
+        <v>1129</v>
       </c>
       <c r="E226" t="s">
-        <v>592</v>
+        <v>1233</v>
       </c>
       <c r="F226" t="s">
         <v>792</v>
@@ -9435,13 +9579,13 @@
         <v>425</v>
       </c>
       <c r="B227" t="s">
-        <v>960</v>
+        <v>953</v>
       </c>
       <c r="D227" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="E227" t="s">
-        <v>593</v>
+        <v>586</v>
       </c>
       <c r="F227" t="s">
         <v>792</v>
@@ -9455,13 +9599,13 @@
         <v>425</v>
       </c>
       <c r="B228" t="s">
-        <v>961</v>
+        <v>954</v>
       </c>
       <c r="D228" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="E228" t="s">
-        <v>594</v>
+        <v>587</v>
       </c>
       <c r="F228" t="s">
         <v>792</v>
@@ -9475,13 +9619,13 @@
         <v>425</v>
       </c>
       <c r="B229" t="s">
-        <v>962</v>
+        <v>955</v>
       </c>
       <c r="D229" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="E229" t="s">
-        <v>595</v>
+        <v>588</v>
       </c>
       <c r="F229" t="s">
         <v>792</v>
@@ -9495,13 +9639,13 @@
         <v>425</v>
       </c>
       <c r="B230" t="s">
-        <v>963</v>
+        <v>956</v>
       </c>
       <c r="D230" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="E230" t="s">
-        <v>596</v>
+        <v>589</v>
       </c>
       <c r="F230" t="s">
         <v>792</v>
@@ -9515,13 +9659,13 @@
         <v>425</v>
       </c>
       <c r="B231" t="s">
-        <v>964</v>
+        <v>957</v>
       </c>
       <c r="D231" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="E231" t="s">
-        <v>597</v>
+        <v>590</v>
       </c>
       <c r="F231" t="s">
         <v>792</v>
@@ -9535,13 +9679,13 @@
         <v>425</v>
       </c>
       <c r="B232" t="s">
-        <v>965</v>
+        <v>1432</v>
       </c>
       <c r="D232" t="s">
-        <v>180</v>
+        <v>1433</v>
       </c>
       <c r="E232" t="s">
-        <v>598</v>
+        <v>1434</v>
       </c>
       <c r="F232" t="s">
         <v>792</v>
@@ -9555,13 +9699,13 @@
         <v>425</v>
       </c>
       <c r="B233" t="s">
-        <v>966</v>
+        <v>958</v>
       </c>
       <c r="D233" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="E233" t="s">
-        <v>599</v>
+        <v>591</v>
       </c>
       <c r="F233" t="s">
         <v>792</v>
@@ -9575,13 +9719,13 @@
         <v>425</v>
       </c>
       <c r="B234" t="s">
-        <v>1312</v>
+        <v>959</v>
       </c>
       <c r="D234" t="s">
-        <v>1313</v>
+        <v>174</v>
       </c>
       <c r="E234" t="s">
-        <v>1314</v>
+        <v>592</v>
       </c>
       <c r="F234" t="s">
         <v>792</v>
@@ -9595,13 +9739,13 @@
         <v>425</v>
       </c>
       <c r="B235" t="s">
-        <v>1435</v>
+        <v>1537</v>
       </c>
       <c r="D235" t="s">
-        <v>1436</v>
+        <v>1538</v>
       </c>
       <c r="E235" t="s">
-        <v>1437</v>
+        <v>1539</v>
       </c>
       <c r="F235" t="s">
         <v>792</v>
@@ -9615,13 +9759,13 @@
         <v>425</v>
       </c>
       <c r="B236" t="s">
-        <v>1438</v>
+        <v>960</v>
       </c>
       <c r="D236" t="s">
-        <v>1439</v>
+        <v>175</v>
       </c>
       <c r="E236" t="s">
-        <v>1440</v>
+        <v>593</v>
       </c>
       <c r="F236" t="s">
         <v>792</v>
@@ -9635,13 +9779,13 @@
         <v>425</v>
       </c>
       <c r="B237" t="s">
-        <v>967</v>
+        <v>1540</v>
       </c>
       <c r="D237" t="s">
-        <v>182</v>
+        <v>1541</v>
       </c>
       <c r="E237" t="s">
-        <v>600</v>
+        <v>1542</v>
       </c>
       <c r="F237" t="s">
         <v>792</v>
@@ -9655,13 +9799,13 @@
         <v>425</v>
       </c>
       <c r="B238" t="s">
-        <v>968</v>
+        <v>961</v>
       </c>
       <c r="D238" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="E238" t="s">
-        <v>601</v>
+        <v>594</v>
       </c>
       <c r="F238" t="s">
         <v>792</v>
@@ -9675,13 +9819,13 @@
         <v>425</v>
       </c>
       <c r="B239" t="s">
-        <v>969</v>
+        <v>962</v>
       </c>
       <c r="D239" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="E239" t="s">
-        <v>602</v>
+        <v>595</v>
       </c>
       <c r="F239" t="s">
         <v>792</v>
@@ -9695,13 +9839,13 @@
         <v>425</v>
       </c>
       <c r="B240" t="s">
-        <v>970</v>
+        <v>963</v>
       </c>
       <c r="D240" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E240" t="s">
-        <v>603</v>
+        <v>596</v>
       </c>
       <c r="F240" t="s">
         <v>792</v>
@@ -9715,13 +9859,13 @@
         <v>425</v>
       </c>
       <c r="B241" t="s">
-        <v>1441</v>
+        <v>964</v>
       </c>
       <c r="D241" t="s">
-        <v>1442</v>
+        <v>179</v>
       </c>
       <c r="E241" t="s">
-        <v>1443</v>
+        <v>597</v>
       </c>
       <c r="F241" t="s">
         <v>792</v>
@@ -9735,13 +9879,13 @@
         <v>425</v>
       </c>
       <c r="B242" t="s">
-        <v>1182</v>
+        <v>965</v>
       </c>
       <c r="D242" t="s">
-        <v>1130</v>
+        <v>180</v>
       </c>
       <c r="E242" t="s">
-        <v>1234</v>
+        <v>598</v>
       </c>
       <c r="F242" t="s">
         <v>792</v>
@@ -9755,13 +9899,13 @@
         <v>425</v>
       </c>
       <c r="B243" t="s">
-        <v>1315</v>
+        <v>966</v>
       </c>
       <c r="D243" t="s">
-        <v>1316</v>
+        <v>181</v>
       </c>
       <c r="E243" t="s">
-        <v>1317</v>
+        <v>599</v>
       </c>
       <c r="F243" t="s">
         <v>792</v>
@@ -9775,13 +9919,13 @@
         <v>425</v>
       </c>
       <c r="B244" t="s">
-        <v>971</v>
+        <v>1312</v>
       </c>
       <c r="D244" t="s">
-        <v>186</v>
+        <v>1313</v>
       </c>
       <c r="E244" t="s">
-        <v>604</v>
+        <v>1314</v>
       </c>
       <c r="F244" t="s">
         <v>792</v>
@@ -9795,13 +9939,13 @@
         <v>425</v>
       </c>
       <c r="B245" t="s">
-        <v>972</v>
+        <v>1435</v>
       </c>
       <c r="D245" t="s">
-        <v>187</v>
+        <v>1436</v>
       </c>
       <c r="E245" t="s">
-        <v>605</v>
+        <v>1437</v>
       </c>
       <c r="F245" t="s">
         <v>792</v>
@@ -9815,13 +9959,13 @@
         <v>425</v>
       </c>
       <c r="B246" t="s">
-        <v>1183</v>
+        <v>1438</v>
       </c>
       <c r="D246" t="s">
-        <v>1131</v>
+        <v>1439</v>
       </c>
       <c r="E246" t="s">
-        <v>1235</v>
+        <v>1440</v>
       </c>
       <c r="F246" t="s">
         <v>792</v>
@@ -9835,13 +9979,13 @@
         <v>425</v>
       </c>
       <c r="B247" t="s">
-        <v>973</v>
+        <v>967</v>
       </c>
       <c r="D247" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="E247" t="s">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="F247" t="s">
         <v>792</v>
@@ -9855,13 +9999,13 @@
         <v>425</v>
       </c>
       <c r="B248" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="D248" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="E248" t="s">
-        <v>607</v>
+        <v>601</v>
       </c>
       <c r="F248" t="s">
         <v>792</v>
@@ -9875,13 +10019,13 @@
         <v>425</v>
       </c>
       <c r="B249" t="s">
-        <v>975</v>
+        <v>1543</v>
       </c>
       <c r="D249" t="s">
-        <v>190</v>
+        <v>1544</v>
       </c>
       <c r="E249" t="s">
-        <v>608</v>
+        <v>1545</v>
       </c>
       <c r="F249" t="s">
         <v>792</v>
@@ -9895,13 +10039,13 @@
         <v>425</v>
       </c>
       <c r="B250" t="s">
-        <v>976</v>
+        <v>969</v>
       </c>
       <c r="D250" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="E250" t="s">
-        <v>609</v>
+        <v>602</v>
       </c>
       <c r="F250" t="s">
         <v>792</v>
@@ -9915,13 +10059,13 @@
         <v>425</v>
       </c>
       <c r="B251" t="s">
-        <v>1444</v>
+        <v>970</v>
       </c>
       <c r="D251" t="s">
-        <v>1445</v>
+        <v>185</v>
       </c>
       <c r="E251" t="s">
-        <v>1446</v>
+        <v>603</v>
       </c>
       <c r="F251" t="s">
         <v>792</v>
@@ -9935,13 +10079,13 @@
         <v>425</v>
       </c>
       <c r="B252" t="s">
-        <v>977</v>
+        <v>1441</v>
       </c>
       <c r="D252" t="s">
-        <v>192</v>
+        <v>1442</v>
       </c>
       <c r="E252" t="s">
-        <v>610</v>
+        <v>1443</v>
       </c>
       <c r="F252" t="s">
         <v>792</v>
@@ -9955,13 +10099,13 @@
         <v>425</v>
       </c>
       <c r="B253" t="s">
-        <v>1447</v>
+        <v>1182</v>
       </c>
       <c r="D253" t="s">
-        <v>1448</v>
+        <v>1130</v>
       </c>
       <c r="E253" t="s">
-        <v>1449</v>
+        <v>1234</v>
       </c>
       <c r="F253" t="s">
         <v>792</v>
@@ -9975,13 +10119,13 @@
         <v>425</v>
       </c>
       <c r="B254" t="s">
-        <v>978</v>
+        <v>1315</v>
       </c>
       <c r="D254" t="s">
-        <v>193</v>
+        <v>1316</v>
       </c>
       <c r="E254" t="s">
-        <v>611</v>
+        <v>1317</v>
       </c>
       <c r="F254" t="s">
         <v>792</v>
@@ -9995,13 +10139,13 @@
         <v>425</v>
       </c>
       <c r="B255" t="s">
-        <v>1184</v>
+        <v>971</v>
       </c>
       <c r="D255" t="s">
-        <v>1132</v>
+        <v>186</v>
       </c>
       <c r="E255" t="s">
-        <v>1236</v>
+        <v>604</v>
       </c>
       <c r="F255" t="s">
         <v>792</v>
@@ -10015,13 +10159,13 @@
         <v>425</v>
       </c>
       <c r="B256" t="s">
-        <v>979</v>
+        <v>972</v>
       </c>
       <c r="D256" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="E256" t="s">
-        <v>612</v>
+        <v>605</v>
       </c>
       <c r="F256" t="s">
         <v>792</v>
@@ -10035,13 +10179,13 @@
         <v>425</v>
       </c>
       <c r="B257" t="s">
-        <v>980</v>
+        <v>1183</v>
       </c>
       <c r="D257" t="s">
-        <v>195</v>
+        <v>1131</v>
       </c>
       <c r="E257" t="s">
-        <v>613</v>
+        <v>1235</v>
       </c>
       <c r="F257" t="s">
         <v>792</v>
@@ -10055,13 +10199,13 @@
         <v>425</v>
       </c>
       <c r="B258" t="s">
-        <v>981</v>
+        <v>973</v>
       </c>
       <c r="D258" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="E258" t="s">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="F258" t="s">
         <v>792</v>
@@ -10075,13 +10219,13 @@
         <v>425</v>
       </c>
       <c r="B259" t="s">
-        <v>1318</v>
+        <v>974</v>
       </c>
       <c r="D259" t="s">
-        <v>1319</v>
+        <v>189</v>
       </c>
       <c r="E259" t="s">
-        <v>1320</v>
+        <v>607</v>
       </c>
       <c r="F259" t="s">
         <v>792</v>
@@ -10095,13 +10239,13 @@
         <v>425</v>
       </c>
       <c r="B260" t="s">
-        <v>982</v>
+        <v>975</v>
       </c>
       <c r="D260" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="E260" t="s">
-        <v>615</v>
+        <v>608</v>
       </c>
       <c r="F260" t="s">
         <v>792</v>
@@ -10115,13 +10259,13 @@
         <v>425</v>
       </c>
       <c r="B261" t="s">
-        <v>1185</v>
+        <v>976</v>
       </c>
       <c r="D261" t="s">
-        <v>1133</v>
+        <v>191</v>
       </c>
       <c r="E261" t="s">
-        <v>1237</v>
+        <v>609</v>
       </c>
       <c r="F261" t="s">
         <v>792</v>
@@ -10135,13 +10279,13 @@
         <v>425</v>
       </c>
       <c r="B262" t="s">
-        <v>1450</v>
+        <v>1444</v>
       </c>
       <c r="D262" t="s">
-        <v>1451</v>
+        <v>1445</v>
       </c>
       <c r="E262" t="s">
-        <v>1452</v>
+        <v>1446</v>
       </c>
       <c r="F262" t="s">
         <v>792</v>
@@ -10155,13 +10299,13 @@
         <v>425</v>
       </c>
       <c r="B263" t="s">
-        <v>983</v>
+        <v>977</v>
       </c>
       <c r="D263" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="E263" t="s">
-        <v>616</v>
+        <v>610</v>
       </c>
       <c r="F263" t="s">
         <v>792</v>
@@ -10175,13 +10319,13 @@
         <v>425</v>
       </c>
       <c r="B264" t="s">
-        <v>984</v>
+        <v>1447</v>
       </c>
       <c r="D264" t="s">
-        <v>199</v>
+        <v>1448</v>
       </c>
       <c r="E264" t="s">
-        <v>617</v>
+        <v>1449</v>
       </c>
       <c r="F264" t="s">
         <v>792</v>
@@ -10195,13 +10339,13 @@
         <v>425</v>
       </c>
       <c r="B265" t="s">
-        <v>985</v>
+        <v>978</v>
       </c>
       <c r="D265" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="E265" t="s">
-        <v>618</v>
+        <v>611</v>
       </c>
       <c r="F265" t="s">
         <v>792</v>
@@ -10215,13 +10359,13 @@
         <v>425</v>
       </c>
       <c r="B266" t="s">
-        <v>986</v>
+        <v>1184</v>
       </c>
       <c r="D266" t="s">
-        <v>201</v>
+        <v>1132</v>
       </c>
       <c r="E266" t="s">
-        <v>619</v>
+        <v>1236</v>
       </c>
       <c r="F266" t="s">
         <v>792</v>
@@ -10235,13 +10379,13 @@
         <v>425</v>
       </c>
       <c r="B267" t="s">
-        <v>1498</v>
+        <v>979</v>
       </c>
       <c r="D267" t="s">
-        <v>1499</v>
+        <v>194</v>
       </c>
       <c r="E267" t="s">
-        <v>1500</v>
+        <v>612</v>
       </c>
       <c r="F267" t="s">
         <v>792</v>
@@ -10255,13 +10399,13 @@
         <v>425</v>
       </c>
       <c r="B268" t="s">
-        <v>987</v>
+        <v>980</v>
       </c>
       <c r="D268" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="E268" t="s">
-        <v>620</v>
+        <v>613</v>
       </c>
       <c r="F268" t="s">
         <v>792</v>
@@ -10275,13 +10419,13 @@
         <v>425</v>
       </c>
       <c r="B269" t="s">
-        <v>988</v>
+        <v>981</v>
       </c>
       <c r="D269" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="E269" t="s">
-        <v>621</v>
+        <v>614</v>
       </c>
       <c r="F269" t="s">
         <v>792</v>
@@ -10295,13 +10439,13 @@
         <v>425</v>
       </c>
       <c r="B270" t="s">
-        <v>989</v>
+        <v>1318</v>
       </c>
       <c r="D270" t="s">
-        <v>204</v>
+        <v>1319</v>
       </c>
       <c r="E270" t="s">
-        <v>622</v>
+        <v>1320</v>
       </c>
       <c r="F270" t="s">
         <v>792</v>
@@ -10315,13 +10459,13 @@
         <v>425</v>
       </c>
       <c r="B271" t="s">
-        <v>990</v>
+        <v>982</v>
       </c>
       <c r="D271" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="E271" t="s">
-        <v>623</v>
+        <v>615</v>
       </c>
       <c r="F271" t="s">
         <v>792</v>
@@ -10335,13 +10479,13 @@
         <v>425</v>
       </c>
       <c r="B272" t="s">
-        <v>1321</v>
+        <v>1185</v>
       </c>
       <c r="D272" t="s">
-        <v>1322</v>
+        <v>1133</v>
       </c>
       <c r="E272" t="s">
-        <v>1323</v>
+        <v>1237</v>
       </c>
       <c r="F272" t="s">
         <v>792</v>
@@ -10355,13 +10499,13 @@
         <v>425</v>
       </c>
       <c r="B273" t="s">
-        <v>1453</v>
+        <v>1450</v>
       </c>
       <c r="D273" t="s">
-        <v>1454</v>
+        <v>1451</v>
       </c>
       <c r="E273" t="s">
-        <v>1455</v>
+        <v>1452</v>
       </c>
       <c r="F273" t="s">
         <v>792</v>
@@ -10375,13 +10519,13 @@
         <v>425</v>
       </c>
       <c r="B274" t="s">
-        <v>991</v>
+        <v>983</v>
       </c>
       <c r="D274" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="E274" t="s">
-        <v>624</v>
+        <v>616</v>
       </c>
       <c r="F274" t="s">
         <v>792</v>
@@ -10395,13 +10539,13 @@
         <v>425</v>
       </c>
       <c r="B275" t="s">
-        <v>992</v>
+        <v>984</v>
       </c>
       <c r="D275" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="E275" t="s">
-        <v>625</v>
+        <v>617</v>
       </c>
       <c r="F275" t="s">
         <v>792</v>
@@ -10415,13 +10559,13 @@
         <v>425</v>
       </c>
       <c r="B276" t="s">
-        <v>993</v>
+        <v>985</v>
       </c>
       <c r="D276" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="E276" t="s">
-        <v>626</v>
+        <v>618</v>
       </c>
       <c r="F276" t="s">
         <v>792</v>
@@ -10435,13 +10579,13 @@
         <v>425</v>
       </c>
       <c r="B277" t="s">
-        <v>994</v>
+        <v>1546</v>
       </c>
       <c r="D277" t="s">
-        <v>209</v>
+        <v>1547</v>
       </c>
       <c r="E277" t="s">
-        <v>627</v>
+        <v>1548</v>
       </c>
       <c r="F277" t="s">
         <v>792</v>
@@ -10455,13 +10599,13 @@
         <v>425</v>
       </c>
       <c r="B278" t="s">
-        <v>1456</v>
+        <v>986</v>
       </c>
       <c r="D278" t="s">
-        <v>1457</v>
+        <v>201</v>
       </c>
       <c r="E278" t="s">
-        <v>1458</v>
+        <v>619</v>
       </c>
       <c r="F278" t="s">
         <v>792</v>
@@ -10475,13 +10619,13 @@
         <v>425</v>
       </c>
       <c r="B279" t="s">
-        <v>995</v>
+        <v>1498</v>
       </c>
       <c r="D279" t="s">
-        <v>210</v>
+        <v>1499</v>
       </c>
       <c r="E279" t="s">
-        <v>628</v>
+        <v>1500</v>
       </c>
       <c r="F279" t="s">
         <v>792</v>
@@ -10495,13 +10639,13 @@
         <v>425</v>
       </c>
       <c r="B280" t="s">
-        <v>1324</v>
+        <v>987</v>
       </c>
       <c r="D280" t="s">
-        <v>1325</v>
+        <v>202</v>
       </c>
       <c r="E280" t="s">
-        <v>1326</v>
+        <v>620</v>
       </c>
       <c r="F280" t="s">
         <v>792</v>
@@ -10515,13 +10659,13 @@
         <v>425</v>
       </c>
       <c r="B281" t="s">
-        <v>1501</v>
+        <v>988</v>
       </c>
       <c r="D281" t="s">
-        <v>1502</v>
+        <v>203</v>
       </c>
       <c r="E281" t="s">
-        <v>1503</v>
+        <v>621</v>
       </c>
       <c r="F281" t="s">
         <v>792</v>
@@ -10535,13 +10679,13 @@
         <v>425</v>
       </c>
       <c r="B282" t="s">
-        <v>996</v>
+        <v>989</v>
       </c>
       <c r="D282" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="E282" t="s">
-        <v>629</v>
+        <v>622</v>
       </c>
       <c r="F282" t="s">
         <v>792</v>
@@ -10555,13 +10699,13 @@
         <v>425</v>
       </c>
       <c r="B283" t="s">
-        <v>997</v>
+        <v>990</v>
       </c>
       <c r="D283" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="E283" t="s">
-        <v>630</v>
+        <v>623</v>
       </c>
       <c r="F283" t="s">
         <v>792</v>
@@ -10575,13 +10719,13 @@
         <v>425</v>
       </c>
       <c r="B284" t="s">
-        <v>998</v>
+        <v>1321</v>
       </c>
       <c r="D284" t="s">
-        <v>213</v>
+        <v>1322</v>
       </c>
       <c r="E284" t="s">
-        <v>631</v>
+        <v>1323</v>
       </c>
       <c r="F284" t="s">
         <v>792</v>
@@ -10595,13 +10739,13 @@
         <v>425</v>
       </c>
       <c r="B285" t="s">
-        <v>1327</v>
+        <v>1453</v>
       </c>
       <c r="D285" t="s">
-        <v>1328</v>
+        <v>1454</v>
       </c>
       <c r="E285" t="s">
-        <v>1329</v>
+        <v>1455</v>
       </c>
       <c r="F285" t="s">
         <v>792</v>
@@ -10615,13 +10759,13 @@
         <v>425</v>
       </c>
       <c r="B286" t="s">
-        <v>999</v>
+        <v>991</v>
       </c>
       <c r="D286" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="E286" t="s">
-        <v>632</v>
+        <v>624</v>
       </c>
       <c r="F286" t="s">
         <v>792</v>
@@ -10635,13 +10779,13 @@
         <v>425</v>
       </c>
       <c r="B287" t="s">
-        <v>1186</v>
+        <v>992</v>
       </c>
       <c r="D287" t="s">
-        <v>1134</v>
+        <v>207</v>
       </c>
       <c r="E287" t="s">
-        <v>1238</v>
+        <v>625</v>
       </c>
       <c r="F287" t="s">
         <v>792</v>
@@ -10655,13 +10799,13 @@
         <v>425</v>
       </c>
       <c r="B288" t="s">
-        <v>1000</v>
+        <v>993</v>
       </c>
       <c r="D288" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="E288" t="s">
-        <v>633</v>
+        <v>626</v>
       </c>
       <c r="F288" t="s">
         <v>792</v>
@@ -10675,13 +10819,13 @@
         <v>425</v>
       </c>
       <c r="B289" t="s">
-        <v>1001</v>
+        <v>994</v>
       </c>
       <c r="D289" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="E289" t="s">
-        <v>634</v>
+        <v>627</v>
       </c>
       <c r="F289" t="s">
         <v>792</v>
@@ -10695,13 +10839,13 @@
         <v>425</v>
       </c>
       <c r="B290" t="s">
-        <v>1002</v>
+        <v>1456</v>
       </c>
       <c r="D290" t="s">
-        <v>217</v>
+        <v>1457</v>
       </c>
       <c r="E290" t="s">
-        <v>635</v>
+        <v>1458</v>
       </c>
       <c r="F290" t="s">
         <v>792</v>
@@ -10715,13 +10859,13 @@
         <v>425</v>
       </c>
       <c r="B291" t="s">
-        <v>1003</v>
+        <v>995</v>
       </c>
       <c r="D291" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="E291" t="s">
-        <v>636</v>
+        <v>628</v>
       </c>
       <c r="F291" t="s">
         <v>792</v>
@@ -10735,13 +10879,13 @@
         <v>425</v>
       </c>
       <c r="B292" t="s">
-        <v>1187</v>
+        <v>1324</v>
       </c>
       <c r="D292" t="s">
-        <v>1135</v>
+        <v>1325</v>
       </c>
       <c r="E292" t="s">
-        <v>1239</v>
+        <v>1326</v>
       </c>
       <c r="F292" t="s">
         <v>792</v>
@@ -10755,13 +10899,13 @@
         <v>425</v>
       </c>
       <c r="B293" t="s">
-        <v>1004</v>
+        <v>1501</v>
       </c>
       <c r="D293" t="s">
-        <v>219</v>
+        <v>1502</v>
       </c>
       <c r="E293" t="s">
-        <v>637</v>
+        <v>1503</v>
       </c>
       <c r="F293" t="s">
         <v>792</v>
@@ -10775,13 +10919,13 @@
         <v>425</v>
       </c>
       <c r="B294" t="s">
-        <v>1330</v>
+        <v>996</v>
       </c>
       <c r="D294" t="s">
-        <v>1331</v>
+        <v>211</v>
       </c>
       <c r="E294" t="s">
-        <v>1332</v>
+        <v>629</v>
       </c>
       <c r="F294" t="s">
         <v>792</v>
@@ -10795,13 +10939,13 @@
         <v>425</v>
       </c>
       <c r="B295" t="s">
-        <v>1333</v>
+        <v>997</v>
       </c>
       <c r="D295" t="s">
-        <v>1334</v>
+        <v>212</v>
       </c>
       <c r="E295" t="s">
-        <v>1335</v>
+        <v>630</v>
       </c>
       <c r="F295" t="s">
         <v>792</v>
@@ -10815,13 +10959,13 @@
         <v>425</v>
       </c>
       <c r="B296" t="s">
-        <v>1005</v>
+        <v>998</v>
       </c>
       <c r="D296" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="E296" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="F296" t="s">
         <v>792</v>
@@ -10835,13 +10979,13 @@
         <v>425</v>
       </c>
       <c r="B297" t="s">
-        <v>1006</v>
+        <v>1549</v>
       </c>
       <c r="D297" t="s">
-        <v>221</v>
+        <v>1550</v>
       </c>
       <c r="E297" t="s">
-        <v>639</v>
+        <v>1551</v>
       </c>
       <c r="F297" t="s">
         <v>792</v>
@@ -10855,13 +10999,13 @@
         <v>425</v>
       </c>
       <c r="B298" t="s">
-        <v>1007</v>
+        <v>1327</v>
       </c>
       <c r="D298" t="s">
-        <v>222</v>
+        <v>1328</v>
       </c>
       <c r="E298" t="s">
-        <v>640</v>
+        <v>1329</v>
       </c>
       <c r="F298" t="s">
         <v>792</v>
@@ -10875,13 +11019,13 @@
         <v>425</v>
       </c>
       <c r="B299" t="s">
-        <v>1008</v>
+        <v>999</v>
       </c>
       <c r="D299" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="E299" t="s">
-        <v>641</v>
+        <v>632</v>
       </c>
       <c r="F299" t="s">
         <v>792</v>
@@ -10895,13 +11039,13 @@
         <v>425</v>
       </c>
       <c r="B300" t="s">
-        <v>1459</v>
+        <v>1186</v>
       </c>
       <c r="D300" t="s">
-        <v>1460</v>
+        <v>1134</v>
       </c>
       <c r="E300" t="s">
-        <v>1461</v>
+        <v>1238</v>
       </c>
       <c r="F300" t="s">
         <v>792</v>
@@ -10915,13 +11059,13 @@
         <v>425</v>
       </c>
       <c r="B301" t="s">
-        <v>1285</v>
+        <v>1000</v>
       </c>
       <c r="D301" t="s">
-        <v>1286</v>
+        <v>215</v>
       </c>
       <c r="E301" t="s">
-        <v>1287</v>
+        <v>633</v>
       </c>
       <c r="F301" t="s">
         <v>792</v>
@@ -10935,13 +11079,13 @@
         <v>425</v>
       </c>
       <c r="B302" t="s">
-        <v>1336</v>
+        <v>1001</v>
       </c>
       <c r="D302" t="s">
-        <v>1337</v>
+        <v>216</v>
       </c>
       <c r="E302" t="s">
-        <v>1338</v>
+        <v>634</v>
       </c>
       <c r="F302" t="s">
         <v>792</v>
@@ -10955,13 +11099,13 @@
         <v>425</v>
       </c>
       <c r="B303" t="s">
-        <v>1009</v>
+        <v>1002</v>
       </c>
       <c r="D303" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E303" t="s">
-        <v>642</v>
+        <v>635</v>
       </c>
       <c r="F303" t="s">
         <v>792</v>
@@ -10975,13 +11119,13 @@
         <v>425</v>
       </c>
       <c r="B304" t="s">
-        <v>1010</v>
+        <v>1003</v>
       </c>
       <c r="D304" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="E304" t="s">
-        <v>643</v>
+        <v>636</v>
       </c>
       <c r="F304" t="s">
         <v>792</v>
@@ -10995,13 +11139,13 @@
         <v>425</v>
       </c>
       <c r="B305" t="s">
-        <v>1011</v>
+        <v>1187</v>
       </c>
       <c r="D305" t="s">
-        <v>226</v>
+        <v>1135</v>
       </c>
       <c r="E305" t="s">
-        <v>644</v>
+        <v>1239</v>
       </c>
       <c r="F305" t="s">
         <v>792</v>
@@ -11015,13 +11159,13 @@
         <v>425</v>
       </c>
       <c r="B306" t="s">
-        <v>1188</v>
+        <v>1004</v>
       </c>
       <c r="D306" t="s">
-        <v>1136</v>
+        <v>219</v>
       </c>
       <c r="E306" t="s">
-        <v>1240</v>
+        <v>637</v>
       </c>
       <c r="F306" t="s">
         <v>792</v>
@@ -11035,13 +11179,13 @@
         <v>425</v>
       </c>
       <c r="B307" t="s">
-        <v>1012</v>
+        <v>1330</v>
       </c>
       <c r="D307" t="s">
-        <v>227</v>
+        <v>1331</v>
       </c>
       <c r="E307" t="s">
-        <v>645</v>
+        <v>1332</v>
       </c>
       <c r="F307" t="s">
         <v>792</v>
@@ -11055,13 +11199,13 @@
         <v>425</v>
       </c>
       <c r="B308" t="s">
-        <v>1504</v>
+        <v>1333</v>
       </c>
       <c r="D308" t="s">
-        <v>1505</v>
+        <v>1334</v>
       </c>
       <c r="E308" t="s">
-        <v>1506</v>
+        <v>1335</v>
       </c>
       <c r="F308" t="s">
         <v>792</v>
@@ -11075,13 +11219,13 @@
         <v>425</v>
       </c>
       <c r="B309" t="s">
-        <v>1013</v>
+        <v>1005</v>
       </c>
       <c r="D309" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="E309" t="s">
-        <v>646</v>
+        <v>638</v>
       </c>
       <c r="F309" t="s">
         <v>792</v>
@@ -11095,13 +11239,13 @@
         <v>425</v>
       </c>
       <c r="B310" t="s">
-        <v>1189</v>
+        <v>1006</v>
       </c>
       <c r="D310" t="s">
-        <v>1137</v>
+        <v>221</v>
       </c>
       <c r="E310" t="s">
-        <v>1241</v>
+        <v>639</v>
       </c>
       <c r="F310" t="s">
         <v>792</v>
@@ -11115,13 +11259,13 @@
         <v>425</v>
       </c>
       <c r="B311" t="s">
-        <v>1014</v>
+        <v>1007</v>
       </c>
       <c r="D311" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="E311" t="s">
-        <v>647</v>
+        <v>640</v>
       </c>
       <c r="F311" t="s">
         <v>792</v>
@@ -11135,13 +11279,13 @@
         <v>425</v>
       </c>
       <c r="B312" t="s">
-        <v>1015</v>
+        <v>1008</v>
       </c>
       <c r="D312" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="E312" t="s">
-        <v>648</v>
+        <v>641</v>
       </c>
       <c r="F312" t="s">
         <v>792</v>
@@ -11155,13 +11299,13 @@
         <v>425</v>
       </c>
       <c r="B313" t="s">
-        <v>1016</v>
+        <v>1459</v>
       </c>
       <c r="D313" t="s">
-        <v>231</v>
+        <v>1460</v>
       </c>
       <c r="E313" t="s">
-        <v>649</v>
+        <v>1461</v>
       </c>
       <c r="F313" t="s">
         <v>792</v>
@@ -11175,13 +11319,13 @@
         <v>425</v>
       </c>
       <c r="B314" t="s">
-        <v>1017</v>
+        <v>1285</v>
       </c>
       <c r="D314" t="s">
-        <v>232</v>
+        <v>1286</v>
       </c>
       <c r="E314" t="s">
-        <v>650</v>
+        <v>1287</v>
       </c>
       <c r="F314" t="s">
         <v>792</v>
@@ -11195,13 +11339,13 @@
         <v>425</v>
       </c>
       <c r="B315" t="s">
-        <v>1018</v>
+        <v>1336</v>
       </c>
       <c r="D315" t="s">
-        <v>233</v>
+        <v>1337</v>
       </c>
       <c r="E315" t="s">
-        <v>651</v>
+        <v>1338</v>
       </c>
       <c r="F315" t="s">
         <v>792</v>
@@ -11215,13 +11359,13 @@
         <v>425</v>
       </c>
       <c r="B316" t="s">
-        <v>1019</v>
+        <v>1009</v>
       </c>
       <c r="D316" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="E316" t="s">
-        <v>652</v>
+        <v>642</v>
       </c>
       <c r="F316" t="s">
         <v>792</v>
@@ -11235,13 +11379,13 @@
         <v>425</v>
       </c>
       <c r="B317" t="s">
-        <v>1020</v>
+        <v>1010</v>
       </c>
       <c r="D317" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="E317" t="s">
-        <v>653</v>
+        <v>643</v>
       </c>
       <c r="F317" t="s">
         <v>792</v>
@@ -11255,13 +11399,13 @@
         <v>425</v>
       </c>
       <c r="B318" t="s">
-        <v>1190</v>
+        <v>1011</v>
       </c>
       <c r="D318" t="s">
-        <v>1138</v>
+        <v>226</v>
       </c>
       <c r="E318" t="s">
-        <v>1242</v>
+        <v>644</v>
       </c>
       <c r="F318" t="s">
         <v>792</v>
@@ -11275,13 +11419,13 @@
         <v>425</v>
       </c>
       <c r="B319" t="s">
-        <v>1021</v>
+        <v>1188</v>
       </c>
       <c r="D319" t="s">
-        <v>236</v>
+        <v>1136</v>
       </c>
       <c r="E319" t="s">
-        <v>654</v>
+        <v>1240</v>
       </c>
       <c r="F319" t="s">
         <v>792</v>
@@ -11295,13 +11439,13 @@
         <v>425</v>
       </c>
       <c r="B320" t="s">
-        <v>1022</v>
+        <v>1012</v>
       </c>
       <c r="D320" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="E320" t="s">
-        <v>655</v>
+        <v>645</v>
       </c>
       <c r="F320" t="s">
         <v>792</v>
@@ -11315,13 +11459,13 @@
         <v>425</v>
       </c>
       <c r="B321" t="s">
-        <v>1023</v>
+        <v>1504</v>
       </c>
       <c r="D321" t="s">
-        <v>238</v>
+        <v>1505</v>
       </c>
       <c r="E321" t="s">
-        <v>656</v>
+        <v>1506</v>
       </c>
       <c r="F321" t="s">
         <v>792</v>
@@ -11335,13 +11479,13 @@
         <v>425</v>
       </c>
       <c r="B322" t="s">
-        <v>1191</v>
+        <v>1013</v>
       </c>
       <c r="D322" t="s">
-        <v>1139</v>
+        <v>228</v>
       </c>
       <c r="E322" t="s">
-        <v>1243</v>
+        <v>646</v>
       </c>
       <c r="F322" t="s">
         <v>792</v>
@@ -11355,13 +11499,13 @@
         <v>425</v>
       </c>
       <c r="B323" t="s">
-        <v>1024</v>
+        <v>1189</v>
       </c>
       <c r="D323" t="s">
-        <v>239</v>
+        <v>1137</v>
       </c>
       <c r="E323" t="s">
-        <v>657</v>
+        <v>1241</v>
       </c>
       <c r="F323" t="s">
         <v>792</v>
@@ -11375,13 +11519,13 @@
         <v>425</v>
       </c>
       <c r="B324" t="s">
-        <v>1025</v>
+        <v>1014</v>
       </c>
       <c r="D324" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="E324" t="s">
-        <v>658</v>
+        <v>647</v>
       </c>
       <c r="F324" t="s">
         <v>792</v>
@@ -11395,13 +11539,13 @@
         <v>425</v>
       </c>
       <c r="B325" t="s">
-        <v>1026</v>
+        <v>1015</v>
       </c>
       <c r="D325" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="E325" t="s">
-        <v>659</v>
+        <v>648</v>
       </c>
       <c r="F325" t="s">
         <v>792</v>
@@ -11415,13 +11559,13 @@
         <v>425</v>
       </c>
       <c r="B326" t="s">
-        <v>1027</v>
+        <v>1016</v>
       </c>
       <c r="D326" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="E326" t="s">
-        <v>660</v>
+        <v>649</v>
       </c>
       <c r="F326" t="s">
         <v>792</v>
@@ -11435,13 +11579,13 @@
         <v>425</v>
       </c>
       <c r="B327" t="s">
-        <v>1028</v>
+        <v>1017</v>
       </c>
       <c r="D327" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="E327" t="s">
-        <v>661</v>
+        <v>650</v>
       </c>
       <c r="F327" t="s">
         <v>792</v>
@@ -11455,13 +11599,13 @@
         <v>425</v>
       </c>
       <c r="B328" t="s">
-        <v>1029</v>
+        <v>1018</v>
       </c>
       <c r="D328" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="E328" t="s">
-        <v>662</v>
+        <v>651</v>
       </c>
       <c r="F328" t="s">
         <v>792</v>
@@ -11475,13 +11619,13 @@
         <v>425</v>
       </c>
       <c r="B329" t="s">
-        <v>1030</v>
+        <v>1019</v>
       </c>
       <c r="D329" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="E329" t="s">
-        <v>663</v>
+        <v>652</v>
       </c>
       <c r="F329" t="s">
         <v>792</v>
@@ -11495,13 +11639,13 @@
         <v>425</v>
       </c>
       <c r="B330" t="s">
-        <v>1031</v>
+        <v>1020</v>
       </c>
       <c r="D330" t="s">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="E330" t="s">
-        <v>664</v>
+        <v>653</v>
       </c>
       <c r="F330" t="s">
         <v>792</v>
@@ -11515,13 +11659,13 @@
         <v>425</v>
       </c>
       <c r="B331" t="s">
-        <v>1032</v>
+        <v>1190</v>
       </c>
       <c r="D331" t="s">
-        <v>247</v>
+        <v>1138</v>
       </c>
       <c r="E331" t="s">
-        <v>665</v>
+        <v>1242</v>
       </c>
       <c r="F331" t="s">
         <v>792</v>
@@ -11535,13 +11679,13 @@
         <v>425</v>
       </c>
       <c r="B332" t="s">
-        <v>1339</v>
+        <v>1021</v>
       </c>
       <c r="D332" t="s">
-        <v>1340</v>
+        <v>236</v>
       </c>
       <c r="E332" t="s">
-        <v>1341</v>
+        <v>654</v>
       </c>
       <c r="F332" t="s">
         <v>792</v>
@@ -11555,13 +11699,13 @@
         <v>425</v>
       </c>
       <c r="B333" t="s">
-        <v>1033</v>
+        <v>1022</v>
       </c>
       <c r="D333" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="E333" t="s">
-        <v>666</v>
+        <v>655</v>
       </c>
       <c r="F333" t="s">
         <v>792</v>
@@ -11575,13 +11719,13 @@
         <v>425</v>
       </c>
       <c r="B334" t="s">
-        <v>1034</v>
+        <v>1023</v>
       </c>
       <c r="D334" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="E334" t="s">
-        <v>667</v>
+        <v>656</v>
       </c>
       <c r="F334" t="s">
         <v>792</v>
@@ -11595,13 +11739,13 @@
         <v>425</v>
       </c>
       <c r="B335" t="s">
-        <v>1035</v>
+        <v>1191</v>
       </c>
       <c r="D335" t="s">
-        <v>250</v>
+        <v>1139</v>
       </c>
       <c r="E335" t="s">
-        <v>668</v>
+        <v>1243</v>
       </c>
       <c r="F335" t="s">
         <v>792</v>
@@ -11615,13 +11759,13 @@
         <v>425</v>
       </c>
       <c r="B336" t="s">
-        <v>1462</v>
+        <v>1024</v>
       </c>
       <c r="D336" t="s">
-        <v>1463</v>
+        <v>239</v>
       </c>
       <c r="E336" t="s">
-        <v>1464</v>
+        <v>657</v>
       </c>
       <c r="F336" t="s">
         <v>792</v>
@@ -11635,13 +11779,13 @@
         <v>425</v>
       </c>
       <c r="B337" t="s">
-        <v>1036</v>
+        <v>1025</v>
       </c>
       <c r="D337" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="E337" t="s">
-        <v>669</v>
+        <v>658</v>
       </c>
       <c r="F337" t="s">
         <v>792</v>
@@ -11655,13 +11799,13 @@
         <v>425</v>
       </c>
       <c r="B338" t="s">
-        <v>1037</v>
+        <v>1026</v>
       </c>
       <c r="D338" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="E338" t="s">
-        <v>670</v>
+        <v>659</v>
       </c>
       <c r="F338" t="s">
         <v>792</v>
@@ -11675,13 +11819,13 @@
         <v>425</v>
       </c>
       <c r="B339" t="s">
-        <v>1038</v>
+        <v>1027</v>
       </c>
       <c r="D339" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="E339" t="s">
-        <v>671</v>
+        <v>660</v>
       </c>
       <c r="F339" t="s">
         <v>792</v>
@@ -11695,13 +11839,13 @@
         <v>425</v>
       </c>
       <c r="B340" t="s">
-        <v>1465</v>
+        <v>1028</v>
       </c>
       <c r="D340" t="s">
-        <v>1466</v>
+        <v>243</v>
       </c>
       <c r="E340" t="s">
-        <v>1467</v>
+        <v>661</v>
       </c>
       <c r="F340" t="s">
         <v>792</v>
@@ -11715,13 +11859,13 @@
         <v>425</v>
       </c>
       <c r="B341" t="s">
-        <v>1039</v>
+        <v>1029</v>
       </c>
       <c r="D341" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="E341" t="s">
-        <v>672</v>
+        <v>662</v>
       </c>
       <c r="F341" t="s">
         <v>792</v>
@@ -11735,13 +11879,13 @@
         <v>425</v>
       </c>
       <c r="B342" t="s">
-        <v>1040</v>
+        <v>1030</v>
       </c>
       <c r="D342" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="E342" t="s">
-        <v>673</v>
+        <v>663</v>
       </c>
       <c r="F342" t="s">
         <v>792</v>
@@ -11755,13 +11899,13 @@
         <v>425</v>
       </c>
       <c r="B343" t="s">
-        <v>1041</v>
+        <v>1031</v>
       </c>
       <c r="D343" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="E343" t="s">
-        <v>674</v>
+        <v>664</v>
       </c>
       <c r="F343" t="s">
         <v>792</v>
@@ -11775,13 +11919,13 @@
         <v>425</v>
       </c>
       <c r="B344" t="s">
-        <v>1468</v>
+        <v>1032</v>
       </c>
       <c r="D344" t="s">
-        <v>1469</v>
+        <v>247</v>
       </c>
       <c r="E344" t="s">
-        <v>1470</v>
+        <v>665</v>
       </c>
       <c r="F344" t="s">
         <v>792</v>
@@ -11795,13 +11939,13 @@
         <v>425</v>
       </c>
       <c r="B345" t="s">
-        <v>1042</v>
+        <v>1339</v>
       </c>
       <c r="D345" t="s">
-        <v>257</v>
+        <v>1340</v>
       </c>
       <c r="E345" t="s">
-        <v>675</v>
+        <v>1341</v>
       </c>
       <c r="F345" t="s">
         <v>792</v>
@@ -11815,13 +11959,13 @@
         <v>425</v>
       </c>
       <c r="B346" t="s">
-        <v>1043</v>
+        <v>1033</v>
       </c>
       <c r="D346" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="E346" t="s">
-        <v>676</v>
+        <v>666</v>
       </c>
       <c r="F346" t="s">
         <v>792</v>
@@ -11835,13 +11979,13 @@
         <v>425</v>
       </c>
       <c r="B347" t="s">
-        <v>1471</v>
+        <v>1034</v>
       </c>
       <c r="D347" t="s">
-        <v>1472</v>
+        <v>249</v>
       </c>
       <c r="E347" t="s">
-        <v>1473</v>
+        <v>667</v>
       </c>
       <c r="F347" t="s">
         <v>792</v>
@@ -11855,13 +11999,13 @@
         <v>425</v>
       </c>
       <c r="B348" t="s">
-        <v>1044</v>
+        <v>1035</v>
       </c>
       <c r="D348" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="E348" t="s">
-        <v>677</v>
+        <v>668</v>
       </c>
       <c r="F348" t="s">
         <v>792</v>
@@ -11875,13 +12019,13 @@
         <v>425</v>
       </c>
       <c r="B349" t="s">
-        <v>1192</v>
+        <v>1462</v>
       </c>
       <c r="D349" t="s">
-        <v>1140</v>
+        <v>1463</v>
       </c>
       <c r="E349" t="s">
-        <v>1244</v>
+        <v>1464</v>
       </c>
       <c r="F349" t="s">
         <v>792</v>
@@ -11895,13 +12039,13 @@
         <v>425</v>
       </c>
       <c r="B350" t="s">
-        <v>1045</v>
+        <v>1036</v>
       </c>
       <c r="D350" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="E350" t="s">
-        <v>678</v>
+        <v>669</v>
       </c>
       <c r="F350" t="s">
         <v>792</v>
@@ -11915,13 +12059,13 @@
         <v>425</v>
       </c>
       <c r="B351" t="s">
-        <v>1046</v>
+        <v>1037</v>
       </c>
       <c r="D351" t="s">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="E351" t="s">
-        <v>679</v>
+        <v>670</v>
       </c>
       <c r="F351" t="s">
         <v>792</v>
@@ -11935,13 +12079,13 @@
         <v>425</v>
       </c>
       <c r="B352" t="s">
-        <v>1047</v>
+        <v>1038</v>
       </c>
       <c r="D352" t="s">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="E352" t="s">
-        <v>680</v>
+        <v>671</v>
       </c>
       <c r="F352" t="s">
         <v>792</v>
@@ -11955,13 +12099,13 @@
         <v>425</v>
       </c>
       <c r="B353" t="s">
-        <v>1288</v>
+        <v>1465</v>
       </c>
       <c r="D353" t="s">
-        <v>1289</v>
+        <v>1466</v>
       </c>
       <c r="E353" t="s">
-        <v>1290</v>
+        <v>1467</v>
       </c>
       <c r="F353" t="s">
         <v>792</v>
@@ -11975,13 +12119,13 @@
         <v>425</v>
       </c>
       <c r="B354" t="s">
-        <v>1048</v>
+        <v>1039</v>
       </c>
       <c r="D354" t="s">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="E354" t="s">
-        <v>681</v>
+        <v>672</v>
       </c>
       <c r="F354" t="s">
         <v>792</v>
@@ -11995,13 +12139,13 @@
         <v>425</v>
       </c>
       <c r="B355" t="s">
-        <v>1049</v>
+        <v>1040</v>
       </c>
       <c r="D355" t="s">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="E355" t="s">
-        <v>682</v>
+        <v>673</v>
       </c>
       <c r="F355" t="s">
         <v>792</v>
@@ -12015,13 +12159,13 @@
         <v>425</v>
       </c>
       <c r="B356" t="s">
-        <v>1474</v>
+        <v>1041</v>
       </c>
       <c r="D356" t="s">
-        <v>1475</v>
+        <v>256</v>
       </c>
       <c r="E356" t="s">
-        <v>1476</v>
+        <v>674</v>
       </c>
       <c r="F356" t="s">
         <v>792</v>
@@ -12035,13 +12179,13 @@
         <v>425</v>
       </c>
       <c r="B357" t="s">
-        <v>1050</v>
+        <v>1468</v>
       </c>
       <c r="D357" t="s">
-        <v>265</v>
+        <v>1469</v>
       </c>
       <c r="E357" t="s">
-        <v>683</v>
+        <v>1470</v>
       </c>
       <c r="F357" t="s">
         <v>792</v>
@@ -12055,13 +12199,13 @@
         <v>425</v>
       </c>
       <c r="B358" t="s">
-        <v>1051</v>
+        <v>1042</v>
       </c>
       <c r="D358" t="s">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="E358" t="s">
-        <v>684</v>
+        <v>675</v>
       </c>
       <c r="F358" t="s">
         <v>792</v>
@@ -12075,13 +12219,13 @@
         <v>425</v>
       </c>
       <c r="B359" t="s">
-        <v>1052</v>
+        <v>1043</v>
       </c>
       <c r="D359" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="E359" t="s">
-        <v>685</v>
+        <v>676</v>
       </c>
       <c r="F359" t="s">
         <v>792</v>
@@ -12095,13 +12239,13 @@
         <v>425</v>
       </c>
       <c r="B360" t="s">
-        <v>1053</v>
+        <v>1471</v>
       </c>
       <c r="D360" t="s">
-        <v>268</v>
+        <v>1472</v>
       </c>
       <c r="E360" t="s">
-        <v>686</v>
+        <v>1473</v>
       </c>
       <c r="F360" t="s">
         <v>792</v>
@@ -12115,13 +12259,13 @@
         <v>425</v>
       </c>
       <c r="B361" t="s">
-        <v>1054</v>
+        <v>1044</v>
       </c>
       <c r="D361" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="E361" t="s">
-        <v>687</v>
+        <v>677</v>
       </c>
       <c r="F361" t="s">
         <v>792</v>
@@ -12135,13 +12279,13 @@
         <v>425</v>
       </c>
       <c r="B362" t="s">
-        <v>1055</v>
+        <v>1192</v>
       </c>
       <c r="D362" t="s">
-        <v>270</v>
+        <v>1140</v>
       </c>
       <c r="E362" t="s">
-        <v>688</v>
+        <v>1244</v>
       </c>
       <c r="F362" t="s">
         <v>792</v>
@@ -12155,13 +12299,13 @@
         <v>425</v>
       </c>
       <c r="B363" t="s">
-        <v>1056</v>
+        <v>1045</v>
       </c>
       <c r="D363" t="s">
-        <v>271</v>
+        <v>260</v>
       </c>
       <c r="E363" t="s">
-        <v>689</v>
+        <v>678</v>
       </c>
       <c r="F363" t="s">
         <v>792</v>
@@ -12175,13 +12319,13 @@
         <v>425</v>
       </c>
       <c r="B364" t="s">
-        <v>1057</v>
+        <v>1046</v>
       </c>
       <c r="D364" t="s">
-        <v>272</v>
+        <v>261</v>
       </c>
       <c r="E364" t="s">
-        <v>690</v>
+        <v>679</v>
       </c>
       <c r="F364" t="s">
         <v>792</v>
@@ -12195,13 +12339,13 @@
         <v>425</v>
       </c>
       <c r="B365" t="s">
-        <v>1477</v>
+        <v>1047</v>
       </c>
       <c r="D365" t="s">
-        <v>1478</v>
+        <v>262</v>
       </c>
       <c r="E365" t="s">
-        <v>1479</v>
+        <v>680</v>
       </c>
       <c r="F365" t="s">
         <v>792</v>
@@ -12215,13 +12359,13 @@
         <v>425</v>
       </c>
       <c r="B366" t="s">
-        <v>1058</v>
+        <v>1288</v>
       </c>
       <c r="D366" t="s">
-        <v>273</v>
+        <v>1289</v>
       </c>
       <c r="E366" t="s">
-        <v>691</v>
+        <v>1290</v>
       </c>
       <c r="F366" t="s">
         <v>792</v>
@@ -12235,13 +12379,13 @@
         <v>425</v>
       </c>
       <c r="B367" t="s">
-        <v>1059</v>
+        <v>1048</v>
       </c>
       <c r="D367" t="s">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="E367" t="s">
-        <v>692</v>
+        <v>681</v>
       </c>
       <c r="F367" t="s">
         <v>792</v>
@@ -12255,13 +12399,13 @@
         <v>425</v>
       </c>
       <c r="B368" t="s">
-        <v>1060</v>
+        <v>1049</v>
       </c>
       <c r="D368" t="s">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="E368" t="s">
-        <v>693</v>
+        <v>682</v>
       </c>
       <c r="F368" t="s">
         <v>792</v>
@@ -12275,13 +12419,13 @@
         <v>425</v>
       </c>
       <c r="B369" t="s">
-        <v>1061</v>
+        <v>1474</v>
       </c>
       <c r="D369" t="s">
-        <v>276</v>
+        <v>1475</v>
       </c>
       <c r="E369" t="s">
-        <v>694</v>
+        <v>1476</v>
       </c>
       <c r="F369" t="s">
         <v>792</v>
@@ -12295,13 +12439,13 @@
         <v>425</v>
       </c>
       <c r="B370" t="s">
-        <v>1062</v>
+        <v>1050</v>
       </c>
       <c r="D370" t="s">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="E370" t="s">
-        <v>695</v>
+        <v>683</v>
       </c>
       <c r="F370" t="s">
         <v>792</v>
@@ -12315,13 +12459,13 @@
         <v>425</v>
       </c>
       <c r="B371" t="s">
-        <v>1063</v>
+        <v>1051</v>
       </c>
       <c r="D371" t="s">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="E371" t="s">
-        <v>696</v>
+        <v>684</v>
       </c>
       <c r="F371" t="s">
         <v>792</v>
@@ -12335,13 +12479,13 @@
         <v>425</v>
       </c>
       <c r="B372" t="s">
-        <v>1064</v>
+        <v>1052</v>
       </c>
       <c r="D372" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="E372" t="s">
-        <v>697</v>
+        <v>685</v>
       </c>
       <c r="F372" t="s">
         <v>792</v>
@@ -12355,13 +12499,13 @@
         <v>425</v>
       </c>
       <c r="B373" t="s">
-        <v>1065</v>
+        <v>1053</v>
       </c>
       <c r="D373" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="E373" t="s">
-        <v>698</v>
+        <v>686</v>
       </c>
       <c r="F373" t="s">
         <v>792</v>
@@ -12375,13 +12519,13 @@
         <v>425</v>
       </c>
       <c r="B374" t="s">
-        <v>1066</v>
+        <v>1054</v>
       </c>
       <c r="D374" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="E374" t="s">
-        <v>699</v>
+        <v>687</v>
       </c>
       <c r="F374" t="s">
         <v>792</v>
@@ -12395,13 +12539,13 @@
         <v>425</v>
       </c>
       <c r="B375" t="s">
-        <v>1067</v>
+        <v>1055</v>
       </c>
       <c r="D375" t="s">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="E375" t="s">
-        <v>700</v>
+        <v>688</v>
       </c>
       <c r="F375" t="s">
         <v>792</v>
@@ -12415,13 +12559,13 @@
         <v>425</v>
       </c>
       <c r="B376" t="s">
-        <v>1068</v>
+        <v>1056</v>
       </c>
       <c r="D376" t="s">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="E376" t="s">
-        <v>701</v>
+        <v>689</v>
       </c>
       <c r="F376" t="s">
         <v>792</v>
@@ -12435,13 +12579,13 @@
         <v>425</v>
       </c>
       <c r="B377" t="s">
-        <v>1069</v>
+        <v>1057</v>
       </c>
       <c r="D377" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="E377" t="s">
-        <v>702</v>
+        <v>690</v>
       </c>
       <c r="F377" t="s">
         <v>792</v>
@@ -12455,13 +12599,13 @@
         <v>425</v>
       </c>
       <c r="B378" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
       <c r="D378" t="s">
-        <v>1481</v>
+        <v>1478</v>
       </c>
       <c r="E378" t="s">
-        <v>1482</v>
+        <v>1479</v>
       </c>
       <c r="F378" t="s">
         <v>792</v>
@@ -12475,13 +12619,13 @@
         <v>425</v>
       </c>
       <c r="B379" t="s">
-        <v>1070</v>
+        <v>1058</v>
       </c>
       <c r="D379" t="s">
-        <v>285</v>
+        <v>273</v>
       </c>
       <c r="E379" t="s">
-        <v>703</v>
+        <v>691</v>
       </c>
       <c r="F379" t="s">
         <v>792</v>
@@ -12495,13 +12639,13 @@
         <v>425</v>
       </c>
       <c r="B380" t="s">
-        <v>1342</v>
+        <v>1059</v>
       </c>
       <c r="D380" t="s">
-        <v>1343</v>
+        <v>274</v>
       </c>
       <c r="E380" t="s">
-        <v>1344</v>
+        <v>692</v>
       </c>
       <c r="F380" t="s">
         <v>792</v>
@@ -12515,13 +12659,13 @@
         <v>425</v>
       </c>
       <c r="B381" t="s">
-        <v>1071</v>
+        <v>1060</v>
       </c>
       <c r="D381" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="E381" t="s">
-        <v>704</v>
+        <v>693</v>
       </c>
       <c r="F381" t="s">
         <v>792</v>
@@ -12535,13 +12679,13 @@
         <v>425</v>
       </c>
       <c r="B382" t="s">
-        <v>1072</v>
+        <v>1061</v>
       </c>
       <c r="D382" t="s">
-        <v>287</v>
+        <v>276</v>
       </c>
       <c r="E382" t="s">
-        <v>705</v>
+        <v>694</v>
       </c>
       <c r="F382" t="s">
         <v>792</v>
@@ -12555,13 +12699,13 @@
         <v>425</v>
       </c>
       <c r="B383" t="s">
-        <v>1193</v>
+        <v>1062</v>
       </c>
       <c r="D383" t="s">
-        <v>1141</v>
+        <v>277</v>
       </c>
       <c r="E383" t="s">
-        <v>1245</v>
+        <v>695</v>
       </c>
       <c r="F383" t="s">
         <v>792</v>
@@ -12575,13 +12719,13 @@
         <v>425</v>
       </c>
       <c r="B384" t="s">
-        <v>1073</v>
+        <v>1063</v>
       </c>
       <c r="D384" t="s">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="E384" t="s">
-        <v>706</v>
+        <v>696</v>
       </c>
       <c r="F384" t="s">
         <v>792</v>
@@ -12595,13 +12739,13 @@
         <v>425</v>
       </c>
       <c r="B385" t="s">
-        <v>1074</v>
+        <v>1064</v>
       </c>
       <c r="D385" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="E385" t="s">
-        <v>707</v>
+        <v>697</v>
       </c>
       <c r="F385" t="s">
         <v>792</v>
@@ -12615,13 +12759,13 @@
         <v>425</v>
       </c>
       <c r="B386" t="s">
-        <v>1075</v>
+        <v>1065</v>
       </c>
       <c r="D386" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="E386" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="F386" t="s">
         <v>792</v>
@@ -12635,13 +12779,13 @@
         <v>425</v>
       </c>
       <c r="B387" t="s">
-        <v>1076</v>
+        <v>1552</v>
       </c>
       <c r="D387" t="s">
-        <v>291</v>
+        <v>1553</v>
       </c>
       <c r="E387" t="s">
-        <v>709</v>
+        <v>1554</v>
       </c>
       <c r="F387" t="s">
         <v>792</v>
@@ -12655,13 +12799,13 @@
         <v>425</v>
       </c>
       <c r="B388" t="s">
-        <v>1077</v>
+        <v>1066</v>
       </c>
       <c r="D388" t="s">
-        <v>292</v>
+        <v>281</v>
       </c>
       <c r="E388" t="s">
-        <v>710</v>
+        <v>699</v>
       </c>
       <c r="F388" t="s">
         <v>792</v>
@@ -12675,13 +12819,13 @@
         <v>425</v>
       </c>
       <c r="B389" t="s">
-        <v>1078</v>
+        <v>1067</v>
       </c>
       <c r="D389" t="s">
-        <v>293</v>
+        <v>282</v>
       </c>
       <c r="E389" t="s">
-        <v>711</v>
+        <v>700</v>
       </c>
       <c r="F389" t="s">
         <v>792</v>
@@ -12695,13 +12839,13 @@
         <v>425</v>
       </c>
       <c r="B390" t="s">
-        <v>1194</v>
+        <v>1068</v>
       </c>
       <c r="D390" t="s">
-        <v>1142</v>
+        <v>283</v>
       </c>
       <c r="E390" t="s">
-        <v>1246</v>
+        <v>701</v>
       </c>
       <c r="F390" t="s">
         <v>792</v>
@@ -12715,13 +12859,13 @@
         <v>425</v>
       </c>
       <c r="B391" t="s">
-        <v>1079</v>
+        <v>1069</v>
       </c>
       <c r="D391" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="E391" t="s">
-        <v>712</v>
+        <v>702</v>
       </c>
       <c r="F391" t="s">
         <v>792</v>
@@ -12735,13 +12879,13 @@
         <v>425</v>
       </c>
       <c r="B392" t="s">
-        <v>1080</v>
+        <v>1480</v>
       </c>
       <c r="D392" t="s">
-        <v>295</v>
+        <v>1481</v>
       </c>
       <c r="E392" t="s">
-        <v>713</v>
+        <v>1482</v>
       </c>
       <c r="F392" t="s">
         <v>792</v>
@@ -12755,13 +12899,13 @@
         <v>425</v>
       </c>
       <c r="B393" t="s">
-        <v>1081</v>
+        <v>1070</v>
       </c>
       <c r="D393" t="s">
-        <v>296</v>
+        <v>285</v>
       </c>
       <c r="E393" t="s">
-        <v>714</v>
+        <v>703</v>
       </c>
       <c r="F393" t="s">
         <v>792</v>
@@ -12775,13 +12919,13 @@
         <v>425</v>
       </c>
       <c r="B394" t="s">
-        <v>1082</v>
+        <v>1342</v>
       </c>
       <c r="D394" t="s">
-        <v>297</v>
+        <v>1343</v>
       </c>
       <c r="E394" t="s">
-        <v>715</v>
+        <v>1344</v>
       </c>
       <c r="F394" t="s">
         <v>792</v>
@@ -12795,13 +12939,13 @@
         <v>425</v>
       </c>
       <c r="B395" t="s">
-        <v>1195</v>
+        <v>1071</v>
       </c>
       <c r="D395" t="s">
-        <v>1143</v>
+        <v>286</v>
       </c>
       <c r="E395" t="s">
-        <v>1247</v>
+        <v>704</v>
       </c>
       <c r="F395" t="s">
         <v>792</v>
@@ -12815,13 +12959,13 @@
         <v>425</v>
       </c>
       <c r="B396" t="s">
-        <v>1083</v>
+        <v>1072</v>
       </c>
       <c r="D396" t="s">
-        <v>298</v>
+        <v>287</v>
       </c>
       <c r="E396" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F396" t="s">
         <v>792</v>
@@ -12835,13 +12979,13 @@
         <v>425</v>
       </c>
       <c r="B397" t="s">
-        <v>1084</v>
+        <v>1193</v>
       </c>
       <c r="D397" t="s">
-        <v>299</v>
+        <v>1141</v>
       </c>
       <c r="E397" t="s">
-        <v>717</v>
+        <v>1245</v>
       </c>
       <c r="F397" t="s">
         <v>792</v>
@@ -12855,13 +12999,13 @@
         <v>425</v>
       </c>
       <c r="B398" t="s">
-        <v>1085</v>
+        <v>1073</v>
       </c>
       <c r="D398" t="s">
-        <v>300</v>
+        <v>288</v>
       </c>
       <c r="E398" t="s">
-        <v>718</v>
+        <v>706</v>
       </c>
       <c r="F398" t="s">
         <v>792</v>
@@ -12875,13 +13019,13 @@
         <v>425</v>
       </c>
       <c r="B399" t="s">
-        <v>1345</v>
+        <v>1074</v>
       </c>
       <c r="D399" t="s">
-        <v>1346</v>
+        <v>289</v>
       </c>
       <c r="E399" t="s">
-        <v>1347</v>
+        <v>707</v>
       </c>
       <c r="F399" t="s">
         <v>792</v>
@@ -12895,13 +13039,13 @@
         <v>425</v>
       </c>
       <c r="B400" t="s">
-        <v>1196</v>
+        <v>1075</v>
       </c>
       <c r="D400" t="s">
-        <v>1144</v>
+        <v>290</v>
       </c>
       <c r="E400" t="s">
-        <v>1248</v>
+        <v>708</v>
       </c>
       <c r="F400" t="s">
         <v>792</v>
@@ -12915,13 +13059,13 @@
         <v>425</v>
       </c>
       <c r="B401" t="s">
-        <v>1197</v>
+        <v>1076</v>
       </c>
       <c r="D401" t="s">
-        <v>1145</v>
+        <v>291</v>
       </c>
       <c r="E401" t="s">
-        <v>1249</v>
+        <v>709</v>
       </c>
       <c r="F401" t="s">
         <v>792</v>
@@ -12935,13 +13079,13 @@
         <v>425</v>
       </c>
       <c r="B402" t="s">
-        <v>1483</v>
+        <v>1077</v>
       </c>
       <c r="D402" t="s">
-        <v>1484</v>
+        <v>292</v>
       </c>
       <c r="E402" t="s">
-        <v>1485</v>
+        <v>710</v>
       </c>
       <c r="F402" t="s">
         <v>792</v>
@@ -12955,13 +13099,13 @@
         <v>425</v>
       </c>
       <c r="B403" t="s">
-        <v>1198</v>
+        <v>1078</v>
       </c>
       <c r="D403" t="s">
-        <v>1146</v>
+        <v>293</v>
       </c>
       <c r="E403" t="s">
-        <v>1250</v>
+        <v>711</v>
       </c>
       <c r="F403" t="s">
         <v>792</v>
@@ -12975,13 +13119,13 @@
         <v>425</v>
       </c>
       <c r="B404" t="s">
-        <v>1086</v>
+        <v>1194</v>
       </c>
       <c r="D404" t="s">
-        <v>301</v>
+        <v>1142</v>
       </c>
       <c r="E404" t="s">
-        <v>719</v>
+        <v>1246</v>
       </c>
       <c r="F404" t="s">
         <v>792</v>
@@ -12995,13 +13139,13 @@
         <v>425</v>
       </c>
       <c r="B405" t="s">
-        <v>1087</v>
+        <v>1079</v>
       </c>
       <c r="D405" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="E405" t="s">
-        <v>720</v>
+        <v>712</v>
       </c>
       <c r="F405" t="s">
         <v>792</v>
@@ -13015,13 +13159,13 @@
         <v>425</v>
       </c>
       <c r="B406" t="s">
-        <v>1088</v>
+        <v>1080</v>
       </c>
       <c r="D406" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="E406" t="s">
-        <v>721</v>
+        <v>713</v>
       </c>
       <c r="F406" t="s">
         <v>792</v>
@@ -13035,13 +13179,13 @@
         <v>425</v>
       </c>
       <c r="B407" t="s">
-        <v>1089</v>
+        <v>1081</v>
       </c>
       <c r="D407" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="E407" t="s">
-        <v>722</v>
+        <v>714</v>
       </c>
       <c r="F407" t="s">
         <v>792</v>
@@ -13055,13 +13199,13 @@
         <v>425</v>
       </c>
       <c r="B408" t="s">
-        <v>1199</v>
+        <v>1082</v>
       </c>
       <c r="D408" t="s">
-        <v>1147</v>
+        <v>297</v>
       </c>
       <c r="E408" t="s">
-        <v>1251</v>
+        <v>715</v>
       </c>
       <c r="F408" t="s">
         <v>792</v>
@@ -13075,13 +13219,13 @@
         <v>425</v>
       </c>
       <c r="B409" t="s">
-        <v>1294</v>
+        <v>1195</v>
       </c>
       <c r="D409" t="s">
-        <v>1295</v>
+        <v>1143</v>
       </c>
       <c r="E409" t="s">
-        <v>1296</v>
+        <v>1247</v>
       </c>
       <c r="F409" t="s">
         <v>792</v>
@@ -13095,13 +13239,13 @@
         <v>425</v>
       </c>
       <c r="B410" t="s">
-        <v>1090</v>
+        <v>1083</v>
       </c>
       <c r="D410" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="E410" t="s">
-        <v>723</v>
+        <v>716</v>
       </c>
       <c r="F410" t="s">
         <v>792</v>
@@ -13115,13 +13259,13 @@
         <v>425</v>
       </c>
       <c r="B411" t="s">
-        <v>1486</v>
+        <v>1084</v>
       </c>
       <c r="D411" t="s">
-        <v>1487</v>
+        <v>299</v>
       </c>
       <c r="E411" t="s">
-        <v>1488</v>
+        <v>717</v>
       </c>
       <c r="F411" t="s">
         <v>792</v>
@@ -13135,13 +13279,13 @@
         <v>425</v>
       </c>
       <c r="B412" t="s">
-        <v>1091</v>
+        <v>1085</v>
       </c>
       <c r="D412" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="E412" t="s">
-        <v>724</v>
+        <v>718</v>
       </c>
       <c r="F412" t="s">
         <v>792</v>
@@ -13155,13 +13299,13 @@
         <v>425</v>
       </c>
       <c r="B413" t="s">
-        <v>1092</v>
+        <v>1345</v>
       </c>
       <c r="D413" t="s">
-        <v>307</v>
+        <v>1346</v>
       </c>
       <c r="E413" t="s">
-        <v>725</v>
+        <v>1347</v>
       </c>
       <c r="F413" t="s">
         <v>792</v>
@@ -13175,13 +13319,13 @@
         <v>425</v>
       </c>
       <c r="B414" t="s">
-        <v>1093</v>
+        <v>1196</v>
       </c>
       <c r="D414" t="s">
-        <v>308</v>
+        <v>1144</v>
       </c>
       <c r="E414" t="s">
-        <v>726</v>
+        <v>1248</v>
       </c>
       <c r="F414" t="s">
         <v>792</v>
@@ -13195,13 +13339,13 @@
         <v>425</v>
       </c>
       <c r="B415" t="s">
-        <v>1094</v>
+        <v>1197</v>
       </c>
       <c r="D415" t="s">
-        <v>309</v>
+        <v>1145</v>
       </c>
       <c r="E415" t="s">
-        <v>727</v>
+        <v>1249</v>
       </c>
       <c r="F415" t="s">
         <v>792</v>
@@ -13215,13 +13359,13 @@
         <v>425</v>
       </c>
       <c r="B416" t="s">
-        <v>1095</v>
+        <v>1483</v>
       </c>
       <c r="D416" t="s">
-        <v>310</v>
+        <v>1484</v>
       </c>
       <c r="E416" t="s">
-        <v>728</v>
+        <v>1485</v>
       </c>
       <c r="F416" t="s">
         <v>792</v>
@@ -13235,13 +13379,13 @@
         <v>425</v>
       </c>
       <c r="B417" t="s">
-        <v>1291</v>
+        <v>1198</v>
       </c>
       <c r="D417" t="s">
-        <v>1292</v>
+        <v>1146</v>
       </c>
       <c r="E417" t="s">
-        <v>1293</v>
+        <v>1250</v>
       </c>
       <c r="F417" t="s">
         <v>792</v>
@@ -13255,13 +13399,13 @@
         <v>425</v>
       </c>
       <c r="B418" t="s">
-        <v>1200</v>
+        <v>1086</v>
       </c>
       <c r="D418" t="s">
-        <v>1148</v>
+        <v>301</v>
       </c>
       <c r="E418" t="s">
-        <v>1252</v>
+        <v>719</v>
       </c>
       <c r="F418" t="s">
         <v>792</v>
@@ -13275,13 +13419,13 @@
         <v>425</v>
       </c>
       <c r="B419" t="s">
-        <v>1096</v>
+        <v>1087</v>
       </c>
       <c r="D419" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="E419" t="s">
-        <v>729</v>
+        <v>720</v>
       </c>
       <c r="F419" t="s">
         <v>792</v>
@@ -13295,13 +13439,13 @@
         <v>425</v>
       </c>
       <c r="B420" t="s">
-        <v>1348</v>
+        <v>1088</v>
       </c>
       <c r="D420" t="s">
-        <v>1349</v>
+        <v>303</v>
       </c>
       <c r="E420" t="s">
-        <v>1350</v>
+        <v>721</v>
       </c>
       <c r="F420" t="s">
         <v>792</v>
@@ -13315,13 +13459,13 @@
         <v>425</v>
       </c>
       <c r="B421" t="s">
-        <v>1097</v>
+        <v>1089</v>
       </c>
       <c r="D421" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="E421" t="s">
-        <v>730</v>
+        <v>722</v>
       </c>
       <c r="F421" t="s">
         <v>792</v>
@@ -13335,13 +13479,13 @@
         <v>425</v>
       </c>
       <c r="B422" t="s">
-        <v>1098</v>
+        <v>1199</v>
       </c>
       <c r="D422" t="s">
-        <v>313</v>
+        <v>1147</v>
       </c>
       <c r="E422" t="s">
-        <v>731</v>
+        <v>1251</v>
       </c>
       <c r="F422" t="s">
         <v>792</v>
@@ -13355,13 +13499,13 @@
         <v>425</v>
       </c>
       <c r="B423" t="s">
-        <v>1099</v>
+        <v>1294</v>
       </c>
       <c r="D423" t="s">
-        <v>314</v>
+        <v>1295</v>
       </c>
       <c r="E423" t="s">
-        <v>732</v>
+        <v>1296</v>
       </c>
       <c r="F423" t="s">
         <v>792</v>
@@ -13375,13 +13519,13 @@
         <v>425</v>
       </c>
       <c r="B424" t="s">
-        <v>1100</v>
+        <v>1090</v>
       </c>
       <c r="D424" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="E424" t="s">
-        <v>733</v>
+        <v>723</v>
       </c>
       <c r="F424" t="s">
         <v>792</v>
@@ -13395,13 +13539,13 @@
         <v>425</v>
       </c>
       <c r="B425" t="s">
-        <v>1101</v>
+        <v>1486</v>
       </c>
       <c r="D425" t="s">
-        <v>316</v>
+        <v>1487</v>
       </c>
       <c r="E425" t="s">
-        <v>734</v>
+        <v>1488</v>
       </c>
       <c r="F425" t="s">
         <v>792</v>
@@ -13415,13 +13559,13 @@
         <v>425</v>
       </c>
       <c r="B426" t="s">
-        <v>1102</v>
+        <v>1091</v>
       </c>
       <c r="D426" t="s">
-        <v>317</v>
+        <v>306</v>
       </c>
       <c r="E426" t="s">
-        <v>735</v>
+        <v>724</v>
       </c>
       <c r="F426" t="s">
         <v>792</v>
@@ -13435,13 +13579,13 @@
         <v>425</v>
       </c>
       <c r="B427" t="s">
-        <v>1103</v>
+        <v>1092</v>
       </c>
       <c r="D427" t="s">
-        <v>318</v>
+        <v>307</v>
       </c>
       <c r="E427" t="s">
-        <v>736</v>
+        <v>725</v>
       </c>
       <c r="F427" t="s">
         <v>792</v>
@@ -13455,13 +13599,13 @@
         <v>425</v>
       </c>
       <c r="B428" t="s">
-        <v>1104</v>
+        <v>1093</v>
       </c>
       <c r="D428" t="s">
-        <v>319</v>
+        <v>308</v>
       </c>
       <c r="E428" t="s">
-        <v>737</v>
+        <v>726</v>
       </c>
       <c r="F428" t="s">
         <v>792</v>
@@ -13475,13 +13619,13 @@
         <v>425</v>
       </c>
       <c r="B429" t="s">
-        <v>1489</v>
+        <v>1094</v>
       </c>
       <c r="D429" t="s">
-        <v>1490</v>
+        <v>309</v>
       </c>
       <c r="E429" t="s">
-        <v>1491</v>
+        <v>727</v>
       </c>
       <c r="F429" t="s">
         <v>792</v>
@@ -13495,13 +13639,13 @@
         <v>425</v>
       </c>
       <c r="B430" t="s">
-        <v>1105</v>
+        <v>1095</v>
       </c>
       <c r="D430" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="E430" t="s">
-        <v>738</v>
+        <v>728</v>
       </c>
       <c r="F430" t="s">
         <v>792</v>
@@ -13515,13 +13659,13 @@
         <v>425</v>
       </c>
       <c r="B431" t="s">
-        <v>1106</v>
+        <v>1291</v>
       </c>
       <c r="D431" t="s">
-        <v>321</v>
+        <v>1292</v>
       </c>
       <c r="E431" t="s">
-        <v>739</v>
+        <v>1293</v>
       </c>
       <c r="F431" t="s">
         <v>792</v>
@@ -13535,13 +13679,13 @@
         <v>425</v>
       </c>
       <c r="B432" t="s">
-        <v>1107</v>
+        <v>1200</v>
       </c>
       <c r="D432" t="s">
-        <v>322</v>
+        <v>1148</v>
       </c>
       <c r="E432" t="s">
-        <v>740</v>
+        <v>1252</v>
       </c>
       <c r="F432" t="s">
         <v>792</v>
@@ -13555,13 +13699,13 @@
         <v>425</v>
       </c>
       <c r="B433" t="s">
-        <v>374</v>
+        <v>1096</v>
       </c>
       <c r="D433" t="s">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="E433" t="s">
-        <v>741</v>
+        <v>729</v>
       </c>
       <c r="F433" t="s">
         <v>792</v>
@@ -13575,13 +13719,13 @@
         <v>425</v>
       </c>
       <c r="B434" t="s">
-        <v>1201</v>
+        <v>1348</v>
       </c>
       <c r="D434" t="s">
-        <v>1149</v>
+        <v>1349</v>
       </c>
       <c r="E434" t="s">
-        <v>1253</v>
+        <v>1350</v>
       </c>
       <c r="F434" t="s">
         <v>792</v>
@@ -13595,13 +13739,13 @@
         <v>425</v>
       </c>
       <c r="B435" t="s">
-        <v>375</v>
+        <v>1097</v>
       </c>
       <c r="D435" t="s">
-        <v>324</v>
+        <v>312</v>
       </c>
       <c r="E435" t="s">
-        <v>742</v>
+        <v>730</v>
       </c>
       <c r="F435" t="s">
         <v>792</v>
@@ -13615,13 +13759,13 @@
         <v>425</v>
       </c>
       <c r="B436" t="s">
-        <v>1492</v>
+        <v>1098</v>
       </c>
       <c r="D436" t="s">
-        <v>1493</v>
+        <v>313</v>
       </c>
       <c r="E436" t="s">
-        <v>1494</v>
+        <v>731</v>
       </c>
       <c r="F436" t="s">
         <v>792</v>
@@ -13635,13 +13779,13 @@
         <v>425</v>
       </c>
       <c r="B437" t="s">
-        <v>376</v>
+        <v>1099</v>
       </c>
       <c r="D437" t="s">
-        <v>325</v>
+        <v>314</v>
       </c>
       <c r="E437" t="s">
-        <v>743</v>
+        <v>732</v>
       </c>
       <c r="F437" t="s">
         <v>792</v>
@@ -13655,13 +13799,13 @@
         <v>425</v>
       </c>
       <c r="B438" t="s">
-        <v>377</v>
+        <v>1100</v>
       </c>
       <c r="D438" t="s">
-        <v>326</v>
+        <v>315</v>
       </c>
       <c r="E438" t="s">
-        <v>744</v>
+        <v>733</v>
       </c>
       <c r="F438" t="s">
         <v>792</v>
@@ -13675,13 +13819,13 @@
         <v>425</v>
       </c>
       <c r="B439" t="s">
-        <v>378</v>
+        <v>1101</v>
       </c>
       <c r="D439" t="s">
-        <v>327</v>
+        <v>316</v>
       </c>
       <c r="E439" t="s">
-        <v>745</v>
+        <v>734</v>
       </c>
       <c r="F439" t="s">
         <v>792</v>
@@ -13695,13 +13839,13 @@
         <v>425</v>
       </c>
       <c r="B440" t="s">
-        <v>379</v>
+        <v>1102</v>
       </c>
       <c r="D440" t="s">
-        <v>328</v>
+        <v>317</v>
       </c>
       <c r="E440" t="s">
-        <v>746</v>
+        <v>735</v>
       </c>
       <c r="F440" t="s">
         <v>792</v>
@@ -13715,13 +13859,13 @@
         <v>425</v>
       </c>
       <c r="B441" t="s">
-        <v>380</v>
+        <v>1103</v>
       </c>
       <c r="D441" t="s">
-        <v>329</v>
+        <v>318</v>
       </c>
       <c r="E441" t="s">
-        <v>747</v>
+        <v>736</v>
       </c>
       <c r="F441" t="s">
         <v>792</v>
@@ -13735,13 +13879,13 @@
         <v>425</v>
       </c>
       <c r="B442" t="s">
-        <v>381</v>
+        <v>1104</v>
       </c>
       <c r="D442" t="s">
-        <v>330</v>
+        <v>319</v>
       </c>
       <c r="E442" t="s">
-        <v>748</v>
+        <v>737</v>
       </c>
       <c r="F442" t="s">
         <v>792</v>
@@ -13755,13 +13899,13 @@
         <v>425</v>
       </c>
       <c r="B443" t="s">
-        <v>382</v>
+        <v>1489</v>
       </c>
       <c r="D443" t="s">
-        <v>331</v>
+        <v>1490</v>
       </c>
       <c r="E443" t="s">
-        <v>749</v>
+        <v>1491</v>
       </c>
       <c r="F443" t="s">
         <v>792</v>
@@ -13775,13 +13919,13 @@
         <v>425</v>
       </c>
       <c r="B444" t="s">
-        <v>1351</v>
+        <v>1105</v>
       </c>
       <c r="D444" t="s">
-        <v>1352</v>
+        <v>320</v>
       </c>
       <c r="E444" t="s">
-        <v>1353</v>
+        <v>738</v>
       </c>
       <c r="F444" t="s">
         <v>792</v>
@@ -13795,13 +13939,13 @@
         <v>425</v>
       </c>
       <c r="B445" t="s">
-        <v>383</v>
+        <v>1106</v>
       </c>
       <c r="D445" t="s">
-        <v>332</v>
+        <v>321</v>
       </c>
       <c r="E445" t="s">
-        <v>750</v>
+        <v>739</v>
       </c>
       <c r="F445" t="s">
         <v>792</v>
@@ -13815,13 +13959,13 @@
         <v>425</v>
       </c>
       <c r="B446" t="s">
-        <v>1202</v>
+        <v>1107</v>
       </c>
       <c r="D446" t="s">
-        <v>1150</v>
+        <v>322</v>
       </c>
       <c r="E446" t="s">
-        <v>1254</v>
+        <v>740</v>
       </c>
       <c r="F446" t="s">
         <v>792</v>
@@ -13835,13 +13979,13 @@
         <v>425</v>
       </c>
       <c r="B447" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="D447" t="s">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="E447" t="s">
-        <v>751</v>
+        <v>741</v>
       </c>
       <c r="F447" t="s">
         <v>792</v>
@@ -13855,13 +13999,13 @@
         <v>425</v>
       </c>
       <c r="B448" t="s">
-        <v>385</v>
+        <v>1201</v>
       </c>
       <c r="D448" t="s">
-        <v>334</v>
+        <v>1149</v>
       </c>
       <c r="E448" t="s">
-        <v>752</v>
+        <v>1253</v>
       </c>
       <c r="F448" t="s">
         <v>792</v>
@@ -13875,13 +14019,13 @@
         <v>425</v>
       </c>
       <c r="B449" t="s">
-        <v>386</v>
+        <v>375</v>
       </c>
       <c r="D449" t="s">
-        <v>335</v>
+        <v>324</v>
       </c>
       <c r="E449" t="s">
-        <v>753</v>
+        <v>742</v>
       </c>
       <c r="F449" t="s">
         <v>792</v>
@@ -13895,13 +14039,13 @@
         <v>425</v>
       </c>
       <c r="B450" t="s">
-        <v>1203</v>
+        <v>1492</v>
       </c>
       <c r="D450" t="s">
-        <v>1151</v>
+        <v>1493</v>
       </c>
       <c r="E450" t="s">
-        <v>1255</v>
+        <v>1494</v>
       </c>
       <c r="F450" t="s">
         <v>792</v>
@@ -13915,13 +14059,13 @@
         <v>425</v>
       </c>
       <c r="B451" t="s">
-        <v>387</v>
+        <v>376</v>
       </c>
       <c r="D451" t="s">
-        <v>336</v>
+        <v>325</v>
       </c>
       <c r="E451" t="s">
-        <v>754</v>
+        <v>743</v>
       </c>
       <c r="F451" t="s">
         <v>792</v>
@@ -13935,13 +14079,13 @@
         <v>425</v>
       </c>
       <c r="B452" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="D452" t="s">
-        <v>337</v>
+        <v>326</v>
       </c>
       <c r="E452" t="s">
-        <v>755</v>
+        <v>744</v>
       </c>
       <c r="F452" t="s">
         <v>792</v>
@@ -13955,13 +14099,13 @@
         <v>425</v>
       </c>
       <c r="B453" t="s">
-        <v>389</v>
+        <v>378</v>
       </c>
       <c r="D453" t="s">
-        <v>338</v>
+        <v>327</v>
       </c>
       <c r="E453" t="s">
-        <v>756</v>
+        <v>745</v>
       </c>
       <c r="F453" t="s">
         <v>792</v>
@@ -13975,13 +14119,13 @@
         <v>425</v>
       </c>
       <c r="B454" t="s">
-        <v>1510</v>
+        <v>379</v>
       </c>
       <c r="D454" t="s">
-        <v>1511</v>
+        <v>328</v>
       </c>
       <c r="E454" t="s">
-        <v>1512</v>
+        <v>746</v>
       </c>
       <c r="F454" t="s">
         <v>792</v>
@@ -13995,13 +14139,13 @@
         <v>425</v>
       </c>
       <c r="B455" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="D455" t="s">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="E455" t="s">
-        <v>757</v>
+        <v>747</v>
       </c>
       <c r="F455" t="s">
         <v>792</v>
@@ -14015,13 +14159,13 @@
         <v>425</v>
       </c>
       <c r="B456" t="s">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="D456" t="s">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="E456" t="s">
-        <v>758</v>
+        <v>748</v>
       </c>
       <c r="F456" t="s">
         <v>792</v>
@@ -14035,13 +14179,13 @@
         <v>425</v>
       </c>
       <c r="B457" t="s">
-        <v>392</v>
+        <v>1555</v>
       </c>
       <c r="D457" t="s">
-        <v>341</v>
+        <v>1556</v>
       </c>
       <c r="E457" t="s">
-        <v>759</v>
+        <v>1557</v>
       </c>
       <c r="F457" t="s">
         <v>792</v>
@@ -14055,13 +14199,13 @@
         <v>425</v>
       </c>
       <c r="B458" t="s">
-        <v>1204</v>
+        <v>382</v>
       </c>
       <c r="D458" t="s">
-        <v>1152</v>
+        <v>331</v>
       </c>
       <c r="E458" t="s">
-        <v>1256</v>
+        <v>749</v>
       </c>
       <c r="F458" t="s">
         <v>792</v>
@@ -14075,13 +14219,13 @@
         <v>425</v>
       </c>
       <c r="B459" t="s">
-        <v>393</v>
+        <v>1351</v>
       </c>
       <c r="D459" t="s">
-        <v>342</v>
+        <v>1352</v>
       </c>
       <c r="E459" t="s">
-        <v>760</v>
+        <v>1353</v>
       </c>
       <c r="F459" t="s">
         <v>792</v>
@@ -14095,13 +14239,13 @@
         <v>425</v>
       </c>
       <c r="B460" t="s">
-        <v>394</v>
+        <v>383</v>
       </c>
       <c r="D460" t="s">
-        <v>343</v>
+        <v>332</v>
       </c>
       <c r="E460" t="s">
-        <v>761</v>
+        <v>750</v>
       </c>
       <c r="F460" t="s">
         <v>792</v>
@@ -14115,13 +14259,13 @@
         <v>425</v>
       </c>
       <c r="B461" t="s">
-        <v>395</v>
+        <v>1202</v>
       </c>
       <c r="D461" t="s">
-        <v>344</v>
+        <v>1150</v>
       </c>
       <c r="E461" t="s">
-        <v>762</v>
+        <v>1254</v>
       </c>
       <c r="F461" t="s">
         <v>792</v>
@@ -14135,13 +14279,13 @@
         <v>425</v>
       </c>
       <c r="B462" t="s">
-        <v>1205</v>
+        <v>384</v>
       </c>
       <c r="D462" t="s">
-        <v>1153</v>
+        <v>333</v>
       </c>
       <c r="E462" t="s">
-        <v>1257</v>
+        <v>751</v>
       </c>
       <c r="F462" t="s">
         <v>792</v>
@@ -14155,13 +14299,13 @@
         <v>425</v>
       </c>
       <c r="B463" t="s">
-        <v>396</v>
+        <v>385</v>
       </c>
       <c r="D463" t="s">
-        <v>345</v>
+        <v>334</v>
       </c>
       <c r="E463" t="s">
-        <v>763</v>
+        <v>752</v>
       </c>
       <c r="F463" t="s">
         <v>792</v>
@@ -14175,13 +14319,13 @@
         <v>425</v>
       </c>
       <c r="B464" t="s">
-        <v>1206</v>
+        <v>386</v>
       </c>
       <c r="D464" t="s">
-        <v>1154</v>
+        <v>335</v>
       </c>
       <c r="E464" t="s">
-        <v>1258</v>
+        <v>753</v>
       </c>
       <c r="F464" t="s">
         <v>792</v>
@@ -14195,13 +14339,13 @@
         <v>425</v>
       </c>
       <c r="B465" t="s">
-        <v>397</v>
+        <v>1203</v>
       </c>
       <c r="D465" t="s">
-        <v>346</v>
+        <v>1151</v>
       </c>
       <c r="E465" t="s">
-        <v>764</v>
+        <v>1255</v>
       </c>
       <c r="F465" t="s">
         <v>792</v>
@@ -14215,13 +14359,13 @@
         <v>425</v>
       </c>
       <c r="B466" t="s">
-        <v>398</v>
+        <v>387</v>
       </c>
       <c r="D466" t="s">
-        <v>347</v>
+        <v>336</v>
       </c>
       <c r="E466" t="s">
-        <v>765</v>
+        <v>754</v>
       </c>
       <c r="F466" t="s">
         <v>792</v>
@@ -14235,13 +14379,13 @@
         <v>425</v>
       </c>
       <c r="B467" t="s">
-        <v>399</v>
+        <v>388</v>
       </c>
       <c r="D467" t="s">
-        <v>348</v>
+        <v>337</v>
       </c>
       <c r="E467" t="s">
-        <v>766</v>
+        <v>755</v>
       </c>
       <c r="F467" t="s">
         <v>792</v>
@@ -14255,13 +14399,13 @@
         <v>425</v>
       </c>
       <c r="B468" t="s">
-        <v>400</v>
+        <v>389</v>
       </c>
       <c r="D468" t="s">
-        <v>349</v>
+        <v>338</v>
       </c>
       <c r="E468" t="s">
-        <v>767</v>
+        <v>756</v>
       </c>
       <c r="F468" t="s">
         <v>792</v>
@@ -14275,13 +14419,13 @@
         <v>425</v>
       </c>
       <c r="B469" t="s">
-        <v>1207</v>
+        <v>1510</v>
       </c>
       <c r="D469" t="s">
-        <v>1155</v>
+        <v>1511</v>
       </c>
       <c r="E469" t="s">
-        <v>1259</v>
+        <v>1512</v>
       </c>
       <c r="F469" t="s">
         <v>792</v>
@@ -14295,13 +14439,13 @@
         <v>425</v>
       </c>
       <c r="B470" t="s">
-        <v>1495</v>
+        <v>390</v>
       </c>
       <c r="D470" t="s">
-        <v>1496</v>
+        <v>339</v>
       </c>
       <c r="E470" t="s">
-        <v>1497</v>
+        <v>757</v>
       </c>
       <c r="F470" t="s">
         <v>792</v>
@@ -14315,13 +14459,13 @@
         <v>425</v>
       </c>
       <c r="B471" t="s">
-        <v>1354</v>
+        <v>391</v>
       </c>
       <c r="D471" t="s">
-        <v>1355</v>
+        <v>340</v>
       </c>
       <c r="E471" t="s">
-        <v>1356</v>
+        <v>758</v>
       </c>
       <c r="F471" t="s">
         <v>792</v>
@@ -14335,13 +14479,13 @@
         <v>425</v>
       </c>
       <c r="B472" t="s">
-        <v>401</v>
+        <v>392</v>
       </c>
       <c r="D472" t="s">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="E472" t="s">
-        <v>768</v>
+        <v>759</v>
       </c>
       <c r="F472" t="s">
         <v>792</v>
@@ -14355,13 +14499,13 @@
         <v>425</v>
       </c>
       <c r="B473" t="s">
-        <v>1357</v>
+        <v>1204</v>
       </c>
       <c r="D473" t="s">
-        <v>1358</v>
+        <v>1152</v>
       </c>
       <c r="E473" t="s">
-        <v>1359</v>
+        <v>1256</v>
       </c>
       <c r="F473" t="s">
         <v>792</v>
@@ -14375,13 +14519,13 @@
         <v>425</v>
       </c>
       <c r="B474" t="s">
-        <v>402</v>
+        <v>393</v>
       </c>
       <c r="D474" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="E474" t="s">
-        <v>769</v>
+        <v>760</v>
       </c>
       <c r="F474" t="s">
         <v>792</v>
@@ -14395,13 +14539,13 @@
         <v>425</v>
       </c>
       <c r="B475" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="D475" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="E475" t="s">
-        <v>770</v>
+        <v>761</v>
       </c>
       <c r="F475" t="s">
         <v>792</v>
@@ -14415,13 +14559,13 @@
         <v>425</v>
       </c>
       <c r="B476" t="s">
-        <v>404</v>
+        <v>395</v>
       </c>
       <c r="D476" t="s">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="E476" t="s">
-        <v>771</v>
+        <v>762</v>
       </c>
       <c r="F476" t="s">
         <v>792</v>
@@ -14435,13 +14579,13 @@
         <v>425</v>
       </c>
       <c r="B477" t="s">
-        <v>405</v>
+        <v>1205</v>
       </c>
       <c r="D477" t="s">
-        <v>354</v>
+        <v>1153</v>
       </c>
       <c r="E477" t="s">
-        <v>772</v>
+        <v>1257</v>
       </c>
       <c r="F477" t="s">
         <v>792</v>
@@ -14455,13 +14599,13 @@
         <v>425</v>
       </c>
       <c r="B478" t="s">
-        <v>406</v>
+        <v>396</v>
       </c>
       <c r="D478" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="E478" t="s">
-        <v>773</v>
+        <v>763</v>
       </c>
       <c r="F478" t="s">
         <v>792</v>
@@ -14475,13 +14619,13 @@
         <v>425</v>
       </c>
       <c r="B479" t="s">
-        <v>407</v>
+        <v>1206</v>
       </c>
       <c r="D479" t="s">
-        <v>356</v>
+        <v>1154</v>
       </c>
       <c r="E479" t="s">
-        <v>774</v>
+        <v>1258</v>
       </c>
       <c r="F479" t="s">
         <v>792</v>
@@ -14495,13 +14639,13 @@
         <v>425</v>
       </c>
       <c r="B480" t="s">
-        <v>1208</v>
+        <v>397</v>
       </c>
       <c r="D480" t="s">
-        <v>1156</v>
+        <v>346</v>
       </c>
       <c r="E480" t="s">
-        <v>1260</v>
+        <v>764</v>
       </c>
       <c r="F480" t="s">
         <v>792</v>
@@ -14515,13 +14659,13 @@
         <v>425</v>
       </c>
       <c r="B481" t="s">
-        <v>1507</v>
+        <v>398</v>
       </c>
       <c r="D481" t="s">
-        <v>1508</v>
+        <v>347</v>
       </c>
       <c r="E481" t="s">
-        <v>1509</v>
+        <v>765</v>
       </c>
       <c r="F481" t="s">
         <v>792</v>
@@ -14535,13 +14679,13 @@
         <v>425</v>
       </c>
       <c r="B482" t="s">
-        <v>408</v>
+        <v>399</v>
       </c>
       <c r="D482" t="s">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="E482" t="s">
-        <v>775</v>
+        <v>766</v>
       </c>
       <c r="F482" t="s">
         <v>792</v>
@@ -14555,13 +14699,13 @@
         <v>425</v>
       </c>
       <c r="B483" t="s">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="D483" t="s">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="E483" t="s">
-        <v>776</v>
+        <v>767</v>
       </c>
       <c r="F483" t="s">
         <v>792</v>
@@ -14575,13 +14719,13 @@
         <v>425</v>
       </c>
       <c r="B484" t="s">
-        <v>410</v>
+        <v>1207</v>
       </c>
       <c r="D484" t="s">
-        <v>359</v>
+        <v>1155</v>
       </c>
       <c r="E484" t="s">
-        <v>777</v>
+        <v>1259</v>
       </c>
       <c r="F484" t="s">
         <v>792</v>
@@ -14595,13 +14739,13 @@
         <v>425</v>
       </c>
       <c r="B485" t="s">
-        <v>411</v>
+        <v>1495</v>
       </c>
       <c r="D485" t="s">
-        <v>360</v>
+        <v>1496</v>
       </c>
       <c r="E485" t="s">
-        <v>778</v>
+        <v>1497</v>
       </c>
       <c r="F485" t="s">
         <v>792</v>
@@ -14615,13 +14759,13 @@
         <v>425</v>
       </c>
       <c r="B486" t="s">
-        <v>412</v>
+        <v>1354</v>
       </c>
       <c r="D486" t="s">
-        <v>361</v>
+        <v>1355</v>
       </c>
       <c r="E486" t="s">
-        <v>779</v>
+        <v>1356</v>
       </c>
       <c r="F486" t="s">
         <v>792</v>
@@ -14635,13 +14779,13 @@
         <v>425</v>
       </c>
       <c r="B487" t="s">
-        <v>413</v>
+        <v>401</v>
       </c>
       <c r="D487" t="s">
-        <v>362</v>
+        <v>350</v>
       </c>
       <c r="E487" t="s">
-        <v>780</v>
+        <v>768</v>
       </c>
       <c r="F487" t="s">
         <v>792</v>
@@ -14655,13 +14799,13 @@
         <v>425</v>
       </c>
       <c r="B488" t="s">
-        <v>414</v>
+        <v>1357</v>
       </c>
       <c r="D488" t="s">
-        <v>363</v>
+        <v>1358</v>
       </c>
       <c r="E488" t="s">
-        <v>781</v>
+        <v>1359</v>
       </c>
       <c r="F488" t="s">
         <v>792</v>
@@ -14675,13 +14819,13 @@
         <v>425</v>
       </c>
       <c r="B489" t="s">
-        <v>415</v>
+        <v>402</v>
       </c>
       <c r="D489" t="s">
-        <v>364</v>
+        <v>351</v>
       </c>
       <c r="E489" t="s">
-        <v>782</v>
+        <v>769</v>
       </c>
       <c r="F489" t="s">
         <v>792</v>
@@ -14695,13 +14839,13 @@
         <v>425</v>
       </c>
       <c r="B490" t="s">
-        <v>416</v>
+        <v>403</v>
       </c>
       <c r="D490" t="s">
-        <v>365</v>
+        <v>352</v>
       </c>
       <c r="E490" t="s">
-        <v>783</v>
+        <v>770</v>
       </c>
       <c r="F490" t="s">
         <v>792</v>
@@ -14715,13 +14859,13 @@
         <v>425</v>
       </c>
       <c r="B491" t="s">
-        <v>1209</v>
+        <v>404</v>
       </c>
       <c r="D491" t="s">
-        <v>1157</v>
+        <v>353</v>
       </c>
       <c r="E491" t="s">
-        <v>1261</v>
+        <v>771</v>
       </c>
       <c r="F491" t="s">
         <v>792</v>
@@ -14735,13 +14879,13 @@
         <v>425</v>
       </c>
       <c r="B492" t="s">
-        <v>417</v>
+        <v>405</v>
       </c>
       <c r="D492" t="s">
-        <v>366</v>
+        <v>354</v>
       </c>
       <c r="E492" t="s">
-        <v>784</v>
+        <v>772</v>
       </c>
       <c r="F492" t="s">
         <v>792</v>
@@ -14755,13 +14899,13 @@
         <v>425</v>
       </c>
       <c r="B493" t="s">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="D493" t="s">
-        <v>367</v>
+        <v>355</v>
       </c>
       <c r="E493" t="s">
-        <v>785</v>
+        <v>773</v>
       </c>
       <c r="F493" t="s">
         <v>792</v>
@@ -14775,13 +14919,13 @@
         <v>425</v>
       </c>
       <c r="B494" t="s">
-        <v>1210</v>
+        <v>407</v>
       </c>
       <c r="D494" t="s">
-        <v>1158</v>
+        <v>356</v>
       </c>
       <c r="E494" t="s">
-        <v>1262</v>
+        <v>774</v>
       </c>
       <c r="F494" t="s">
         <v>792</v>
@@ -14795,13 +14939,13 @@
         <v>425</v>
       </c>
       <c r="B495" t="s">
-        <v>419</v>
+        <v>1208</v>
       </c>
       <c r="D495" t="s">
-        <v>368</v>
+        <v>1156</v>
       </c>
       <c r="E495" t="s">
-        <v>786</v>
+        <v>1260</v>
       </c>
       <c r="F495" t="s">
         <v>792</v>
@@ -14815,13 +14959,13 @@
         <v>425</v>
       </c>
       <c r="B496" t="s">
-        <v>1360</v>
+        <v>1507</v>
       </c>
       <c r="D496" t="s">
-        <v>1361</v>
+        <v>1508</v>
       </c>
       <c r="E496" t="s">
-        <v>1362</v>
+        <v>1509</v>
       </c>
       <c r="F496" t="s">
         <v>792</v>
@@ -14835,13 +14979,13 @@
         <v>425</v>
       </c>
       <c r="B497" t="s">
-        <v>420</v>
+        <v>408</v>
       </c>
       <c r="D497" t="s">
-        <v>369</v>
+        <v>357</v>
       </c>
       <c r="E497" t="s">
-        <v>787</v>
+        <v>775</v>
       </c>
       <c r="F497" t="s">
         <v>792</v>
@@ -14855,13 +14999,13 @@
         <v>425</v>
       </c>
       <c r="B498" t="s">
-        <v>421</v>
+        <v>409</v>
       </c>
       <c r="D498" t="s">
-        <v>370</v>
+        <v>358</v>
       </c>
       <c r="E498" t="s">
-        <v>788</v>
+        <v>776</v>
       </c>
       <c r="F498" t="s">
         <v>792</v>
@@ -14875,13 +15019,13 @@
         <v>425</v>
       </c>
       <c r="B499" t="s">
-        <v>422</v>
+        <v>410</v>
       </c>
       <c r="D499" t="s">
-        <v>371</v>
+        <v>359</v>
       </c>
       <c r="E499" t="s">
-        <v>789</v>
+        <v>777</v>
       </c>
       <c r="F499" t="s">
         <v>792</v>
@@ -14895,13 +15039,13 @@
         <v>425</v>
       </c>
       <c r="B500" t="s">
-        <v>423</v>
+        <v>411</v>
       </c>
       <c r="D500" t="s">
-        <v>372</v>
+        <v>360</v>
       </c>
       <c r="E500" t="s">
-        <v>790</v>
+        <v>778</v>
       </c>
       <c r="F500" t="s">
         <v>792</v>
@@ -14915,13 +15059,13 @@
         <v>425</v>
       </c>
       <c r="B501" t="s">
-        <v>424</v>
+        <v>412</v>
       </c>
       <c r="D501" t="s">
-        <v>373</v>
+        <v>361</v>
       </c>
       <c r="E501" t="s">
-        <v>791</v>
+        <v>779</v>
       </c>
       <c r="F501" t="s">
         <v>792</v>
@@ -14935,18 +15079,338 @@
         <v>425</v>
       </c>
       <c r="B502" t="s">
+        <v>413</v>
+      </c>
+      <c r="D502" t="s">
+        <v>362</v>
+      </c>
+      <c r="E502" t="s">
+        <v>780</v>
+      </c>
+      <c r="F502" t="s">
+        <v>792</v>
+      </c>
+      <c r="G502" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="503" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A503" t="s">
+        <v>425</v>
+      </c>
+      <c r="B503" t="s">
+        <v>414</v>
+      </c>
+      <c r="D503" t="s">
+        <v>363</v>
+      </c>
+      <c r="E503" t="s">
+        <v>781</v>
+      </c>
+      <c r="F503" t="s">
+        <v>792</v>
+      </c>
+      <c r="G503" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="504" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A504" t="s">
+        <v>425</v>
+      </c>
+      <c r="B504" t="s">
+        <v>415</v>
+      </c>
+      <c r="D504" t="s">
+        <v>364</v>
+      </c>
+      <c r="E504" t="s">
+        <v>782</v>
+      </c>
+      <c r="F504" t="s">
+        <v>792</v>
+      </c>
+      <c r="G504" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="505" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A505" t="s">
+        <v>425</v>
+      </c>
+      <c r="B505" t="s">
+        <v>416</v>
+      </c>
+      <c r="D505" t="s">
+        <v>365</v>
+      </c>
+      <c r="E505" t="s">
+        <v>783</v>
+      </c>
+      <c r="F505" t="s">
+        <v>792</v>
+      </c>
+      <c r="G505" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="506" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A506" t="s">
+        <v>425</v>
+      </c>
+      <c r="B506" t="s">
+        <v>1209</v>
+      </c>
+      <c r="D506" t="s">
+        <v>1157</v>
+      </c>
+      <c r="E506" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F506" t="s">
+        <v>792</v>
+      </c>
+      <c r="G506" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="507" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A507" t="s">
+        <v>425</v>
+      </c>
+      <c r="B507" t="s">
+        <v>417</v>
+      </c>
+      <c r="D507" t="s">
+        <v>366</v>
+      </c>
+      <c r="E507" t="s">
+        <v>784</v>
+      </c>
+      <c r="F507" t="s">
+        <v>792</v>
+      </c>
+      <c r="G507" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="508" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A508" t="s">
+        <v>425</v>
+      </c>
+      <c r="B508" t="s">
+        <v>418</v>
+      </c>
+      <c r="D508" t="s">
+        <v>367</v>
+      </c>
+      <c r="E508" t="s">
+        <v>785</v>
+      </c>
+      <c r="F508" t="s">
+        <v>792</v>
+      </c>
+      <c r="G508" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="509" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A509" t="s">
+        <v>425</v>
+      </c>
+      <c r="B509" t="s">
+        <v>1210</v>
+      </c>
+      <c r="D509" t="s">
+        <v>1158</v>
+      </c>
+      <c r="E509" t="s">
+        <v>1262</v>
+      </c>
+      <c r="F509" t="s">
+        <v>792</v>
+      </c>
+      <c r="G509" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="510" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A510" t="s">
+        <v>425</v>
+      </c>
+      <c r="B510" t="s">
+        <v>419</v>
+      </c>
+      <c r="D510" t="s">
+        <v>368</v>
+      </c>
+      <c r="E510" t="s">
+        <v>786</v>
+      </c>
+      <c r="F510" t="s">
+        <v>792</v>
+      </c>
+      <c r="G510" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="511" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A511" t="s">
+        <v>425</v>
+      </c>
+      <c r="B511" t="s">
+        <v>1558</v>
+      </c>
+      <c r="D511" t="s">
+        <v>1559</v>
+      </c>
+      <c r="E511" t="s">
+        <v>1560</v>
+      </c>
+      <c r="F511" t="s">
+        <v>792</v>
+      </c>
+      <c r="G511" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="512" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A512" t="s">
+        <v>425</v>
+      </c>
+      <c r="B512" t="s">
+        <v>1360</v>
+      </c>
+      <c r="D512" t="s">
+        <v>1361</v>
+      </c>
+      <c r="E512" t="s">
+        <v>1362</v>
+      </c>
+      <c r="F512" t="s">
+        <v>792</v>
+      </c>
+      <c r="G512" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="513" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A513" t="s">
+        <v>425</v>
+      </c>
+      <c r="B513" t="s">
+        <v>420</v>
+      </c>
+      <c r="D513" t="s">
+        <v>369</v>
+      </c>
+      <c r="E513" t="s">
+        <v>787</v>
+      </c>
+      <c r="F513" t="s">
+        <v>792</v>
+      </c>
+      <c r="G513" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="514" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A514" t="s">
+        <v>425</v>
+      </c>
+      <c r="B514" t="s">
+        <v>421</v>
+      </c>
+      <c r="D514" t="s">
+        <v>370</v>
+      </c>
+      <c r="E514" t="s">
+        <v>788</v>
+      </c>
+      <c r="F514" t="s">
+        <v>792</v>
+      </c>
+      <c r="G514" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="515" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A515" t="s">
+        <v>425</v>
+      </c>
+      <c r="B515" t="s">
+        <v>422</v>
+      </c>
+      <c r="D515" t="s">
+        <v>371</v>
+      </c>
+      <c r="E515" t="s">
+        <v>789</v>
+      </c>
+      <c r="F515" t="s">
+        <v>792</v>
+      </c>
+      <c r="G515" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="516" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A516" t="s">
+        <v>425</v>
+      </c>
+      <c r="B516" t="s">
+        <v>423</v>
+      </c>
+      <c r="D516" t="s">
+        <v>372</v>
+      </c>
+      <c r="E516" t="s">
+        <v>790</v>
+      </c>
+      <c r="F516" t="s">
+        <v>792</v>
+      </c>
+      <c r="G516" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="517" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A517" t="s">
+        <v>425</v>
+      </c>
+      <c r="B517" t="s">
+        <v>424</v>
+      </c>
+      <c r="D517" t="s">
+        <v>373</v>
+      </c>
+      <c r="E517" t="s">
+        <v>791</v>
+      </c>
+      <c r="F517" t="s">
+        <v>792</v>
+      </c>
+      <c r="G517" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="518" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A518" t="s">
+        <v>425</v>
+      </c>
+      <c r="B518" t="s">
         <v>1211</v>
       </c>
-      <c r="D502" t="s">
+      <c r="D518" t="s">
         <v>1159</v>
       </c>
-      <c r="E502" t="s">
+      <c r="E518" t="s">
         <v>1263</v>
       </c>
-      <c r="F502" t="s">
-        <v>792</v>
-      </c>
-      <c r="G502" t="s">
+      <c r="F518" t="s">
+        <v>792</v>
+      </c>
+      <c r="G518" t="s">
         <v>7</v>
       </c>
     </row>
